--- a/PTBR/Lang/PTBR/Dialog/Drama/loytel.xlsx
+++ b/PTBR/Lang/PTBR/Dialog/Drama/loytel.xlsx
@@ -17,7 +17,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="17">
+  <fonts count="18">
     <font>
       <name val="游ゴシック"/>
       <charset val="128"/>
@@ -128,6 +128,13 @@
       <color rgb="FF000000"/>
       <sz val="11"/>
     </font>
+    <font>
+      <name val="ＭＳ ゴシック;Noto Sans JP;游ゴシック;メイリオ"/>
+      <charset val="128"/>
+      <family val="3"/>
+      <color rgb="FF000000"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -162,7 +169,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="62">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -256,7 +263,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -343,6 +350,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="general" vertical="bottom" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -543,8 +553,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N709"/>
-  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:N758"/>
+  <sheetFormatPr baseColWidth="8" defaultColWidth="11.53515625" defaultRowHeight="12.8" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="8.85" customWidth="1" style="32" min="1" max="1"/>
     <col width="19.85" customWidth="1" style="32" min="2" max="2"/>
@@ -654,9 +664,9 @@
           <t>What is it? Make it quick, I'm busy.</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>O que foi? Seja rápido, estou ocupado(a).</t>
+      <c r="L8" s="32" t="inlineStr">
+        <is>
+          <t>Que foi? Depressa, estou ocupado.</t>
         </is>
       </c>
     </row>
@@ -688,7 +698,7 @@
           <t>I have some questions.</t>
         </is>
       </c>
-      <c r="L10" t="inlineStr">
+      <c r="L10" s="32" t="inlineStr">
         <is>
           <t>Tenho algumas perguntas.</t>
         </is>
@@ -718,9 +728,9 @@
           <t>Can you give me advice on frontier business?</t>
         </is>
       </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>Você pode me dar conselhos sobre negócios na fronteira?</t>
+      <c r="L11" s="32" t="inlineStr">
+        <is>
+          <t>Pode me dar conselhos sobre negócios de fronteira?</t>
         </is>
       </c>
     </row>
@@ -769,9 +779,9 @@
           <t>What do you want to know?</t>
         </is>
       </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que você quer saber?  </t>
+      <c r="L16" s="32" t="inlineStr">
+        <is>
+          <t>O que você quer saber?</t>
         </is>
       </c>
     </row>
@@ -799,9 +809,9 @@
           <t>Ash and Fia's job</t>
         </is>
       </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O trabalho de Ash e Fia  </t>
+      <c r="L17" s="32" t="inlineStr">
+        <is>
+          <t>Trabalho de Ash e Fia</t>
         </is>
       </c>
     </row>
@@ -829,9 +839,9 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Voltar)  </t>
+      <c r="L18" s="32" t="inlineStr">
+        <is>
+          <t>(Voltar)</t>
         </is>
       </c>
     </row>
@@ -868,9 +878,9 @@
           <t>You haven't heard anything from them? Well, perhaps it's better for you not to know then.</t>
         </is>
       </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você não ouviu nada deles? Bem, talvez seja melhor que você não saiba então.  </t>
+      <c r="L22" s="32" t="inlineStr">
+        <is>
+          <t>Você não ouviu nada delas? Bom, talvez seja melhor você não saber, então.</t>
         </is>
       </c>
     </row>
@@ -900,9 +910,9 @@
           <t>Good thinking. What do you need to know?</t>
         </is>
       </c>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Boa ideia. O que você precisa saber?  </t>
+      <c r="L25" s="32" t="inlineStr">
+        <is>
+          <t>Bem pensado. O que você precisa saber?</t>
         </is>
       </c>
     </row>
@@ -930,9 +940,9 @@
           <t>About Hearth Stone</t>
         </is>
       </c>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sobre a Pedra do Lar  </t>
+      <c r="L26" s="32" t="inlineStr">
+        <is>
+          <t>Sobre a Pedra do Lar</t>
         </is>
       </c>
     </row>
@@ -960,9 +970,9 @@
           <t>Home Ranking</t>
         </is>
       </c>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Classificação das Casas  </t>
+      <c r="L27" s="32" t="inlineStr">
+        <is>
+          <t>Ranking do Lar</t>
         </is>
       </c>
     </row>
@@ -990,9 +1000,9 @@
           <t>Opening business</t>
         </is>
       </c>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Abrindo um negócio  </t>
+      <c r="L28" s="32" t="inlineStr">
+        <is>
+          <t>Abrindo negócios</t>
         </is>
       </c>
     </row>
@@ -1020,9 +1030,9 @@
           <t>Running a tourist spot</t>
         </is>
       </c>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Gerenciando um ponto turístico  </t>
+      <c r="L29" s="32" t="inlineStr">
+        <is>
+          <t>Administrando um ponto turístico</t>
         </is>
       </c>
     </row>
@@ -1050,9 +1060,9 @@
           <t>Running a shop</t>
         </is>
       </c>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Administrando uma loja  </t>
+      <c r="L30" s="32" t="inlineStr">
+        <is>
+          <t>Administrando uma loja</t>
         </is>
       </c>
     </row>
@@ -1085,9 +1095,9 @@
           <t>About Tax Free Land</t>
         </is>
       </c>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sobre Terras Isentas de Impostos  </t>
+      <c r="L31" s="32" t="inlineStr">
+        <is>
+          <t>Sobre Terras Isentas de Imposto</t>
         </is>
       </c>
     </row>
@@ -1115,9 +1125,9 @@
           <t>(Back)</t>
         </is>
       </c>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Voltar)  </t>
+      <c r="L32" s="32" t="inlineStr">
+        <is>
+          <t>(Voltar)</t>
         </is>
       </c>
     </row>
@@ -1163,13 +1173,11 @@
 You can check the current heirlooms, as well as your home ranking position and rewards, from the Home Board.</t>
         </is>
       </c>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>Entre os móveis instalados em sua base, os itens mais valiosos no topo são designados como "Relíquia". Competir pelo valor dessas relíquias é conhecido como "Classificação das Casas"._x000D_
-_x000D_
-Se você ficar entre os 125 melhores nessa classificação, receberá uma quantia fixa de recompensas todo mês, o que pode ser uma fonte valiosa de renda no início._x000D_
-_x000D_
-Você pode verificar as relíquias atuais, assim como sua posição na classificação das casas e suas recompensas, no Quadro da Casa.</t>
+      <c r="L36" s="32" t="inlineStr">
+        <is>
+          <t>Entre os móveis instalados na sua base, os poucos mais valiosos são designados "Relíquias de Família". Disputar o valor dessas relíquias é o que chamamos de "Ranking do Lar".
+Se você ficar entre os 125 primeiros deste ranking, recebe um conjunto de recompensas todo mês, o que pode ser uma fonte de renda valiosa no começo.
+Você pode conferir as relíquias atuais, além da posição e das recompensas do seu ranking, no Quadro do Lar.</t>
         </is>
       </c>
     </row>
@@ -1209,13 +1217,11 @@
 I have the Open for Business policy book in stock as well, so check my wares if you want it.</t>
         </is>
       </c>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Seja criando um ponto turístico ou abrindo uma loja, é óbvio que você não pode fazer negócios sem clientes. Para atrair clientes para sua base, você precisa implementar a política "Aberto para Negócios"._x000D_
-_x000D_
-Quando essa política estiver ativa, os clientes começarão a visitar sua base de acordo com sua popularidade. A maioria dos clientes ficará por alguns dias, então, se você fornecer camas para eles, também poderá ganhar taxas de hospedagem._x000D_
-_x000D_
-Eu tenho o livro da política Aberto para Negócios em estoque, então confira meus produtos se quiser um.  </t>
+      <c r="L40" s="32" t="inlineStr">
+        <is>
+          <t>Quer montar um ponto turístico ou abrir uma loja, é óbvio que não há negócio sem clientes. Para atrair clientes à sua base, você precisa ativar a política "Aberto ao Público".
+Com a política ativa, os clientes começam a chegar conforme a fama da sua base. A maioria fica alguns dias, então, se oferecer camas, você ainda ganha diárias.
+Eu tenho o livro da política Aberto ao Público em estoque, dá uma olhada no meu balcão se quiser.</t>
         </is>
       </c>
     </row>
@@ -1254,11 +1260,11 @@
 </t>
         </is>
       </c>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sua base tem um valor turístico, que aumenta com a instalação de exibições como figuras, cartas e pinturas.  _x000D_
-_x000D_
-Quando o valor turístico for alto, você poderá receber uma renda diária de turismo vinda dos visitantes. Embora a renda possa não ser tão significativa no início, com poucas exibições, ainda é uma fonte razoável de ganhos nos estágios iniciais.  </t>
+      <c r="L44" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sua base tem um valor turístico, que aumenta ao instalar exposições como bonecos, cartas e pinturas.
+Com o valor turístico alto, você recebe renda diária dos visitantes. No começo, com poucas exposições, a renda pode ser pequena, mas ainda é uma fonte decente nos estágios iniciais.
+</t>
         </is>
       </c>
     </row>
@@ -1298,13 +1304,11 @@
 You can easily make price tags at the Signboard Workshop, so give it a try If you're interested,</t>
         </is>
       </c>
-      <c r="L48" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Interessado em administrar uma loja?  _x000D_
-_x000D_
-Você pode vender itens para os clientes colocando etiquetas de preço nos itens instalados em sua base. Diferente do envio de produtos através de uma caixa de transporte, esse método leva mais tempo, mas gera lucros maiores.  _x000D_
-_x000D_
-Você pode criar etiquetas de preço facilmente na Oficina de Placas, então experimente se estiver interessado.  </t>
+      <c r="L48" s="32" t="inlineStr">
+        <is>
+          <t>Interessado em administrar uma loja?
+Você vende itens aos clientes prendendo etiquetas de preço nos itens instalados na base. Diferente de despachar pela caixa de remessas, esse método demora mais mas rende mais.
+Etiquetas se fazem fácil na Oficina de Placas, então tente se estiver interessado.</t>
         </is>
       </c>
     </row>
@@ -1324,11 +1328,10 @@
 When an item sells out, a "sold out" tag is automatically placed in its spot. If there are other items of the same category around the sign, residents will automatically restock the items for you.</t>
         </is>
       </c>
-      <c r="L49" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh, e enquanto estiver na oficina, você também deve fazer uma "Placa de Estoque de Mercadorias".  _x000D_
-_x000D_
-Quando um item se esgota, uma etiqueta de "esgotado" é automaticamente colocada no lugar. Se houver outros itens da mesma categoria próximos à placa, os residentes irão reabastecê-los automaticamente para você.  </t>
+      <c r="L49" s="32" t="inlineStr">
+        <is>
+          <t>Ah, e já que está na oficina, faça também uma "Placa de Estoque".
+Quando um item esgota, uma etiqueta de "esgotado" aparece no lugar dele automaticamente. Se houver outros itens da mesma categoria perto da placa, os moradores repõem o estoque por conta própria.</t>
         </is>
       </c>
     </row>
@@ -1350,13 +1353,11 @@
 Once all the items inside are sold, the price tag will be removed. However, if you find it troublesome to put the price tag back on, you can leave one "unsellable item" inside.</t>
         </is>
       </c>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aqui vai uma dica útil para você.  _x000D_
-_x000D_
-Se você colocar uma etiqueta de preço em um recipiente com itens dentro, poderá vender tudo como um pacote.  _x000D_
-_x000D_
-Quando todos os itens dentro forem vendidos, a etiqueta de preço será removida. No entanto, se achar incômodo recolocá-la, pode deixar um "item não vendável" dentro.  </t>
+      <c r="L50" s="32" t="inlineStr">
+        <is>
+          <t>Aqui vai uma dica útil.
+Se prender uma etiqueta de preço num contêiner com itens dentro, você vende tudo dentro dele como pacote.
+Quando todos os itens forem vendidos, a etiqueta sai. Mas se for chato recolocar a etiqueta, deixe um "item invendável" dentro.</t>
         </is>
       </c>
     </row>
@@ -1394,11 +1395,10 @@
 The growth of the Hearth Stone is crucial for developing your base, as it increases the admin power needed to enforce policies, unlocks building modes, and prevents enemies from destroying items at your base. </t>
         </is>
       </c>
-      <c r="L54" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sua terra possui uma pedra mística conhecida como "Pedra do Lar", uma pedra espiritual que, segundo antigos pactos, promete a prosperidade da sua terra.  _x000D_
-_x000D_
-O crescimento da Pedra do Lar é essencial para o desenvolvimento da sua base, pois aumenta o poder administrativo necessário para impor políticas, desbloqueia modos de construção e impede que inimigos destruam itens na sua base.  </t>
+      <c r="L54" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sua terra guarda uma pedra mística chamada "Pedra do Lar", uma pedra espiritual que, segundo pactos antigos, promete a prosperidade da sua terra.
+O crescimento da Pedra do Lar é crucial para desenvolver a base: ela aumenta o poder administrativo necessário para as políticas, destrava modos de construção e impede que inimigos destrutam seus itens. </t>
         </is>
       </c>
     </row>
@@ -1420,13 +1420,11 @@
 Once the experience points reach their maximum, the stone will automatically level up. </t>
         </is>
       </c>
-      <c r="L55" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Para fazer a pedra crescer, você precisa acumular seus pontos de experiência até o máximo. Os pontos de experiência aumentam com o tempo, mesmo que você não faça nada, mas também podem ser ganhos enviando itens ou através de ações específicas dos moradores.  _x000D_
-_x000D_
-Ao enviar regularmente itens indesejados e contratar muitos moradores, os pontos de experiência irão se acumular naturalmente.  _x000D_
-_x000D_
-Assim que os pontos de experiência atingirem o máximo, a pedra subirá de nível automaticamente.  </t>
+      <c r="L55" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Para crescer a pedra, é preciso acumular o máximo dos pontos de experiência dela. A experiência aumenta com o tempo mesmo sem você fazer nada, mas também sobe despachando itens ou com ações específicas dos moradores.
+Despachando itens indesejados regularmente e contratando muitos moradores, a experiência acumula naturalmente.
+Quando a experiência chegar ao máximo, a pedra sobe de nível sozinha. </t>
         </is>
       </c>
     </row>
@@ -1444,9 +1442,9 @@
           <t xml:space="preserve">One thing to note is that as the Hearth Stone grows, the strength of the enemies that appear at your base will also increase. If you are struggling with the current enemies attacking your base, it might be wise to enact a "Growth Suppression" policy to slow down the stone's growth. </t>
         </is>
       </c>
-      <c r="L56" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Uma coisa importante a se notar é que, à medida que a Pedra do Lar cresce, a força dos inimigos que aparecem na sua base também aumentará. Se estiver tendo dificuldades com os inimigos que estão atacando sua base, pode ser sábio adotar a política de "Supressão de Crescimento" para desacelerar o crescimento da pedra.  </t>
+      <c r="L56" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Um detalhe: conforme a Pedra do Lar cresce, a força dos inimigos que surgem na sua base também aumenta. Se você está apanhando dos inimigos atuais, pode ser sábio decretar a política "Supressão de Crescimento" para frear o crescimento da pedra. </t>
         </is>
       </c>
     </row>
@@ -1482,13 +1480,11 @@
 You don't need to worry about it now, but remember that it will be difficult to generate satisfactory income from non-exempt land. </t>
         </is>
       </c>
-      <c r="L60" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não há desvantagens em possuir muitas terras, mas simplesmente aumentar a quantidade de terras que você possui não dobrará necessariamente sua renda.  _x000D_
-_x000D_
-Em Mysilia, existe um sistema de isenção de impostos, e essa política é inicialmente aplicada às primeiras terras que você adquire.  _x000D_
-_x000D_
-Você não precisa se preocupar com isso agora, mas lembre-se de que será difícil gerar uma renda satisfatória em terras não isentas.  </t>
+      <c r="L60" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não há desvantagem em possuir muitas terras, mas simplesmente aumentar a quantidade não dobra a renda por tabela.
+Em Mysilia existe um sistema de isenção fiscal, e essa política se aplica de início às primeiras terras que você possuir.
+Não precisa se preocupar agora, mas lembre que será difícil tirar renda satisfatória de terras não isentas. </t>
         </is>
       </c>
     </row>
@@ -1508,11 +1504,10 @@
 Taxes on non-exempt land apply to tourism income, lodging fees, and residential taxes. Shipping and sales of goods to visitors are not affected, so you can proceed without concern.</t>
         </is>
       </c>
-      <c r="L61" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Atualmente, apenas três terrenos podem ser designados como terras isentas de impostos. Se você planeja desenvolver atrações turísticas ou acomodações, leve isso em consideração.  _x000D_
-_x000D_
-Os impostos sobre terras não isentas se aplicam à renda do turismo, às taxas de hospedagem e aos impostos residenciais. O envio e a venda de mercadorias para visitantes não são afetados, então você pode prosseguir sem preocupação.  </t>
+      <c r="L61" s="32" t="inlineStr">
+        <is>
+          <t>Atualmente, só três terras podem ser designadas isentas de imposto. Se pretende desenvolver pontos turísticos ou hospedagens, não esqueça.
+O imposto sobre terras não isentas incide sobre renda turística, diárias e imposto residencial. Despacho e venda para visitantes não são afetados, pode seguir sem medo.</t>
         </is>
       </c>
     </row>
@@ -1546,11 +1541,10 @@
 I may feel somewhat tricked by Ashland's persuasive words, but working leisurely surrounded by nature isn’t too bad. When you’re a inspector of my caliber, works from renowned nobilities in Mysilia come flooding in non-stop. Perhaps, my weary soul needed this brief respite in a tranquil meadow.</t>
         </is>
       </c>
-      <c r="L65" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por que essa cara triste? Não há motivo para se encolher.  _x000D_
-_x000D_
-Posso até me sentir um pouco enganado pelas palavras persuasivas de Ashland, mas trabalhar tranquilamente cercado pela natureza não é tão ruim. Quando se é um inspetor do meu nível, obras de nobres renomados de Mysilia chegam sem parar. Talvez minha alma cansada precisasse desse breve descanso em um campo tranquilo.  </t>
+      <c r="L65" s="32" t="inlineStr">
+        <is>
+          <t>Por que essa cara? Não precisa se encolher assim.
+Posso me sentir meio enganado pelas palavras persuasivas de Ashland, mas trabalhar de boa cercado pela natureza não é ruim de todo. Quando se é um inspetor da minha laia, os trabalhos das nobrezas renomadas de Mysilia chegam sem parar. Talvez minha alma cansada precisasse desta breve pausa numa campina tranquila.</t>
         </is>
       </c>
     </row>
@@ -1568,9 +1562,9 @@
           <t>Rest assured, I'm almost grateful to Ashland right now. I'll handle my tasks diligently, and the future of this land is practically guaranteed with me in charge.</t>
         </is>
       </c>
-      <c r="L66" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Fique tranquilo, no momento estou quase grato a Ashland. Vou cumprir minhas tarefas com diligência, e o futuro desta terra está praticamente garantido comigo no comando.  </t>
+      <c r="L66" s="32" t="inlineStr">
+        <is>
+          <t>Fique tranquilo, quase que fico grato a Ashland agora. Vou cumprir minhas tarefas com zelo, e o futuro desta terra está praticamente garantido comigo no comando.</t>
         </is>
       </c>
     </row>
@@ -1592,13 +1586,11 @@
 The quickest way to earn money is to ship items from the shipping box. Once you can cultivate fields and harvest crops, it'll become a steady income.</t>
         </is>
       </c>
-      <c r="L67" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agora, você deve ter seus planos, mas antes de tudo, precisamos ganhar dinheiro.  _x000D_
-_x000D_
-Fundos abundantes são essenciais para o desenvolvimento de uma nova terra. Banhos quentes, camas macias e o aroma de vinho doce não são o que você precisa agora. Primeiro, enriquecemos esta terra desde suas raízes.  _x000D_
-_x000D_
-A maneira mais rápida de ganhar dinheiro é enviando itens pela caixa de transporte. Quando puder cultivar campos e colher safras, isso se tornará uma fonte de renda estável.  </t>
+      <c r="L67" s="32" t="inlineStr">
+        <is>
+          <t>Agora, você deve ter seus planos, mas precisamos ganhar dinheiro antes de tudo.
+Fundos fartos são essenciais para o desenvolvimento de uma terra nova. Banho quente, cama macia e cheiro de vinho doce não são o que você precisa neste momento. Primeiro, enriquecemos esta terra desde a raiz.
+O caminho mais rápido é despachar itens pela caixa de remessas. Quando você conseguir cultivar campos e colher plantações, vira renda constante.</t>
         </is>
       </c>
     </row>
@@ -1616,9 +1608,9 @@
           <t>...Huh, what's with that look? As if you've never heard of a shipping box before?</t>
         </is>
       </c>
-      <c r="L68" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Hã? Que olhar é esse? Como se nunca tivesse ouvido falar de uma caixa de transporte antes?  </t>
+      <c r="L68" s="32" t="inlineStr">
+        <is>
+          <t>...Hã, que olhar é esse? Como se você nunca tivesse visto uma caixa de remessas?</t>
         </is>
       </c>
     </row>
@@ -1636,7 +1628,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L69" t="inlineStr">
+      <c r="L69" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -1658,11 +1650,10 @@
 ...Here, I'll give you the materials to make one. Craft a 'shipping box' from the 'workbench' and set it on the ground.</t>
         </is>
       </c>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que descoberta, não há uma caixa de transporte nesta terra ainda! Isso é algum tipo de era primitiva?  _x000D_
-_x000D_
-...Aqui, vou te dar os materiais para fazer uma. Construa uma 'caixa de transporte' na 'bancada de trabalho' e coloque-a no chão.  </t>
+      <c r="L70" s="32" t="inlineStr">
+        <is>
+          <t>Que revelação, não há caixa de remessas nesta terra ainda! Isto é alguma era primitiva?
+...Toma, te dou os materiais para fazer uma. Fabrique uma 'caixa de remessas' na 'bancada de trabalho' e coloque no chão.</t>
         </is>
       </c>
     </row>
@@ -1709,11 +1700,10 @@
 In case you don't know, you can click on an ingredient icon in the crafting screen to change an ingredient.</t>
         </is>
       </c>
-      <c r="L74" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...E lembre-se de usar a madeira de palulu que eu te dei. A caixa de transporte precisa ter a cor chique e elegante da madeira de palulu. Não vou tolerar nada diferente. Isso fere meu senso estético.  _x000D_
-_x000D_
-Caso não saiba, você pode clicar no ícone de um ingrediente na tela de criação para alterá-lo.  </t>
+      <c r="L74" s="32" t="inlineStr">
+        <is>
+          <t>...E lembre de usar a madeira de palulu que te dei. A caixa de remessas precisa ter a cor chique e elegante do palulu. Não tolero nada diferente. Ofende meu senso estético.
+Caso não saiba, você pode clicar no ícone de um ingrediente na tela de fabricação para trocá-lo.</t>
         </is>
       </c>
     </row>
@@ -1757,13 +1747,12 @@
 </t>
         </is>
       </c>
-      <c r="L80" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Hmm, uma caixa de transporte bem colorida e agradável. Finalmente, um raio de civilização brilha sobre esta terra selvagem.  _x000D_
-_x000D_
-Os itens na caixa de transporte são coletados automaticamente todas as manhãs, e os lucros são enviados diretamente para você. Envie uma boa quantidade de itens e até receberá alguns lingotes de ouro.  _x000D_
-_x000D_
-Estou com dor de cabeça, então vou descansar hoje, mas tente jogar alguns itens na caixa de transporte.  </t>
+      <c r="L80" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hum, uma caixa de remessas de cores agradáveis e tranquilizadoras. Finalmente, um raio de civilização brilha sobre esta terra indomada.
+Os itens na caixa de remessas são coletados automaticamente toda manhã, e os ganhos vão direto para você. Despache uma boa quantidade e até barras de ouro aparecem.
+Estou com dor de cabeça, hoje fico descansando, mas tente jogar uns itens na caixa de remessas.
+</t>
         </is>
       </c>
     </row>
@@ -1795,9 +1784,9 @@
           <t>What's with that outfit of yours? ... Are you taking the frontier business lightly?</t>
         </is>
       </c>
-      <c r="L89" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O que é essa roupa que você está usando? ... Está levando o trabalho na fronteira na brincadeira?  </t>
+      <c r="L89" s="32" t="inlineStr">
+        <is>
+          <t>Que roupa é essa sua? ... Você está levando o negócio da fronteira na leveza?</t>
         </is>
       </c>
     </row>
@@ -1815,9 +1804,9 @@
           <t>I don't scold serious pioneers, but I absolutely despise those who treat the frontier as a game or a fanciful dream. Those without commitment are to leave this land, no questions asked.</t>
         </is>
       </c>
-      <c r="L90" t="inlineStr">
-        <is>
-          <t>Eu não repreendo pioneiros sérios, mas desprezo aqueles que tratam a fronteira como um jogo ou um sonho fantasioso. Quem não tem compromisso deve deixar esta terra, sem mais perguntas.</t>
+      <c r="L90" s="32" t="inlineStr">
+        <is>
+          <t>Eu não repreendo pioneiros sérios, mas desprezo profundamente quem trata a fronteira como brincadeira ou sonho fantasioso. Quem não tem comprometimento deixa esta terra, sem perguntas.</t>
         </is>
       </c>
     </row>
@@ -1837,11 +1826,10 @@
 Craft a 'Hoe' and a 'Shovel' on your own. Once you've managed to put together these two farming tools, come back and talk to me.</t>
         </is>
       </c>
-      <c r="L91" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eu estava prestes a te ensinar o essencial da agricultura, mas com essa vestimenta quase inexistente, você mal parece apto para o trabalho no campo. Sua atitude me deixou em dúvida, então, primeiro, preciso testar seu potencial como pioneiro.  _x000D_
-_x000D_
-Fabrique uma 'Enxada' e uma 'Pá' por conta própria. Assim que conseguir montar essas duas ferramentas agrícolas, volte e fale comigo.  </t>
+      <c r="L91" s="32" t="inlineStr">
+        <is>
+          <t>Então, eu ia te ensinar a essência da lavoura, mas com esse traje quase nu você não serve para o trabalho. Sua atitude levantou dúvidas em mim, então primeiro preciso testar seu potencial como pioneiro.
+Fabrique uma 'Enxada' e uma 'Pá' por conta própria. Quando montar essas duas ferramentas, volte e fale comigo.</t>
         </is>
       </c>
     </row>
@@ -1894,11 +1882,10 @@
 You can remove grasses with the shovel, then till the soil with the hoe to make a farming field which is essential for crop cultivation. I will give you these seeds for the reward. Try making a field and sowing them.</t>
         </is>
       </c>
-      <c r="L97" t="inlineStr">
-        <is>
-          <t>Hmm, muito bem. Essa enxada e essa pá são ótimas. Elas combinam bem com você._x000D_
-_x000D_
-Você pode remover a grama com a pá e depois arar o solo com a enxada para criar um campo de cultivo, essencial para o plantio. Vou lhe dar essas sementes como recompensa. Tente preparar um campo e plantá-las.</t>
+      <c r="L97" s="32" t="inlineStr">
+        <is>
+          <t>Hum, bem feito. Essas são uma bela 'Enxada' e uma bela 'Pá'. Ficam bem em você.
+Dá para limpar o mato com a pá, depois lavrar a terra com a enxada para fazer um campo de plantio, essencial para cultivar. Vou te dar estas sementes de recompensa. Tente fazer um campo e semeá-las.</t>
         </is>
       </c>
     </row>
@@ -1920,13 +1907,11 @@
 You can check the current fertility level on the home board. When fertility is low, a quick solution is to clear the weeds and cut down trees around the area. Remember this well.</t>
         </is>
       </c>
-      <c r="L98" t="inlineStr">
-        <is>
-          <t>Deixe-me ensinar algo importante antes de você ir._x000D_
-_x000D_
-Toda plantação e planta nesta terra consome 'fertilidade'. Se a fertilidade cair muito, o solo ficará estéril e a produtividade das suas colheitas diminuirá._x000D_
-_x000D_
-Você pode verificar o nível atual de fertilidade no quadro da casa. Quando a fertilidade estiver baixa, uma solução rápida é limpar as ervas daninhas e cortar as árvores ao redor. Lembre-se bem disso.</t>
+      <c r="L98" s="32" t="inlineStr">
+        <is>
+          <t>Deixe-me ensinar algo importante antes de ir.
+Toda plantação desta terra consome 'fertilidade'. Se a fertilidade cair demais, o solo fica estéril, e a colheita diminui.
+Você confere a fertilidade atual no quadro do lar. Quando estiver baixa, uma solução rápida é limpar o mato e cortar as árvores ao redor. Grave bem isso.</t>
         </is>
       </c>
     </row>
@@ -1999,7 +1984,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L106" t="inlineStr">
+      <c r="L106" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2024,7 +2009,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L107" t="inlineStr">
+      <c r="L107" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2046,11 +2031,10 @@
 It's not good to hold in stress. Why don't you learn from me, and enjoy the tranquil and magnificent nature of this meadow?</t>
         </is>
       </c>
-      <c r="L108" t="inlineStr">
-        <is>
-          <t>Qual é o motivo dessas caras tão sérias, vocês dois?_x000D_
-_x000D_
-Não é bom guardar estresse. Por que não aprendem comigo e aproveitam a tranquilidade e a grandiosidade da natureza deste prado?</t>
+      <c r="L108" s="32" t="inlineStr">
+        <is>
+          <t>Que caras sérias são essas, vocês dois?
+Não é bom guardar estresse. Que tal aprender comigo e aproveitar a natureza tranquila e magnífica desta campina?</t>
         </is>
       </c>
     </row>
@@ -2073,9 +2057,9 @@
           <t>Ah, Loytel, good timing. Actually, I've just received this letter from Mysilia.</t>
         </is>
       </c>
-      <c r="L109" t="inlineStr">
-        <is>
-          <t>Ah, Loytel, que bom que você veio. Na verdade, acabei de receber esta carta de Mysilia.</t>
+      <c r="L109" s="32" t="inlineStr">
+        <is>
+          <t>Ah, Loytel, boa hora. É que acabei de receber esta carta de Mysilia.</t>
         </is>
       </c>
     </row>
@@ -2093,9 +2077,9 @@
           <t>...A letter huh? Let's have a look.</t>
         </is>
       </c>
-      <c r="L110" t="inlineStr">
-        <is>
-          <t>...Uma carta, hein? Deixe-me ver.</t>
+      <c r="L110" s="32" t="inlineStr">
+        <is>
+          <t>...Uma carta? Deixa ver.</t>
         </is>
       </c>
     </row>
@@ -2131,16 +2115,13 @@
 Mysilian Finance Bureau</t>
         </is>
       </c>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>Caro Loytel,_x000D_
-_x000D_
-Lamentavelmente, as raras flores que você colecionou com tanta paixão, especialmente a 'Tulipa Fantasma Azul', foram avaliadas como falsas. Os fundos que você investiu são irrecuperáveis, e foi descoberto que essa flor é proibida para cultivo em Mysilia. Como ela foi exibida no Dia da Memória Real pela família real, você está sendo acusado de causar um grave dano à honra real, resultando em uma dívida de vinte milhões de Orens._x000D_
-_x000D_
-É uma situação desafiadora, senhor, mas esperamos que você supere essa adversidade e recupere sua glória._x000D_
-_x000D_
-Atenciosamente,_x000D_
-Departamento Financeiro de Mysilia</t>
+      <c r="L112" s="32" t="inlineStr">
+        <is>
+          <t>Prezado Loytel,
+Lamentavelmente, suas raras flores colecionadas com paixão, em especial a 'Tulipa Azul Fantasma', foram avaliadas como falsas. Os fundos investidos são irrecuperáveis, e descobriu-se que esta flor tem cultivo proibido em Mysilia. Como foi exibida no Dia Memorial Real pela família real, você responderá por grave dano à honra real, resultando em uma dívida de vinte milhões de orens.
+É uma situação árdua, Senhor, mas esperamos que supere esta adversidade e retome sua glória.
+Atenciosamente,
+Bureau de Finanças de Mysilia</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2139,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L113" t="inlineStr">
+      <c r="L113" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2178,9 +2159,9 @@
           <t>So, this means I'm bankrupt and saddled with a colossal debt of twenty million Orens?</t>
         </is>
       </c>
-      <c r="L114" t="inlineStr">
-        <is>
-          <t>Então, isso significa que estou falido e sobrecarregado com uma dívida colossal de vinte milhões de Orens?</t>
+      <c r="L114" s="32" t="inlineStr">
+        <is>
+          <t>Então quer dizer que estou falido e carregando uma dívida colossal de vinte milhões de orens?</t>
         </is>
       </c>
     </row>
@@ -2203,7 +2184,7 @@
           <t>...Yes, it seems so.</t>
         </is>
       </c>
-      <c r="L115" t="inlineStr">
+      <c r="L115" s="32" t="inlineStr">
         <is>
           <t>...Sim, parece que sim.</t>
         </is>
@@ -2228,9 +2209,9 @@
           <t>I’d like to see this fake tulip once we're back in Mysilia.</t>
         </is>
       </c>
-      <c r="L116" t="inlineStr">
-        <is>
-          <t>Gostaria de ver essa tulipa falsa assim que voltarmos para Mysilia.</t>
+      <c r="L116" s="32" t="inlineStr">
+        <is>
+          <t>Quero ver essa tulipa falsa quando voltarmos a Mysilia.</t>
         </is>
       </c>
     </row>
@@ -2248,9 +2229,9 @@
           <t>(Takes a deep breath)</t>
         </is>
       </c>
-      <c r="L117" t="inlineStr">
-        <is>
-          <t>(Toma um profundo fôlego)</t>
+      <c r="L117" s="32" t="inlineStr">
+        <is>
+          <t>(Respira fundo)</t>
         </is>
       </c>
     </row>
@@ -2270,11 +2251,10 @@
 It's fortunate that I was here in this meadow when such an absurd tragedy struck. Had I been in Mysilia, I would have been imprisoned for a crime I didn't commit.</t>
         </is>
       </c>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>...Essa é a situação. Entendeu, #pc?_x000D_
-_x000D_
-Por sorte, eu estava aqui neste prado quando essa tragédia absurda aconteceu. Se estivesse em Mysilia, teria sido preso por um crime que não cometi.</t>
+      <c r="L118" s="32" t="inlineStr">
+        <is>
+          <t>...É essa a situação. Entendeu, #pc?
+É uma sorte que eu estivesse nesta campina quando uma tragédia tão absurda ocorreu. Se eu estivesse em Mysilia, estaria preso por um crime que não cometi.</t>
         </is>
       </c>
     </row>
@@ -2292,9 +2272,9 @@
           <t>...Alright, let's turn this land into a bustling city of gold and pay off the debt no matter what. Do not worry. With my wisdom and experience, I am certain to overcome this hardship.</t>
         </is>
       </c>
-      <c r="L119" t="inlineStr">
-        <is>
-          <t>...Muito bem, vamos transformar esta terra em uma próspera cidade de ouro e quitar essa dívida, custe o que custar. Não se preocupem. Com minha sabedoria e experiência, tenho certeza de que superarei essa dificuldade.</t>
+      <c r="L119" s="32" t="inlineStr">
+        <is>
+          <t>...Muito bem, vamos transformar esta terra numa cidade dourada e movimentada e pagar a dívida custe o que custar. Não se preocupe. Com minha sabedoria e experiência, certamente superarei esta provação.</t>
         </is>
       </c>
     </row>
@@ -2317,9 +2297,9 @@
           <t>A phantom azure tulip. Didn't you find such a flower suspicious?</t>
         </is>
       </c>
-      <c r="L120" t="inlineStr">
-        <is>
-          <t>Uma Tulipa Fantasma Azul. Você não achou essa flor suspeita?</t>
+      <c r="L120" s="32" t="inlineStr">
+        <is>
+          <t>Uma tulipa azul fantasma. Você não achou suspeita uma flor dessas?</t>
         </is>
       </c>
     </row>
@@ -2337,7 +2317,7 @@
           <t>...my head hurts, I need to rest now.</t>
         </is>
       </c>
-      <c r="L121" t="inlineStr">
+      <c r="L121" s="32" t="inlineStr">
         <is>
           <t>...minha cabeça dói, preciso descansar agora.</t>
         </is>
@@ -2362,7 +2342,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L122" t="inlineStr">
+      <c r="L122" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2387,9 +2367,9 @@
           <t>Twenty million Orens... That's enough to buy a small town easily.</t>
         </is>
       </c>
-      <c r="L123" t="inlineStr">
-        <is>
-          <t>Vinte milhões de Orens... Isso dá para comprar facilmente uma cidade pequena.</t>
+      <c r="L123" s="32" t="inlineStr">
+        <is>
+          <t>Vinte milhões de orens... Daria para comprar uma cidadezinha fácil, fácil.</t>
         </is>
       </c>
     </row>
@@ -2412,9 +2392,9 @@
           <t>Knowing Loytel, he'll find some way to handle it... probably.</t>
         </is>
       </c>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>Conhecendo Loytel, ele vai dar um jeito nisso... provavelmente.</t>
+      <c r="L124" s="32" t="inlineStr">
+        <is>
+          <t>Conhecendo o Loytel, ele acha um jeito de resolver... provavelmente.</t>
         </is>
       </c>
     </row>
@@ -2495,9 +2475,9 @@
           <t>Lord Loytel, you have been gazing at the sky for so long.</t>
         </is>
       </c>
-      <c r="L134" t="inlineStr">
-        <is>
-          <t>Lord Loytel, você está olhando para o céu há tanto tempo.</t>
+      <c r="L134" s="32" t="inlineStr">
+        <is>
+          <t>Lorde Loytel, o senhor fica contemplando o céu há tanto tempo.</t>
         </is>
       </c>
     </row>
@@ -2517,11 +2497,10 @@
 Life in this vast plain isn't bad, but I wonder if the day will come again when I can drink the exquisite wine of Olvina.</t>
         </is>
       </c>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>Ah, Lady Farris. Não é nada... Só estava relembrando os dias na corte de Mysilia._x000D_
-_x000D_
-A vida nesta vasta planície não é ruim, mas me pergunto se um dia poderei voltar a degustar o requintado vinho de Olvina.</t>
+      <c r="L135" s="32" t="inlineStr">
+        <is>
+          <t>Ah, Lady Farris. Não é nada... só estava recordando os dias na corte de Mysilia.
+A vida nesta planície imensa não é ruim, mas será que voltará o dia em que poderei beber o vinho requintado de Olvina?</t>
         </is>
       </c>
     </row>
@@ -2544,9 +2523,9 @@
           <t>...You're worried about the debt, aren't you?</t>
         </is>
       </c>
-      <c r="L136" t="inlineStr">
-        <is>
-          <t>...Você está preocupado com a dívida, não está?</t>
+      <c r="L136" s="32" t="inlineStr">
+        <is>
+          <t>...Está preocupado com a dívida, não está?</t>
         </is>
       </c>
     </row>
@@ -2564,9 +2543,9 @@
           <t>...I'd be lying if I said it doesn't bother me. But, I am, after all, a Mysilian frontier inspector by name. I should forget the unfortunate incident and dedicate myself to developing this land.</t>
         </is>
       </c>
-      <c r="L137" t="inlineStr">
-        <is>
-          <t>...Eu mentiria se dissesse que isso não me incomoda. Mas, afinal, sou um inspetor de fronteira de Mysilia de nome. Devo esquecer esse infeliz incidente e me dedicar ao desenvolvimento desta terra.</t>
+      <c r="L137" s="32" t="inlineStr">
+        <is>
+          <t>...Mentiria se dissesse que não me abala. Mas, afinal de contas, sou um inspetor de fronteira de Mysilia pelo nome. Devo esquecer o incidente infeliz e me dedicar a desenvolver esta terra.</t>
         </is>
       </c>
     </row>
@@ -2589,9 +2568,9 @@
           <t>That's reassuring to hear, Lord Loytel. But I wonder, is failure always a darkness to be avoided? Is misfortune always a shadow to be shunned?</t>
         </is>
       </c>
-      <c r="L138" t="inlineStr">
-        <is>
-          <t>É bom ouvir isso, Lord Loytel. Mas eu me pergunto: será que o fracasso é sempre uma escuridão a ser evitada? Será que a desgraça é sempre uma sombra a ser temida?</t>
+      <c r="L138" s="32" t="inlineStr">
+        <is>
+          <t>É reconfortante ouvir isso, Lorde Loytel. Mas me pergunto: será que o fracasso é sempre uma escuridão a evitar? Será que a desgraça é sempre uma sombra a temer?</t>
         </is>
       </c>
     </row>
@@ -2609,7 +2588,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L139" t="inlineStr">
+      <c r="L139" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -2634,9 +2613,9 @@
           <t>I may not know much about frontier works, but sometimes, the most beautiful things are the arts born from mistakes. Lord Loytel, I believe that you can turn this difficulty into strength and reclaim your glory.</t>
         </is>
       </c>
-      <c r="L140" t="inlineStr">
-        <is>
-          <t>Talvez eu não saiba muito sobre trabalho nas fronteiras, mas às vezes, as coisas mais belas são as artes nascidas dos erros. Lord Loytel, acredito que você pode transformar essa dificuldade em força e recuperar sua glória.</t>
+      <c r="L140" s="32" t="inlineStr">
+        <is>
+          <t>Não conheço muito dos trabalhos de fronteira, mas às vezes as coisas mais belas são as artes que nascem dos erros. Lorde Loytel, acredito que o senhor pode transformar esta dificuldade em força e retomar sua glória.</t>
         </is>
       </c>
     </row>
@@ -2654,9 +2633,9 @@
           <t>What an insight... Lady Farris, your words have moved me.</t>
         </is>
       </c>
-      <c r="L141" t="inlineStr">
-        <is>
-          <t>Que visão... Lady Farris, suas palavras me tocaram.</t>
+      <c r="L141" s="32" t="inlineStr">
+        <is>
+          <t>Que percepção... Lady Farris, suas palavras me tocaram.</t>
         </is>
       </c>
     </row>
@@ -2676,11 +2655,10 @@
 Unlike Ash and Fiama, you seem to be a wise person. Lady Farris, I hope you will continue to support me.</t>
         </is>
       </c>
-      <c r="L142" t="inlineStr">
-        <is>
-          <t>Sim, a colonização é como a arte. Não se trata de esquecer os eventos infelizes, mas de usá-los como alimento para forjar o futuro. Aprendi isso com suas palavras._x000D_
-_x000D_
-Ao contrário de Ash e Fiama, você parece ser uma pessoa sábia. Lady Farris, espero que continue me apoiando.</t>
+      <c r="L142" s="32" t="inlineStr">
+        <is>
+          <t>Sim, pioneirismo é como a arte. Não se trata de esquecer os eventos infelizes, mas de usar essas experiências como alimento para forjar o futuro. Aprendi com suas palavras.
+Diferente de Ash e Fiama, você parece ser uma pessoa sábia. Lady Farris, espero que continue me apoiando.</t>
         </is>
       </c>
     </row>
@@ -2703,9 +2681,9 @@
           <t>Yes, gladly. In fact, I have been working on a new song to encourage you, titled 'Dance of Dreams in the Azure Illusion'.</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>Sim, com prazer. Na verdade, estou compondo uma nova canção para encorajá-lo, intitulada 'Dança dos Sonhos na Ilusão Azul'.</t>
+      <c r="L143" s="32" t="inlineStr">
+        <is>
+          <t>Sim, com prazer. Aliás, estou compondo uma canção nova para animá-lo, com o título 'Dança dos Sonhos na Ilusão Azul'.</t>
         </is>
       </c>
     </row>
@@ -2723,9 +2701,9 @@
           <t>(Takes a deep breath)</t>
         </is>
       </c>
-      <c r="L144" t="inlineStr">
-        <is>
-          <t>(Toma um profundo fôlego)</t>
+      <c r="L144" s="32" t="inlineStr">
+        <is>
+          <t>(Respira fundo)</t>
         </is>
       </c>
     </row>
@@ -2748,9 +2726,9 @@
           <t>It was unfortunate that the azure tulips turned out to be fake, but the inspiration your tragedy has given us is real. That's why I want to turn the story of the azure tulips into a song, to tell the settlers who are yet to come. Those who hear the song shall envision the ephemeral beauty of the azure tulips they can no longer see, and be moved by the dedication you have for frontier works.</t>
         </is>
       </c>
-      <c r="L145" t="inlineStr">
-        <is>
-          <t>Foi uma pena que as tulipas azuis tenham sido falsas, mas a inspiração que sua tragédia nos trouxe é real. Por isso, quero transformar a história das tulipas azuis em uma canção, para contar aos colonos que ainda virão. Aqueles que ouvirem a música imaginarão a efêmera beleza das tulipas azuis que não podem mais ver e se comoverão com a dedicação que você tem pelo trabalho na fronteira.</t>
+      <c r="L145" s="32" t="inlineStr">
+        <is>
+          <t>Foi uma pena que as tulipas azuis fossem falsas, mas a inspiração que a tragédia nos deu é real. Por isso quero transformar a história das tulipas azuis em canção, para contar aos colonos que ainda virão. Quem ouvir a canção há de imaginar a beleza efêmera das tulipas azuis que já não pode ver, e se comover com a dedicação do senhor aos trabalhos da fronteira.</t>
         </is>
       </c>
     </row>
@@ -2768,9 +2746,9 @@
           <t>Lady Farris... I mean, that's...</t>
         </is>
       </c>
-      <c r="L146" t="inlineStr">
-        <is>
-          <t>Lady Farris... quero dizer, isso é...</t>
+      <c r="L146" s="32" t="inlineStr">
+        <is>
+          <t>Lady Farris... digo, isso é...</t>
         </is>
       </c>
     </row>
@@ -2793,9 +2771,9 @@
           <t>What's the matter?</t>
         </is>
       </c>
-      <c r="L147" t="inlineStr">
-        <is>
-          <t>O que foi?</t>
+      <c r="L147" s="32" t="inlineStr">
+        <is>
+          <t>Que foi?</t>
         </is>
       </c>
     </row>
@@ -2813,9 +2791,9 @@
           <t>It's just... I've got a bit of a headache... I'm sure it must be a wonderful song, but give me some time to think...</t>
         </is>
       </c>
-      <c r="L148" t="inlineStr">
-        <is>
-          <t>É que... estou com uma leve dor de cabeça... Tenho certeza de que deve ser uma música maravilhosa, mas me dê um tempo para pensar..."</t>
+      <c r="L148" s="32" t="inlineStr">
+        <is>
+          <t>É que... tenho uma pequena dor de cabeça... Tenho certeza de que será uma canção linda, mas me dê um tempo para pensar...</t>
         </is>
       </c>
     </row>
@@ -2907,9 +2885,9 @@
           <t>Lord Loytel, #pc, just the right timing. Those two travelers over there wish to talk to you.</t>
         </is>
       </c>
-      <c r="L158" t="inlineStr">
-        <is>
-          <t>Lord Loytel, #pc, que bom que chegaram. Aqueles dois viajantes ali gostariam de falar com vocês.</t>
+      <c r="L158" s="32" t="inlineStr">
+        <is>
+          <t>Lorde Loytel, #pc, timing perfeito. Aqueles dois viajantes ali desejam falar com o senhor.</t>
         </is>
       </c>
     </row>
@@ -2927,9 +2905,9 @@
           <t>Hmm, travelers, you say? They seem harmless enough, though their attire is a bit odd.</t>
         </is>
       </c>
-      <c r="L159" t="inlineStr">
-        <is>
-          <t>Hmm, viajantes, é isso? Parecem inofensivos, embora suas roupas sejam um tanto peculiares.</t>
+      <c r="L159" s="32" t="inlineStr">
+        <is>
+          <t>Hum, viajantes, diz você? Parecem inofensivos, embora o traje seja um tanto esquisito.</t>
         </is>
       </c>
     </row>
@@ -2952,9 +2930,9 @@
           <t>They told me they're wandering alchemists. Apparently, they travel around various places.</t>
         </is>
       </c>
-      <c r="L160" t="inlineStr">
-        <is>
-          <t>Eles me disseram que são alquimistas errantes. Pelo visto, viajam por diversos lugares.</t>
+      <c r="L160" s="32" t="inlineStr">
+        <is>
+          <t>Disseram que são alquimistas andarilhos. Aparentemente viajam por vários lugares.</t>
         </is>
       </c>
     </row>
@@ -2974,11 +2952,10 @@
 Wait, hold on... The lead plate that man is wearing around his neck looks familiar.</t>
         </is>
       </c>
-      <c r="L161" t="inlineStr">
-        <is>
-          <t>Alquimistas, é? Ostentando um título tão duvidoso, provavelmente estão tentando vender algumas poções questionáveis. Alquimia, de todas as coisas, é..._x000D_
-_x000D_
-Espere, um momento... A placa de chumbo que aquele homem está usando no pescoço me parece familiar.</t>
+      <c r="L161" s="32" t="inlineStr">
+        <is>
+          <t>Alquimistas, é? Ostentando um título tão duvidoso, devem estar querendo vender poções questionáveis. Alquimia, santo do céu, é que...
+Peraí... A chapa de chumbo que aquele homem traz no pescoço parece familiar.</t>
         </is>
       </c>
     </row>
@@ -2998,11 +2975,10 @@
 ...Hard to believe, but it seems this frivolous-looking man is an elite among elites.</t>
         </is>
       </c>
-      <c r="L162" t="inlineStr">
-        <is>
-          <t>O brilho opaco da placa de chumbo verde, gravada com o símbolo do sol... Não há engano, isso é uma marca de distinção da renomada Academia de Palmia, concedida apenas àqueles que alcançaram um sucesso acadêmico excepcional. Quem usa essa placa é recebido como um convidado de honra em qualquer corte de Tyris._x000D_
-_x000D_
-...Difícil de acreditar, mas parece que esse homem de aparência despreocupada é uma elite entre as elites.</t>
+      <c r="L162" s="32" t="inlineStr">
+        <is>
+          <t>O brilho fosco da chapa verde de chumbo, gravada com o símbolo do sol... Não há erro, é um emblema de distinção da estimada Academia de Palmia, dado só a quem alcança êxito acadêmico notável. Usando aquela chapa, um seria recebido como hóspede de honra em qualquer corte de Tyris.
+...Difícil de acreditar, mas esse homem de aparência frívola parece ser a elite da elite.</t>
         </is>
       </c>
     </row>
@@ -3022,11 +2998,10 @@
 This traveler must be a renowned alchemist, indeed. Be sure to keep your manners!</t>
         </is>
       </c>
-      <c r="L163" t="inlineStr">
-        <is>
-          <t>Ahem... Você entendeu, #pc?_x000D_
-_x000D_
-Este viajante deve ser um alquimista renomado, sem dúvida. Certifique-se de manter a etiqueta!</t>
+      <c r="L163" s="32" t="inlineStr">
+        <is>
+          <t>Hem-hem... Entende, #pc?
+Esse viajante deve ser um alquimista renomado, de fato. Cuide das suas maneiras!</t>
         </is>
       </c>
     </row>
@@ -3049,7 +3024,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L164" t="inlineStr">
+      <c r="L164" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -3071,11 +3046,10 @@
 Though this is but a vast empty plain, might there be something we can do for you?</t>
         </is>
       </c>
-      <c r="L165" t="inlineStr">
-        <is>
-          <t>Bem-vindos, viajantes!_x000D_
-_x000D_
-Embora esta seja apenas uma vasta planície desabitada, há algo que possamos fazer por vocês?</t>
+      <c r="L165" s="32" t="inlineStr">
+        <is>
+          <t>Bem-vindos, viajantes!
+Apesar de ser uma planície vazia e imensa, haveria algo em que possamos ajudá-los?</t>
         </is>
       </c>
     </row>
@@ -3100,11 +3074,10 @@
 We're grateful for the warm welcome. I am called Kettle, and this is my companion, Quruitzia.</t>
         </is>
       </c>
-      <c r="L166" t="inlineStr">
-        <is>
-          <t>Bom dia, colonos desta terra. Chamar isto de uma planície vazia não faz justiça à verdade. Aqui, há a brisa da liberdade, e há esperança._x000D_
-_x000D_
-Somos gratos pela calorosa recepção. Meu nome é Kettle, e esta é minha companheira, Quruitzia.</t>
+      <c r="L166" s="32" t="inlineStr">
+        <is>
+          <t>Bom dia, colonos desta terra. Chamar isto de planície vazia desmente a verdade. Aqui há a brisa da liberdade, e há esperança.
+Agradecemos o acolhimento caloroso. Chamo-me Kettle, e esta é minha companheira, Quruitzia.</t>
         </is>
       </c>
     </row>
@@ -3127,7 +3100,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L167" t="inlineStr">
+      <c r="L167" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -3152,9 +3125,9 @@
           <t>We heard about your settlement during our travels and hoped to find shelter and bread for the night. I hope we're not imposing?</t>
         </is>
       </c>
-      <c r="L168" t="inlineStr">
-        <is>
-          <t>Ouvimos falar sobre seu assentamento durante nossas viagens e esperávamos encontrar abrigo e pão para passar a noite. Espero que não estejamos incomodando.</t>
+      <c r="L168" s="32" t="inlineStr">
+        <is>
+          <t>Ouvimos do seu assentamento durante nossas viagens e esperávamos encontrar abrigo e pão para a noite. Espero não estar impondo?</t>
         </is>
       </c>
     </row>
@@ -3172,9 +3145,9 @@
           <t>Not at all, Master Kettle. I am Loytel, the frontier inspector of this land. You're welcome to rest your wings here as long as you like.</t>
         </is>
       </c>
-      <c r="L169" t="inlineStr">
-        <is>
-          <t>De forma alguma, Mestre Kettle. Sou Loytel, o inspetor de fronteira desta terra. Sintam-se à vontade para descansar aqui pelo tempo que quiserem.</t>
+      <c r="L169" s="32" t="inlineStr">
+        <is>
+          <t>Nem um pouco, Mestre Kettle. Sou Loytel, o inspetor de fronteira desta terra. Pousem as asas aqui quanto tempo quiserem.</t>
         </is>
       </c>
     </row>
@@ -3197,9 +3170,9 @@
           <t>That's very kind of you. There's a strange harmony here, and I can feel the breath of mana. In our travels, such places are rare. I was hoping to explore the area a bit.</t>
         </is>
       </c>
-      <c r="L170" t="inlineStr">
-        <is>
-          <t>Isso é muito gentil da sua parte. Há uma harmonia estranha aqui, e consigo sentir o sopro do mana. Em nossas viagens, lugares assim são raros. Eu gostaria de explorar um pouco a região.</t>
+      <c r="L170" s="32" t="inlineStr">
+        <is>
+          <t>Muito gentil da sua parte. Há uma harmonia estranha aqui, e consigo sentir o sopro da mana. Em nossas viagens, lugares assim são raros. Eu gostaria de explorar a área um pouco.</t>
         </is>
       </c>
     </row>
@@ -3217,9 +3190,9 @@
           <t>Interesting. Ash mentioned something similar before. His hunches are hit or miss, but if you say so, there might indeed be something special about this land.</t>
         </is>
       </c>
-      <c r="L171" t="inlineStr">
-        <is>
-          <t>Interessante. Ash mencionou algo semelhante antes. Seus palpites são incertos, mas se você diz isso, talvez haja mesmo algo especial nesta terra.</t>
+      <c r="L171" s="32" t="inlineStr">
+        <is>
+          <t>Interessante. O Ash mencionou algo parecido antes. Os palpites dele são coerentes ou não, mas se você diz, talvez esta terra tenha mesmo algo especial.</t>
         </is>
       </c>
     </row>
@@ -3239,11 +3212,10 @@
 Let me welcome you again, Master Kettle. I hope your stay here proves to be meaningful for you as well.</t>
         </is>
       </c>
-      <c r="L172" t="inlineStr">
-        <is>
-          <t>De qualquer forma, ter um alquimista do seu calibre por perto certamente é reconfortante._x000D_
-_x000D_
-Deixe-me recebê-lo novamente, Mestre Kettle. Espero que sua estadia aqui também seja significativa para você.</t>
+      <c r="L172" s="32" t="inlineStr">
+        <is>
+          <t>Enfim, ter um alquimista do seu calibre por perto é tranquilizador.
+Deixe-me recebê-lo mais uma vez, Mestre Kettle. Espero que a estadia aqui também signifique algo para você.</t>
         </is>
       </c>
     </row>
@@ -3326,9 +3298,9 @@
           <t>Ah, preparing food already? Admirable dedication so early in the morning, Quru...Quru..</t>
         </is>
       </c>
-      <c r="L182" t="inlineStr">
-        <is>
-          <t>Ah, já preparando a comida? Admirável dedicação tão cedo pela manhã, Quru...Quru...</t>
+      <c r="L182" s="32" t="inlineStr">
+        <is>
+          <t>Ah, preparando comida já? Dedicação admirável tão cedo, Quru...Quru...</t>
         </is>
       </c>
     </row>
@@ -3351,7 +3323,7 @@
           <t>Quruitzia.</t>
         </is>
       </c>
-      <c r="L183" t="inlineStr">
+      <c r="L183" s="32" t="inlineStr">
         <is>
           <t>Quruitzia.</t>
         </is>
@@ -3371,9 +3343,9 @@
           <t xml:space="preserve">Right, Quruitzia. I've been meaning to ask, why does Master Kettle always have his eyes closed? </t>
         </is>
       </c>
-      <c r="L184" t="inlineStr">
-        <is>
-          <t>Isso, Quruitzia. Eu queria perguntar, por que o Mestre Kettle está sempre de olhos fechados?</t>
+      <c r="L184" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Isso, Quruitzia. Queria perguntar: por que o Mestre Kettle fica sempre de olhos fechados? </t>
         </is>
       </c>
     </row>
@@ -3396,7 +3368,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L185" t="inlineStr">
+      <c r="L185" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3416,7 +3388,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L186" t="inlineStr">
+      <c r="L186" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3441,7 +3413,7 @@
           <t>He is blind.</t>
         </is>
       </c>
-      <c r="L187" t="inlineStr">
+      <c r="L187" s="32" t="inlineStr">
         <is>
           <t>Ele é cego.</t>
         </is>
@@ -3461,9 +3433,9 @@
           <t>I... see. My apologies, that was an insensitive question to ask... But, doesn’t his blindness make alchemy difficult? Let alone traveling normally must be a challenge indeed?</t>
         </is>
       </c>
-      <c r="L188" t="inlineStr">
-        <is>
-          <t>Eu... entendo. Minhas desculpas, foi uma pergunta insensível... Mas, isso não torna a alquimia difícil para ele? Sem falar que viajar normalmente já deve ser um grande desafio.</t>
+      <c r="L188" s="32" t="inlineStr">
+        <is>
+          <t>En... tendi. Desculpa, foi pergunta insensível... Mas a cegueira não atrapalha a alquimia? Sem falar que até viajar assim deve ser um desafio e tanto?</t>
         </is>
       </c>
     </row>
@@ -3486,7 +3458,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L189" t="inlineStr">
+      <c r="L189" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3506,7 +3478,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L190" t="inlineStr">
+      <c r="L190" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3531,9 +3503,9 @@
           <t>I am with him.</t>
         </is>
       </c>
-      <c r="L191" t="inlineStr">
-        <is>
-          <t>Eu estou com ele.</t>
+      <c r="L191" s="32" t="inlineStr">
+        <is>
+          <t>Estou com ele.</t>
         </is>
       </c>
     </row>
@@ -3551,9 +3523,9 @@
           <t>R-Right, of course! With a reliable companion like you by his side, he must feel much more at ease. It’s like you’re tied together with invisible threads of trust.</t>
         </is>
       </c>
-      <c r="L192" t="inlineStr">
-        <is>
-          <t>C-Certo, é claro! Com uma companheira confiável como você ao lado dele, ele deve se sentir muito mais seguro. É como se estivessem ligados por fios invisíveis de confiança.</t>
+      <c r="L192" s="32" t="inlineStr">
+        <is>
+          <t>C-Certo, claro! Com uma companheira confiável assim ao lado, ele deve se sentir bem mais tranquilo. É como se vocês fossem atados por fios invisíveis de confiança.</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3548,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L193" t="inlineStr">
+      <c r="L193" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3596,7 +3568,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L194" t="inlineStr">
+      <c r="L194" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3618,11 +3590,10 @@
 By the way, what is this delicious-looking dish? I've been curious since I smelled it.</t>
         </is>
       </c>
-      <c r="L195" t="inlineStr">
-        <is>
-          <t>Hoje está... particularmente frio, não acha? _x000D_
-_x000D_
-A propósito, que prato delicioso é esse? Fiquei curioso desde que senti o cheiro.</t>
+      <c r="L195" s="32" t="inlineStr">
+        <is>
+          <t>Hoje está... particularmente frio, não está?
+Aliás, o que é esse prato de aparência deliciosa? Fiquei curioso desde que senti o cheiro.</t>
         </is>
       </c>
     </row>
@@ -3645,9 +3616,9 @@
           <t>This is an Api nut stew... please, have some if you’d like.</t>
         </is>
       </c>
-      <c r="L196" t="inlineStr">
-        <is>
-          <t>É um ensopado de noz Api... por favor, sirva-se, se quiser.</t>
+      <c r="L196" s="32" t="inlineStr">
+        <is>
+          <t>É um ensopado de castanha de api... sirva-se se quiser.</t>
         </is>
       </c>
     </row>
@@ -3665,9 +3636,9 @@
           <t>Oh, Api nut is my favorite! And a freshly made, piping hot stew, no less! Let me have a taste.</t>
         </is>
       </c>
-      <c r="L197" t="inlineStr">
-        <is>
-          <t>Oh, noz Api é minha favorita! E um ensopado recém-preparado, bem quente! Deixe-me provar.</t>
+      <c r="L197" s="32" t="inlineStr">
+        <is>
+          <t>Oh, a castanha de api é minha favorita! E um ensopado recém-feito, pipocando de quente, ainda por cima! Deixa eu provar.</t>
         </is>
       </c>
     </row>
@@ -3685,7 +3656,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L198" t="inlineStr">
+      <c r="L198" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3705,9 +3676,9 @@
           <t>... Ack, ughhh!</t>
         </is>
       </c>
-      <c r="L199" t="inlineStr">
-        <is>
-          <t>... Ack, ughhh!</t>
+      <c r="L199" s="32" t="inlineStr">
+        <is>
+          <t>... Ack, blerghhh!</t>
         </is>
       </c>
     </row>
@@ -3730,7 +3701,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L200" t="inlineStr">
+      <c r="L200" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3750,9 +3721,9 @@
           <t>This is... a truly unique stew. I mean, it’s... an innovative approach that took me by surprise. The flavor of the Api fruit is like... like I’ve never experienced before... it’s..</t>
         </is>
       </c>
-      <c r="L201" t="inlineStr">
-        <is>
-          <t>Este é... um ensopado realmente único. Quero dizer, é... uma abordagem inovadora que me pegou de surpresa. O sabor da fruta Api é como... como se eu nunca tivesse experimentado algo assim antes... é...</t>
+      <c r="L201" s="32" t="inlineStr">
+        <is>
+          <t>Isto é... um ensopado verdadeiramente singular. Digo, é... uma abordagem inovadora que me pegou de surpresa. O sabor da fruta de api é como... como nada que eu já experimentei... é...</t>
         </is>
       </c>
     </row>
@@ -3775,7 +3746,7 @@
           <t>Die!</t>
         </is>
       </c>
-      <c r="L202" t="inlineStr">
+      <c r="L202" s="32" t="inlineStr">
         <is>
           <t>Morra!</t>
         </is>
@@ -3795,9 +3766,9 @@
           <t>Wha... Oh, Quruitzia, where are you going? Wait! Quruitzia!</t>
         </is>
       </c>
-      <c r="L203" t="inlineStr">
-        <is>
-          <t>O quê... Ah, Quruitzia, para onde você está indo? Espere! Quruitzia!</t>
+      <c r="L203" s="32" t="inlineStr">
+        <is>
+          <t>Mas... Oh, Quruitzia, aonde você vai? Espera! Quruitzia!</t>
         </is>
       </c>
     </row>
@@ -3815,7 +3786,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L204" t="inlineStr">
+      <c r="L204" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -3835,9 +3806,9 @@
           <t>Phew... What a temperamental lass. This is going to be challenging...</t>
         </is>
       </c>
-      <c r="L205" t="inlineStr">
-        <is>
-          <t>Phew... Que garota temperamental. Isso vai ser complicado...</t>
+      <c r="L205" s="32" t="inlineStr">
+        <is>
+          <t>Ufa... Que moça temperamental. Isto vai ser desafiador...</t>
         </is>
       </c>
     </row>
@@ -3921,9 +3892,9 @@
           <t>Master Kettle, might I have a moment of your time?</t>
         </is>
       </c>
-      <c r="L216" t="inlineStr">
-        <is>
-          <t>Mestre Kettle, posso tomar um momento do seu tempo?</t>
+      <c r="L216" s="32" t="inlineStr">
+        <is>
+          <t>Mestre Kettle, posso pedir um momento do seu tempo?</t>
         </is>
       </c>
     </row>
@@ -3946,9 +3917,9 @@
           <t xml:space="preserve">Call me just Kettle. What do you need? </t>
         </is>
       </c>
-      <c r="L217" t="inlineStr">
-        <is>
-          <t>Me chame apenas de Kettle. O que você precisa?</t>
+      <c r="L217" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Pode me chamar só de Kettle. O que você precisa? </t>
         </is>
       </c>
     </row>
@@ -3968,11 +3939,10 @@
 Alchemy is quite useful for making potions and medicines and various other things. But at its core, it's a study focused on artificially transforming base metals into precious ones, am I right?... No, let's not beat around the bush. Can you turn things into gold?</t>
         </is>
       </c>
-      <c r="L218" t="inlineStr">
-        <is>
-          <t>Bem então, Kettle, eu queria lhe perguntar algo._x000D_
-_x000D_
-A alquimia é bastante útil para fazer poções, remédios e várias outras coisas. Mas, em sua essência, é um estudo focado em transformar metais básicos em metais preciosos artificialmente, certo?... Não, vamos direto ao ponto. Você consegue transformar coisas em ouro?</t>
+      <c r="L218" s="32" t="inlineStr">
+        <is>
+          <t>Pois então, Kettle, queria te perguntar uma coisa.
+A alquimia é bem útil para fazer poções, remédios e várias outras coisas. Mas, no fundo, é um estudo focado em transformar artificialmente metais vulgares em preciosos, correto?... Não, vamos sem rodeios. Dá para transformar coisas em ouro?</t>
         </is>
       </c>
     </row>
@@ -3997,11 +3967,10 @@
 Unfortunately, that's beyond my capabilities. To transmute mere scrap into gold, one would need the 'Sage's Stone', a magical gemstone spoken of in legends, yet unseen by any living soul.</t>
         </is>
       </c>
-      <c r="L219" t="inlineStr">
-        <is>
-          <t>Ah, ouro..._x000D_
-_x000D_
-Infelizmente, isso está além das minhas capacidades. Para transmutar simples sucata em ouro, seria necessária a 'Pedra do Sábio', uma gema mágica mencionada em lendas, mas que nunca foi vista por uma alma viva.</t>
+      <c r="L219" s="32" t="inlineStr">
+        <is>
+          <t>Ah, ouro...
+Infelizmente, isso está além das minhas capacidades. Para transmutar sucata em ouro, seria preciso a 'Pedra do Sábio', uma gema mágica citada em lendas, jamais vista por olhos vivos.</t>
         </is>
       </c>
     </row>
@@ -4019,9 +3988,9 @@
           <t>..I thought as much. There are no easy paths in this world...</t>
         </is>
       </c>
-      <c r="L220" t="inlineStr">
-        <is>
-          <t>...Eu já imaginava. Não há caminhos fáceis neste mundo...</t>
+      <c r="L220" s="32" t="inlineStr">
+        <is>
+          <t>..Suspeitei. Não há caminhos fáceis neste mundo...</t>
         </is>
       </c>
     </row>
@@ -4044,7 +4013,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L221" t="inlineStr">
+      <c r="L221" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -4069,9 +4038,9 @@
           <t>I cannnot transmute gold. But if gold is what you need, there are more direct ways to acquire it.</t>
         </is>
       </c>
-      <c r="L222" t="inlineStr">
-        <is>
-          <t>Eu não posso transmutar ouro. Mas, se é ouro que você procura, há maneiras mais diretas de obtê-lo.</t>
+      <c r="L222" s="32" t="inlineStr">
+        <is>
+          <t>Não consigo transmutar ouro. Mas se ouro é o que você precisa, há caminhos mais diretos para obtê-lo.</t>
         </is>
       </c>
     </row>
@@ -4089,7 +4058,7 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L223" t="inlineStr">
+      <c r="L223" s="32" t="inlineStr">
         <is>
           <t>…</t>
         </is>
@@ -4109,7 +4078,7 @@
           <t>Do go on...</t>
         </is>
       </c>
-      <c r="L224" t="inlineStr">
+      <c r="L224" s="32" t="inlineStr">
         <is>
           <t>Continue...</t>
         </is>
@@ -4134,9 +4103,9 @@
           <t>Far to the north, at the base of a mountain range, lies a hill known as Vernis. Beneath it, a rich vein of ore sleeps within its underground caves, once mined for coal. However, as monsters began to appear, the mines were abandoned, and now no one dares approach.</t>
         </is>
       </c>
-      <c r="L225" t="inlineStr">
-        <is>
-          <t>Ao extremo norte, na base de uma cadeia de montanhas, há uma colina conhecida como Vernis. Sob ela, um rico veio de minério repousa nas cavernas subterrâneas, que antes eram mineradas por carvão. No entanto, com o surgimento de monstros, as minas foram abandonadas, e agora ninguém ousa se aproximar.</t>
+      <c r="L225" s="32" t="inlineStr">
+        <is>
+          <t>Muito ao norte, ao pé de uma cordilheira, há uma colina chamada Vernis. Sob ela, uma veia rica de minério dorme nas cavernas subterrâneas, outrora mineradas por carvão. Porém, com o surgimento de monstros, as minas foram abandonadas, e hoje ninguém se arrisca por lá.</t>
         </is>
       </c>
     </row>
@@ -4159,9 +4128,9 @@
           <t>...The forgotten mines of Vernis still hold gold. Of course, claiming it would require a courage or recklessness worthy of its fiery glow.</t>
         </is>
       </c>
-      <c r="L226" t="inlineStr">
-        <is>
-          <t>...As minas esquecidas de Vernis ainda guardam ouro. Claro, reivindicá-lo exigiria uma coragem — ou imprudência — digna de seu brilho ardente.</t>
+      <c r="L226" s="32" t="inlineStr">
+        <is>
+          <t>...As minas esquecidas de Vernis ainda guardam ouro. Claro, reivindicá-lo exigiria coragem ou imprudência dignas de seu brilho flamejante.</t>
         </is>
       </c>
     </row>
@@ -4179,9 +4148,9 @@
           <t>What a revelation, Kettle! You've given us invaluable information.</t>
         </is>
       </c>
-      <c r="L227" t="inlineStr">
-        <is>
-          <t>Que revelação, Kettle! Você nos deu uma informação valiosa.</t>
+      <c r="L227" s="32" t="inlineStr">
+        <is>
+          <t>Que revelação, Kettle! Você nos deu uma informação valiosíssima.</t>
         </is>
       </c>
     </row>
@@ -4199,9 +4168,9 @@
           <t>The forgotten gold beneath the mine of Vernis, you heard him, #pc? It seems tending to these fields of weeds and stones is no longer our priority. We must head to Vernis and uncover its golden veins!</t>
         </is>
       </c>
-      <c r="L228" t="inlineStr">
-        <is>
-          <t>O ouro esquecido sob a mina de Vernis, você ouviu isso, #pc? Parece que cuidar desses campos de ervas daninhas e pedras já não é mais nossa prioridade. Precisamos ir a Vernis e descobrir suas veias de ouro!</t>
+      <c r="L228" s="32" t="inlineStr">
+        <is>
+          <t>O ouro esquecido sob a mina de Vernis, você ouviu, #pc? Parece que cuidar destes campos de mato e pedra já não é nossa prioridade. Temos de ir a Vernis e desenterrar suas veias de ouro!</t>
         </is>
       </c>
     </row>
@@ -4219,9 +4188,9 @@
           <t>Though I'd like to leave at once, you must have preparations of your own. Speak to me when you're ready to embark on the venture to Vernis.</t>
         </is>
       </c>
-      <c r="L229" t="inlineStr">
-        <is>
-          <t>Embora eu queira partir imediatamente, você deve fazer seus próprios preparativos. Fale comigo quando estiver pronto para embarcar nessa jornada até Vernis.</t>
+      <c r="L229" s="32" t="inlineStr">
+        <is>
+          <t>Embora queira partir agora, você deve ter seus preparos. Fale comigo quando estiver pronto para a empreitada até Vernis.</t>
         </is>
       </c>
     </row>
@@ -4271,9 +4240,9 @@
           <t>Kettle says Vernis is located straight north from here. It's a bit of a journey, so it's wise to prepare enough food for the round trip.</t>
         </is>
       </c>
-      <c r="L239" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Kettle disse que Vernis fica diretamente ao norte daqui. É uma jornada considerável, então é aconselhável preparar comida suficiente para a viagem de ida e volta.  </t>
+      <c r="L239" s="32" t="inlineStr">
+        <is>
+          <t>Kettle diz que Vernis fica retinho ao norte daqui. A viagem é um pouco longa, então é sábio preparar comida suficiente para ida e volta.</t>
         </is>
       </c>
     </row>
@@ -4293,11 +4262,10 @@
 I'll go ahead to Vernis to scout the area. Reach out to me once you get there.</t>
         </is>
       </c>
-      <c r="L240" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Como podemos ficar lá por um tempo, certifique-se de resolver qualquer pendência que tenha nesta base.  _x000D_
-_x000D_
-Vou seguir à frente para Vernis para explorar a área. Entre em contato comigo assim que chegar lá.  </t>
+      <c r="L240" s="32" t="inlineStr">
+        <is>
+          <t>Como talvez fiquemos lá por um tempo, resolva qualquer pendência nesta base antes.
+Vou adiantar-me até Vernis para reconhecer a área. Fale comigo quando chegar lá.</t>
         </is>
       </c>
     </row>
@@ -4335,9 +4303,9 @@
           <t>Ah, #pc, you've finally arrived.</t>
         </is>
       </c>
-      <c r="L244" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, #pc, você finalmente chegou.  </t>
+      <c r="L244" s="32" t="inlineStr">
+        <is>
+          <t>Ah, #pc, finalmente chegou.</t>
         </is>
       </c>
     </row>
@@ -4357,11 +4325,10 @@
 I thought from Kettle’s tales that the mine had only recently been abandoned, but it appears to have been deserted for many years now. I've walked around a bit, and all I've found is debris and cobwebs.</t>
         </is>
       </c>
-      <c r="L245" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Esta é Vernis, que já foi uma próspera cidade mineradora...  _x000D_
-_x000D_
-Pelas histórias de Kettle, pensei que a mina tivesse sido abandonada recentemente, mas parece que está deserta há muitos anos. Andei por aí um pouco, e tudo que encontrei foram destroços e teias de aranha.  </t>
+      <c r="L245" s="32" t="inlineStr">
+        <is>
+          <t>Esta é Vernis, outrora próspera como cidade mineradora...
+Pelos relatos de Kettle, pensei que a mina tinha sido abandonada recentemente, mas parece desabitada há muitos anos. Andei por ali um pouco e só encontrei escombros e teias de aranha.</t>
         </is>
       </c>
     </row>
@@ -4379,9 +4346,9 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L246" t="inlineStr">
-        <is>
-          <t xml:space="preserve">…  </t>
+      <c r="L246" s="32" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
       <c r="M246" s="32" t="n"/>
@@ -4400,9 +4367,9 @@
           <t>You... You just made a bit unmotivated face, didn't you?</t>
         </is>
       </c>
-      <c r="L247" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você... Você acabou de fazer uma cara desanimada, não foi?  </t>
+      <c r="L247" s="32" t="inlineStr">
+        <is>
+          <t>Você... Você acabou de fazer uma carinha de desânimo, não fez?</t>
         </is>
       </c>
     </row>
@@ -4425,9 +4392,9 @@
           <t>…</t>
         </is>
       </c>
-      <c r="L248" t="inlineStr">
-        <is>
-          <t xml:space="preserve">…  </t>
+      <c r="L248" s="32" t="inlineStr">
+        <is>
+          <t>…</t>
         </is>
       </c>
     </row>
@@ -4445,9 +4412,9 @@
           <t>...#pc, looking at this abandoned mine and desolate land, do you feel nothing?</t>
         </is>
       </c>
-      <c r="L249" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...#pc, ao olhar para esta mina abandonada e esta terra desolada, você não sente nada?  </t>
+      <c r="L249" s="32" t="inlineStr">
+        <is>
+          <t>...#pc, olhando para esta mina abandonada e esta terra desolada, você não sente nada?</t>
         </is>
       </c>
     </row>
@@ -4465,9 +4432,9 @@
           <t>This place was once bustling with life and hope, inscribed in every stone. Sadly, that light has faded over time, and now not even a shadow remains.</t>
         </is>
       </c>
-      <c r="L250" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Este lugar já foi vibrante, cheio de vida e esperança, gravadas em cada pedra. Infelizmente, essa luz se apagou com o tempo, e agora nem mesmo uma sombra restou.  </t>
+      <c r="L250" s="32" t="inlineStr">
+        <is>
+          <t>Este lugar já foi fervilhando de vida e esperança, inscritas em cada pedra. Tristemente, essa luz se apagou com o tempo, e hoje nem sombra resta.</t>
         </is>
       </c>
     </row>
@@ -4485,21 +4452,18 @@
       </c>
       <c r="K251" s="36" t="inlineStr">
         <is>
-          <t>...But, I can hear it. The voice of these decayed rocks and withered soil whispering of past glories.
+          <t>...But, I can hear it. The voice of these decayed pebbles and withered soil whispering of past glories.
 "#pc, Vernis is not over yet..."
 "#pc, I can still make it..."
 "#pc, don't abandon us...!"</t>
         </is>
       </c>
-      <c r="L251" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Mas, eu posso ouvi-lo. A voz dessas rochas desgastadas e desse solo ressequido sussurrando sobre glórias passadas.  _x000D_
-_x000D_
-"#pc, Vernis ainda não acabou..."  _x000D_
-_x000D_
-"#pc, eu ainda posso me reerguer..."  _x000D_
-_x000D_
-"#pc, não nos abandone...!"  </t>
+      <c r="L251" s="32" t="inlineStr">
+        <is>
+          <t>...Mas eu consigo ouvir. A voz destas pedrinhas apodrecidas e desta terra murcha sussurrando glórias passadas.
+"#pc, Vernis ainda não acabou..."
+"#pc, eu ainda consigo..."
+"#pc, não nos abandone...!"</t>
         </is>
       </c>
     </row>
@@ -4519,11 +4483,10 @@
 Vernis isn’t just an abandoned mine that has seen its end. It is a place of infinite possibilities, a new beginning. I'd like to see the day when this place is bustling with the laughter of people once again.</t>
         </is>
       </c>
-      <c r="L252" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você também ouve, não é?  _x000D_
-_x000D_
-Vernis não é apenas uma mina abandonada que chegou ao fim. Este é um lugar de infinitas possibilidades, um novo começo. Eu gostaria de ver o dia em que este lugar volte a se encher com o riso das pessoas.  </t>
+      <c r="L252" s="32" t="inlineStr">
+        <is>
+          <t>Você também ouve, certo?
+Vernis não é só uma mina abandonada que chegou ao fim. É um lugar de possibilidades infinitas, um novo começo. Quero ver o dia em que este lugar volta a ferver com o riso das pessoas.</t>
         </is>
       </c>
     </row>
@@ -4567,11 +4530,10 @@
 Before we can really start developing, we need to clear the land first.</t>
         </is>
       </c>
-      <c r="L257" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Esta terra está deteriorada demais para atrair novos colonos. Até mesmo a mina está bloqueada por enormes rochas.  _x000D_
-_x000D_
-Antes de realmente começarmos o desenvolvimento, precisamos limpar a área primeiro.  </t>
+      <c r="L257" s="32" t="inlineStr">
+        <is>
+          <t>Esta terra está caída demais para atrair colonos novos. Até a mina está bloqueada por pedras enormes.
+Antes de começar o desenvolvimento de verdade, precisamos limpar a terra.</t>
         </is>
       </c>
     </row>
@@ -4591,11 +4553,10 @@
 Let me teach you how to make a bomb. It’s a recipe for a homemade bomb called "Flam". Use it to clear all the obstructive rocks.</t>
         </is>
       </c>
-      <c r="L258" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode tentar minerar as enormes rochas com uma picareta resistente, mas ainda assim será muito exaustivo.  _x000D_
-_x000D_
-Deixe-me ensinar você a fazer uma bomba. É uma receita para uma bomba caseira chamada "Flam". Use-a para remover todas as rochas que estão no caminho.  </t>
+      <c r="L258" s="32" t="inlineStr">
+        <is>
+          <t>Você até conseguiria minerar as pedras enormes com uma picareta resistente, mas ainda seria exaustivo.
+Deixe-me te ensinar a fazer uma bomba. É a receita de uma bomba caseira chamada "Flam". Use-a para limpar todas as pedras atrapalhadas.</t>
         </is>
       </c>
     </row>
@@ -4629,13 +4590,11 @@
 Once you've destroyed the huge rocks, come and talk to me. </t>
         </is>
       </c>
-      <c r="L260" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Felizmente, Vernis era uma cidade mineradora. Os materiais necessários para fabricar bombas devem ser fáceis de encontrar por aqui.  _x000D_
-_x000D_
-Lembre-se de que o poder destrutivo da bomba depende da dureza da pedra usada na fabricação. Um flam feito de granito deve ser forte o suficiente por enquanto.  _x000D_
-_x000D_
-Assim que destruir as enormes rochas, venha falar comigo.  </t>
+      <c r="L260" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por sorte, Vernis era uma cidade mineradora. Os materiais para fazer bombas devem ser fáceis de achar por aqui.
+Repare que o poder destrutivo da bomba depende da dureza da pedra usada na fabricação. Um flam de granito deve ser forte o bastante por ora.
+Quando destruir as pedras enormes, venha falar comigo. </t>
         </is>
       </c>
     </row>
@@ -4680,11 +4639,10 @@
 All we need now is to claim the rights to the land, and then we can start developing. I'll give you a deed, so read it aloud. </t>
         </is>
       </c>
-      <c r="L266" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh, você já terminou?  _x000D_
-_x000D_
-Agora só precisamos reivindicar os direitos sobre a terra e então podemos começar o desenvolvimento. Vou lhe dar uma escritura, então leia-a em voz alta.  </t>
+      <c r="L266" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Oh, já terminou?
+Agora só falta reivindicar os direitos da terra, e o desenvolvimento pode começar. Vou te dar uma escritura, leia-a em voz alta. </t>
         </is>
       </c>
     </row>
@@ -4702,9 +4660,9 @@
           <t>But before that, let me share some important things about acquiring new land.</t>
         </is>
       </c>
-      <c r="L267" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mas antes disso, deixe-me compartilhar algumas informações importantes sobre a aquisição de novas terras.  </t>
+      <c r="L267" s="32" t="inlineStr">
+        <is>
+          <t>Mas antes disso, deixe-me compartilhar coisas importantes sobre adquirir terra nova.</t>
         </is>
       </c>
     </row>
@@ -4722,9 +4680,9 @@
           <t>You can own as many lands as you like, but when you use a Scroll of Return, you'll only return to your current home. You can change your current home by using the Hearth Stone, so make sure to check that when you acquire a new land.</t>
         </is>
       </c>
-      <c r="L268" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pode possuir quantas terras quiser, mas ao usar um Pergaminho de Retorno, você sempre voltará para sua casa atual. Você pode mudar sua casa atual usando a Pedra do Lar, então certifique-se de verificar isso ao adquirir um novo terreno.  </t>
+      <c r="L268" s="32" t="inlineStr">
+        <is>
+          <t>Você pode possuir quantas terras quiser, mas quando usar um Pergaminho de Retorno, voltará só para o seu lar atual. Dá para mudar o lar atual pela Pedra do Lar, então confira isso ao adquirir uma terra nova.</t>
         </is>
       </c>
     </row>
@@ -4742,9 +4700,9 @@
           <t>If you want to move residents from your old base, invite them as companions, then take them to the new base and talk to them there. However, it's probably easier to move companions into the Hearth Stone at the residents' board and summon them locally.</t>
         </is>
       </c>
-      <c r="L269" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se quiser mover moradores da sua base antiga, convide-os como companheiros, leve-os até a nova base e fale com eles lá. No entanto, provavelmente será mais fácil movê-los usando a Pedra do Lar no quadro de moradores e convocá-los diretamente no novo local.  </t>
+      <c r="L269" s="32" t="inlineStr">
+        <is>
+          <t>Se quiser mudar moradores da base antiga, convide-os como companheiros, leve-os à base nova e fale com eles lá. Porém, provavelmente é mais fácil mover companheiros para a Pedra do Lar no quadro de moradores e invocá-los no local.</t>
         </is>
       </c>
     </row>
@@ -4764,11 +4722,10 @@
 There's no downside to owning multiple lands, and as your bases develop, you'll gain access to special products and convenient features like inter-base transfers. So, keep developing new lands! </t>
         </is>
       </c>
-      <c r="L270" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Por enquanto, é isso.  _x000D_
-_x000D_
-Não há desvantagens em possuir várias terras e, à medida que suas bases se desenvolvem, você terá acesso a produtos especiais e recursos convenientes, como transferências entre bases. Então, continue expandindo novas terras!  </t>
+      <c r="L270" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Por ora, é isso.
+Não há desvantagem em possuir várias terras, e conforme as bases se desenvolvem, você ganha produtos especiais e recursos práticos como transferências entre bases. Então continue desenvolvendo terras novas! </t>
         </is>
       </c>
     </row>
@@ -4846,9 +4803,8 @@
       </c>
       <c r="L279" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Muito bem, agora podemos desenvolver Vernis sem qualquer restrição.  _x000D_
-_x000D_
-Ainda é apenas um monte de destroços, mas assim que construirmos os prédios, os mineradores começarão a vir para cá. Com a capital real Palmia a leste e a cidade portuária de Kapul a oeste, é, sem dúvida, uma localização promissora.  </t>
+          <t>Bom, agora podemos desenvolver Vernis sem reservas.
+Ainda é só um monte de escombros, mas quando os prédios subirem, os mineiros começarão a chegar aos borbotões. Com a capital real Palmia a leste e a cidade portuária Kapul a oeste, a localização é promissora de verdade.</t>
         </is>
       </c>
     </row>
@@ -4871,9 +4827,9 @@
           <t>It seems the development is progressing well.</t>
         </is>
       </c>
-      <c r="L280" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Parece que o desenvolvimento está progredindo bem.  </t>
+      <c r="L280" s="32" t="inlineStr">
+        <is>
+          <t>Parece que o desenvolvimento está progredindo bem.</t>
         </is>
       </c>
     </row>
@@ -4891,9 +4847,9 @@
           <t>Ah, Kettle, you've arrived! And Quruitzia too!</t>
         </is>
       </c>
-      <c r="L281" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, Kettle, você chegou! E Quruitzia também!  </t>
+      <c r="L281" s="32" t="inlineStr">
+        <is>
+          <t>Ah, Kettle, você chegou! E Quruitzia também!</t>
         </is>
       </c>
     </row>
@@ -4916,9 +4872,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L282" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L282" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -4936,9 +4892,9 @@
           <t>We’ll need all the help we can get in this new land, so I called them both.</t>
         </is>
       </c>
-      <c r="L283" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Precisamos de toda a ajuda possível nesta nova terra, então os chamei.  </t>
+      <c r="L283" s="32" t="inlineStr">
+        <is>
+          <t>Vamos precisar de toda a ajuda possível nesta terra nova, então chamei os dois.</t>
         </is>
       </c>
     </row>
@@ -4956,9 +4912,9 @@
           <t>Now, have you entered the mine yet? I had to turn back as monsters were wandering around, but it seems there are still many ores buried there. It's a good idea to explore the mine when you have time to spare.</t>
         </is>
       </c>
-      <c r="L284" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agora, você já entrou na mina? Eu tive que recuar, pois havia monstros vagando por lá, mas parece que ainda há muitos minérios enterrados. É uma boa ideia explorar a mina quando tiver tempo disponível.  </t>
+      <c r="L284" s="32" t="inlineStr">
+        <is>
+          <t>Já entrou na mina? Eu tive de voltar porque monstros rondavam por lá, mas aparentemente ainda há muitos minérios enterrados. Vale a pena explorar a mina quando sobrar tempo.</t>
         </is>
       </c>
     </row>
@@ -4978,11 +4934,10 @@
 Develop this land and upgrade the Hearth Stone, then report back to me. Ask me anytime if you’re unsure how to upgrade it.</t>
         </is>
       </c>
-      <c r="L285" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Embora eu esteja curioso sobre o ouro adormecido na mina, por ora, os negócios da fronteira são nossa maior prioridade. Poderemos explorar mais fundo à medida que mais mineradores chegarem.  _x000D_
-_x000D_
-Desenvolva esta terra e melhore a Pedra do Lar, depois me avise. Pergunte-me a qualquer momento se tiver dúvidas sobre como aprimorá-la.  </t>
+      <c r="L285" s="32" t="inlineStr">
+        <is>
+          <t>Embora eu queira saber do ouro adormecido na mina, por ora, os negócios da fronteira vêm primeiro. Poderemos descer mais fundo quando mais mineiros chegarem.
+Desenvolva esta terra e faça a Pedra do Lar subir de nível, depois reporte a mim. Pergunte a mim quando quiser se não souber como.</t>
         </is>
       </c>
     </row>
@@ -5000,9 +4955,9 @@
           <t xml:space="preserve">Well, what are we waiting for? Let's revive Vernis into a lively mining town once again! </t>
         </is>
       </c>
-      <c r="L286" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem, o que estamos esperando? Vamos reviver Vernis e torná-la uma próspera cidade mineradora mais uma vez!  </t>
+      <c r="L286" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Então, o que estamos esperando? Vamos ressuscitar Vernis como uma cidade mineradora vivaz de novo! </t>
         </is>
       </c>
     </row>
@@ -5053,9 +5008,9 @@
           <t xml:space="preserve">(Voice echoing from beneath) GRRRAAAAWWWWRRRR!! </t>
         </is>
       </c>
-      <c r="L294" t="inlineStr">
-        <is>
-          <t xml:space="preserve">(Voz ecoando do subterrâneo) GRRRAAAAWWWWRRRR!!  </t>
+      <c r="L294" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">(Voz ecoando de baixo) GRRRAAAAWWWWRRRR!! </t>
         </is>
       </c>
     </row>
@@ -5078,9 +5033,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L295" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L295" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5098,9 +5053,9 @@
           <t xml:space="preserve">That voice again. It's scaring the miners into fleeing. It seems to be coming from underground, but what's going on? </t>
         </is>
       </c>
-      <c r="L296" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Essa voz de novo. Está assustando os mineradores, fazendo-os fugir. Parece vir do subsolo, mas o que está acontecendo?  </t>
+      <c r="L296" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Essa voz de novo. Está assustando os mineiros, que fogem. Parece vir do subterrâneo, mas o que será que está acontecendo? </t>
         </is>
       </c>
     </row>
@@ -5130,14 +5085,12 @@
 </t>
         </is>
       </c>
-      <c r="L297" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lord Loytel, sobre esse assunto...  _x000D_
-_x000D_
-Estão circulando rumores sobre uma sombra gigantesca nas profundezas da mina. Dizem que essa sombra pronunciou as seguintes palavras:  _x000D_
-_x000D_
-"EU SOU O DRAGÃO DE AÇO CORGON. OFEREÇAM A GAROTA DE CABELOS VERMELHOS COMO SACRIFÍCIO. PARTAM, SE PREZAM SUAS MISERÁVEIS VIDAS."_x000D_
-  </t>
+      <c r="L297" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Lorde Loytel, sobre esse assunto...
+Há rumores se espalhando sobre uma sombra colossal no fundo das minas. Dizem que a sombra pronunciou estas palavras:
+"EU SOU O DRAGÃO DE AÇO CORGON. OFEREÇAM A GAROTA RUIVA COMO SACRIFÍCIO. PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS."
+</t>
         </is>
       </c>
     </row>
@@ -5160,9 +5113,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L298" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L298" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5181,9 +5134,9 @@
           <t>This sounds like a threat... though it's somewhat incoherent... I think I have heard the name Steel Dragon Corgon before.</t>
         </is>
       </c>
-      <c r="L299" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isso soa como uma ameaça... embora um tanto incoerente... Acho que já ouvi esse nome, Dragão de Aço Corgon, antes.  </t>
+      <c r="L299" s="32" t="inlineStr">
+        <is>
+          <t>Parece uma ameaça... embora meio incoerente... Acho que já ouvi o nome Dragão de Aço Corgon antes.</t>
         </is>
       </c>
     </row>
@@ -5208,11 +5161,10 @@
 One of these stones, the Sage's Magic Stone, was given to the legendary dragon, the Steel Dragon Corgon. Though, it was said to have been slain by the dragon slayer 'Thorran' twenty years ago. </t>
         </is>
       </c>
-      <c r="L300" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Há muito tempo, existiam três poderosas pedras mágicas que continham um grande poder em Palmia. Elas foram entregues a seres formidáveis e malignos como chaves que guardavam um segredo.  _x000D_
-_x000D_
-Uma dessas pedras, a Pedra Mágica do Sábio, foi dada ao lendário dragão, o Dragão de Aço Corgon. No entanto, dizem que ele foi morto pelo caçador de dragões 'Thorran' há vinte anos.  </t>
+      <c r="L300" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Outrora havia três poderosas pedras mágicas guardando grande poder em Palmia. Foram enviadas aos seres mais formidáveis e malignos como chaves guardando um segredo.
+Uma dessas pedras, a Pedra Mágica do Sábio, foi dada ao dragão lendário, o Dragão de Aço Corgon. Ainda que se diga que ele foi morto pelo matador de dragões 'Thorran' vinte anos atrás. </t>
         </is>
       </c>
     </row>
@@ -5230,9 +5182,9 @@
           <t>A dragon that should be dead... This is turning into a troublesome matter. And I'm concerned about this demand to 'sacrifice the red-haired girl'. A girl with red hair..?</t>
         </is>
       </c>
-      <c r="L301" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Um dragão que deveria estar morto... Isso está se tornando um problema complicado. E me preocupa essa exigência de 'sacrificar a garota de cabelos vermelhos'. Uma garota de cabelos vermelhos..?  </t>
+      <c r="L301" s="32" t="inlineStr">
+        <is>
+          <t>Um dragão que deveria estar morto... Isso está virando um problema sério. E me preocupa essa exigência de 'sacrificar a garota ruiva'. Uma garota de cabelos ruivos...?</t>
         </is>
       </c>
     </row>
@@ -5255,9 +5207,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L302" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L302" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5275,9 +5227,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L303" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L303" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5295,9 +5247,9 @@
           <t>If we were to sacrifice Quruitzia...</t>
         </is>
       </c>
-      <c r="L304" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se sacrificássemos Quruitzia...  </t>
+      <c r="L304" s="32" t="inlineStr">
+        <is>
+          <t>Se sacrificássemos a Quruitzia...</t>
         </is>
       </c>
     </row>
@@ -5320,9 +5272,9 @@
           <t>...Lord Loytel.</t>
         </is>
       </c>
-      <c r="L305" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Lord Loytel.  </t>
+      <c r="L305" s="32" t="inlineStr">
+        <is>
+          <t>...Lorde Loytel.</t>
         </is>
       </c>
     </row>
@@ -5342,11 +5294,10 @@
 Still, a dragon living deep in the mines, huh.</t>
         </is>
       </c>
-      <c r="L306" t="inlineStr">
-        <is>
-          <t xml:space="preserve">N-Não, eu só estava refletindo sobre o absurdo disso. É claro que não podemos aceitar tal exigência!  _x000D_
-_x000D_
-Ainda assim, um dragão vivendo nas profundezas da mina, hein.  </t>
+      <c r="L306" s="32" t="inlineStr">
+        <is>
+          <t>N-Não, eu só estava ponderando o absurdo. Claro que não obedeceremos a tal exigência!
+Ainda assim, um dragão morando no fundo das minas, hein.</t>
         </is>
       </c>
     </row>
@@ -5369,9 +5320,9 @@
           <t xml:space="preserve">Gold. The Steel dragon is said to crave gold. </t>
         </is>
       </c>
-      <c r="L307" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ouro. Dizem que o Dragão de Aço deseja ouro.  </t>
+      <c r="L307" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ouro. Dizem que o Dragão de Aço cobiça ouro. </t>
         </is>
       </c>
     </row>
@@ -5389,9 +5340,9 @@
           <t>I see, gathering gold is a dragon trait I've heard of. So, you're suggesting that there's a hoard of gold collected by the dragon hidden underground in the mines.</t>
         </is>
       </c>
-      <c r="L308" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Entendo, já ouvi falar que os dragões têm essa obsessão. Então você está sugerindo que existe um tesouro de ouro acumulado pelo dragão escondido nas minas.  </t>
+      <c r="L308" s="32" t="inlineStr">
+        <is>
+          <t>Entendo, reunir ouro é um traço de dragão que já ouvi falar. Então está sugerindo que há um tesouro de ouro coletado pelo dragão escondido no subterrâneo das minas.</t>
         </is>
       </c>
     </row>
@@ -5414,9 +5365,9 @@
           <t xml:space="preserve">No, it's said that the Steel Dragon actually eats gold. </t>
         </is>
       </c>
-      <c r="L309" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não, dizem que o Dragão de Aço na verdade come ouro.  </t>
+      <c r="L309" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Não, dizem que o Dragão de Aço na verdade come ouro. </t>
         </is>
       </c>
     </row>
@@ -5434,9 +5385,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L310" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L310" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -5454,9 +5405,9 @@
           <t>...Well, that simplifies matters.</t>
         </is>
       </c>
-      <c r="L311" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Bom, isso simplifica as coisas.  </t>
+      <c r="L311" s="32" t="inlineStr">
+        <is>
+          <t>...Bom, isso simplifica as coisas.</t>
         </is>
       </c>
     </row>
@@ -5476,11 +5427,10 @@
 Though I'd like to set out immediately, you must have your preparations to make. Speak to me once you're ready to hunt the dragon.</t>
         </is>
       </c>
-      <c r="L312" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você ouviu, #pc, agora é com você. Não podemos permitir que um dragão ganancioso que devora nosso ouro permaneça em Vernis por muito tempo.  _x000D_
-_x000D_
-Embora eu queira partir imediatamente, você deve fazer seus preparativos. Fale comigo quando estiver pronto para caçar o dragão.  </t>
+      <c r="L312" s="32" t="inlineStr">
+        <is>
+          <t>Você ouviu, #pc, agora é com você. Não podemos permitir que um dragão frívolo que come nosso ouro fique de molho em Vernis por muito tempo.
+Embora queira partir já, você deve ter seus preparos. Fale comigo quando estiver pronto para caçar o dragão.</t>
         </is>
       </c>
     </row>
@@ -5515,9 +5465,9 @@
           <t xml:space="preserve">Facing a dragon requires appropriate preparations. High-quality gear is essential, and you'll need to protect yourself from the dragon's fiery breath with fire resistance and measures to prevent your belongings from catching fire. </t>
         </is>
       </c>
-      <c r="L318" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Enfrentar um dragão exige preparações adequadas. Equipamentos de alta qualidade são essenciais, e você precisará se proteger do sopro flamejante do dragão com resistência ao fogo e medidas para evitar que seus pertences peguem fogo.  </t>
+      <c r="L318" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Encarar um dragão exige preparos adequados. Equipamento de qualidade é essencial, e você vai precisar se proteger do sopro flamejante do dragão com resistência ao fogo e medidas para que suas pertenças não peguem fogo. </t>
         </is>
       </c>
     </row>
@@ -5539,13 +5489,11 @@
 Also, when hit by elemental attacks like fire or ice, your belongings could catch fire or shatter. Be sure to increase your resistance or pack fireproof and coldproof blankets in your backpack to prevent item destruction.</t>
         </is>
       </c>
-      <c r="L319" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Talvez você já saiba disso como aventureiro, mas deixe-me explicar só por precaução.  _x000D_
-_x000D_
-Resistências podem reduzir significativamente o dano causado por certos elementos e também diminuir a chance de sofrer efeitos negativos como queimaduras ou cegueira.  _x000D_
-_x000D_
-Além disso, ao ser atingido por ataques elementais como fogo ou gelo, seus pertences podem pegar fogo ou se estilhaçar. Certifique-se de aumentar sua resistência ou carregar mantas à prova de fogo e frio na mochila para evitar a destruição de itens.  </t>
+      <c r="L319" s="32" t="inlineStr">
+        <is>
+          <t>Você talvez saiba mais disso como aventureiro, mas deixe-me explicar por precaução.
+Resistências reduzem muito o dano de elementos específicos e também diminuem a chance de sofrer estados como queimadura ou cegueira.
+Além disso, ao ser atingido por ataques elementais como fogo ou gelo, suas pertenças podem pegar fogo ou se estilhaçar. Aumente suas resistências e leve cobertas corta-fogo e anti-gelo na mochila para evitar a destruição de itens.</t>
         </is>
       </c>
     </row>
@@ -5579,11 +5527,10 @@
 The dragon resides deep within the mines, so take this key to the lower levels as well.</t>
         </is>
       </c>
-      <c r="L321" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aqui, pegue isto. Pedi ao Kettle para preparar alguns itens que podem ajudá-lo a derrotar o dragão.  _x000D_
-_x000D_
-O dragão reside nas profundezas da mina, então leve esta chave para acessar os níveis inferiores também.  </t>
+      <c r="L321" s="32" t="inlineStr">
+        <is>
+          <t>Toma, leve estes. Mandei Kettle preparar alguns itens que podem ajudar na caçada ao dragão.
+O dragão reside no fundo das minas, então leve também esta chave para os níveis inferiores.</t>
         </is>
       </c>
     </row>
@@ -5603,11 +5550,10 @@
 Proceed with caution into the lower levels, and gauge your own strength. If the enemies feel too strong, don't hesitate to retreat and regroup.</t>
         </is>
       </c>
-      <c r="L322" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Muito bem, agora você está pronto!  _x000D_
-_x000D_
-Siga com cautela para os níveis inferiores e avalie sua própria força. Se os inimigos parecerem fortes demais, não hesite em recuar e se reagrupar.  </t>
+      <c r="L322" s="32" t="inlineStr">
+        <is>
+          <t>Muito bem, está tudo pronto!
+Desça com cautela aos níveis inferiores e meça suas forças. Se os inimigos parecerem fortes demais, não hesite em recuar e se reorganizar.</t>
         </is>
       </c>
     </row>
@@ -5658,11 +5604,10 @@
 Yes, #pc, we got worried and decided to follow you.</t>
         </is>
       </c>
-      <c r="L330" t="inlineStr">
-        <is>
-          <t>Que ar sombrio é esse por aqui...?_x000D_
-_x000D_
-Sim, #pc, ficamos preocupados e decidimos segui-lo.</t>
+      <c r="L330" s="32" t="inlineStr">
+        <is>
+          <t>Que ar sinistro é esse por aqui...?
+É, #pc, ficamos preocupados e resolvemos te seguir.</t>
         </is>
       </c>
     </row>
@@ -5680,9 +5625,9 @@
           <t>Look at these gruesome charred corpses strewn everywhere. Is this the work of the Steel Dragon?</t>
         </is>
       </c>
-      <c r="L331" t="inlineStr">
-        <is>
-          <t>Olhe para esses cadáveres horríveis espalhados por toda parte. Isso foi obra do Dragão de Aço?</t>
+      <c r="L331" s="32" t="inlineStr">
+        <is>
+          <t>Olhe esses cadáveres carbonizados espalhados por toda parte. Isto é obra do Dragão de Aço?</t>
         </is>
       </c>
     </row>
@@ -5709,13 +5654,11 @@
 This scorched corpse carries a scent I recognize... they are of Tephra, the ancient demon of molten rock, the master of scorching flames.</t>
         </is>
       </c>
-      <c r="L332" t="inlineStr">
-        <is>
-          <t>Não, dragões não fazem isso._x000D_
-_x000D_
-Dragões são criaturas singulares. O destino se entrelaça com seu poder, atraindo diversos seres a ele._x000D_
-_x000D_
-Reconheço essas marcas nos corpos carbonizados... são de Tephra, o antigo demônio da rocha derretida, mestre das chamas ardentes.</t>
+      <c r="L332" s="32" t="inlineStr">
+        <is>
+          <t>Não, dragões não fazem isso.
+Dragões são criaturas únicas. O destino tece ao redor do poder deles, atraindo vários seres atraídos por ele.
+Este cadáver carbonizado exala um cheiro que reconheço... são de Tephra, o demônio ancestral da rocha derretida, o senhor das chamas abrasadoras.</t>
         </is>
       </c>
     </row>
@@ -5735,11 +5678,10 @@
 ...It's an adventurer job, of course. Do you think a Frontier Inspector is expected to fight a monster like this?</t>
         </is>
       </c>
-      <c r="L333" t="inlineStr">
-        <is>
-          <t>Um demônio... deve ser um servo de Corgon. Certo, #pc, deixo isso com você._x000D_
-_x000D_
-...É um trabalho para aventureiros, claro. Você acha que um Inspetor da Fronteira deve enfrentar um monstro desses?</t>
+      <c r="L333" s="32" t="inlineStr">
+        <is>
+          <t>Um demônio, deve ser um capacho de Corgon. Muito bem, #pc, deixo com você.
+...É trabalho de aventureiro, claro. Acha que se espera de um Inspetor de Fronteira que lute com um monstro desses?</t>
         </is>
       </c>
     </row>
@@ -5770,9 +5712,9 @@
           <t>Here it comes! Show the demon what you are made of!</t>
         </is>
       </c>
-      <c r="L336" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lá vem ele! Mostre ao demônio do que você é capaz!  </t>
+      <c r="L336" s="32" t="inlineStr">
+        <is>
+          <t>Lá vem ele! Mostre ao demônio do que você é capaz!</t>
         </is>
       </c>
     </row>
@@ -5839,10 +5781,10 @@
       </c>
       <c r="L344" s="36" t="inlineStr">
         <is>
-          <t>Bom trabalho!
-Você é mesmo um grande aventureiro, não é? Tenho que admitir, estou impressionado.
-Embora, agora que o servo dele foi derrotado, o Dragão de Aço não ficará em silêncio. Uh... que sombra enorme é essa...? 
-(Mantenha pressionado CTRL para pular)</t>
+          <t xml:space="preserve">Bom trabalho!
+Que aventureiro, hein? Confesso que estou impressionado.
+Apesar disso, agora que o capacho dele foi derrotado, o Dragão de Aço não ficará calado. Uh... o que é essa sombra enorme...?
+(Segure CTRL para pular) </t>
         </is>
       </c>
     </row>
@@ -5949,11 +5891,9 @@
       </c>
       <c r="L350" s="36" t="inlineStr">
         <is>
-          <t>EU SOU O DRAGÃO DE AÇO CORGON._x000D_
-_x000D_
-HUMANOS ESTÚPIDOS._x000D_
-_x000D_
-PARTAM, SE PREZAM POR SUAS VIDAS MISERÁVEIS.</t>
+          <t>EU SOU O DRAGÃO DE AÇO CORGON.
+VOCÊS, HUMANOS ESTÚPIDOS.
+PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS.</t>
         </is>
       </c>
     </row>
@@ -5985,7 +5925,7 @@
       </c>
       <c r="L351" s="36" t="inlineStr">
         <is>
-          <t>Fale no diabo, e ele aparece. Está pronto, #pc?</t>
+          <t>Falando do diabo, ele aparece. Está pronto, #pc?</t>
         </is>
       </c>
     </row>
@@ -6021,11 +5961,9 @@
       </c>
       <c r="L352" s="36" t="inlineStr">
         <is>
-          <t>EU SOU O DRAGÃO DE AÇO CORGON..._x000D_
-_x000D_
-HUMANOS ESTÚPIDOS..._x000D_
-_x000D_
-PARTAM, SE PREZAM POR SUAS VIDAS MISERÁVEIS...</t>
+          <t>EU SOU O DRAGÃO DE AÇO CORGON...
+VOCÊS, HUMANOS ESTÚPIDOS...
+PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS...</t>
         </is>
       </c>
     </row>
@@ -6057,7 +5995,7 @@
       </c>
       <c r="L353" s="36" t="inlineStr">
         <is>
-          <t>Ugh, que voz assustadora! Aí vem ele, #pc, fique atento!</t>
+          <t>Ugh, que voz aterrorizante! Lá vem ele, #pc, fique esperto!</t>
         </is>
       </c>
     </row>
@@ -6091,9 +6029,8 @@
       </c>
       <c r="L354" s="36" t="inlineStr">
         <is>
-          <t>EU SOU O DRAGÃO DE AÇO CORGON..._x000D_
-_x000D_
-PARTAM, SE PREZAM POR SUAS VIDAS MISERÁVEIS...</t>
+          <t>EU SOU O DRAGÃO DE AÇO CORGON...
+PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS...</t>
         </is>
       </c>
     </row>
@@ -6189,7 +6126,7 @@
       </c>
       <c r="L357" s="36" t="inlineStr">
         <is>
-          <t>Tem algo... estranho aqui?</t>
+          <t>Tem... algo errado aqui?</t>
         </is>
       </c>
     </row>
@@ -6259,13 +6196,10 @@
       </c>
       <c r="L359" s="36" t="inlineStr">
         <is>
-          <t>EU SOU O DRAGÃO DE AÇO CORGON...!_x000D_
-_x000D_
-PARTAM, SE PREZAM POR SUAS VIDAS MISERÁVEIS...!_x000D_
-_x000D_
-EU SOU O DRAGÃO DE AÇO CORGON...!_x000D_
-_x000D_
-PARTAM, SE PREZAM POR SUAS VIDAS MISERÁVEIS...!</t>
+          <t>EU SOU O DRAGÃO DE AÇO CORGON...!
+PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS...!
+EU SOU O DRAGÃO DE AÇO CORGON...!
+PARTAM, SE AMAM SUAS VIDAS MISERÁVEIS...!</t>
         </is>
       </c>
     </row>
@@ -6297,7 +6231,7 @@
       </c>
       <c r="L360" s="36" t="inlineStr">
         <is>
-          <t>Esse dragão está se repetindo como uma máquina quebrada. Definitivamente tem algo errado.</t>
+          <t>Esse dragão está se repetindo como máquina quebrada. Tem alguma coisa muito suspeita aí.</t>
         </is>
       </c>
     </row>
@@ -6329,7 +6263,7 @@
       </c>
       <c r="L361" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">#pc, me empreste sua tocha. Vamos lançar um pouco de luz nisso... Vamos, mostre-se, Dragão de Aço Corgon!  </t>
+          <t>#pc, me empresta sua tocha. Vamos clarear essa... Ora, mostre-se, Dragão de Aço Corgon!</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6469,7 @@
       </c>
       <c r="L369" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">O que diabos é isso...?  </t>
+          <t>O que é isso, afinal...?</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6501,7 @@
       </c>
       <c r="L370" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Será que é isso que projetou uma sombra tão enorme...?  </t>
+          <t>Será que é isto o que projetava uma sombra tão enorme...</t>
         </is>
       </c>
     </row>
@@ -6599,7 +6533,7 @@
       </c>
       <c r="L371" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Um... filhote de dragão...  </t>
+          <t>O... filho do dragão...</t>
         </is>
       </c>
     </row>
@@ -6631,7 +6565,7 @@
       </c>
       <c r="L372" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Acho que consigo lidar com isso sozinho. Então, este aqui estava usando o nome do Dragão de Aço para assustar os mineradores de Vernis?  </t>
+          <t>Eu provavelmente derrubaria isso sozinho. Então era este que usava o nome do Dragão de Aço para amedrontar os mineiros de Vernis?</t>
         </is>
       </c>
     </row>
@@ -6663,7 +6597,7 @@
       </c>
       <c r="L373" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Um dragão jovem... e o Dragão de Aço Corgon, que se pensava estar extinto há décadas... Entendo, esse deve ser o último descendente de Corgon.  </t>
+          <t>...Um dragão filhote... e o Dragão de Aço Corgon, que se julgava extinto há décadas... Entendo, este deve ser o último descendente vivo de Corgon.</t>
         </is>
       </c>
     </row>
@@ -6714,7 +6648,7 @@
       </c>
       <c r="L375" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Filho de Corgon...  </t>
+          <t>O filho de Corgon...</t>
         </is>
       </c>
     </row>
@@ -6773,9 +6707,8 @@
       </c>
       <c r="L378" s="36" t="inlineStr">
         <is>
-          <t>Sim, ele deve ter repetido as mesmas palavras, imitando seu progenitor._x000D_
-_x000D_
-Ou talvez, o próprio Dragão de Aço moribundo tenha ensinado isso a este pequeno para afastar os humanos...</t>
+          <t>Sim, deve ter repetido as mesmas palavras, imitando o pai.
+Ou talvez o próprio Dragão de Aço, em seus últimos momentos, tenha ensinado a ele, para afastar os humanos...</t>
         </is>
       </c>
     </row>
@@ -6871,7 +6804,7 @@
       </c>
       <c r="L381" s="36" t="inlineStr">
         <is>
-          <t>(sussurrando)...Lorde Loytel, esta é sua chance de se redimir com Quruitzia... Ela se vê na situação desse filhote de dragão e sente profunda empatia...</t>
+          <t>(sussurrando)...Lorde Loytel, esta é a chance de fazer as pazes com a Quruitzia... Ela se enxerga na situação deste filhote e está profundamente comovida...</t>
         </is>
       </c>
     </row>
@@ -6903,7 +6836,7 @@
       </c>
       <c r="L382" s="36" t="inlineStr">
         <is>
-          <t>Ah! (sussurrando)... Certo, este é o momento em que devo despertar e aceitar os verdadeiros sentimentos de Quruitzia, não é? Estou lhe devendo uma, Lady Farris!</t>
+          <t>Ah! (sussurrando) ...Verdade, é aqui que devo extrair e acolher os sentimentos verdadeiros de Quruitzia, né? Devo-lhe muito... Lady Farris!</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6868,7 @@
       </c>
       <c r="L383" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">...(olha de relance) </t>
+          <t xml:space="preserve">...(olha de lado) </t>
         </is>
       </c>
     </row>
@@ -6967,7 +6900,7 @@
       </c>
       <c r="L384" s="36" t="inlineStr">
         <is>
-          <t>Ha! Fingir-se de inofensivo agora não vai adiantar nada, dragão vil! Quase sacrificamos um dos nossos por sua causa. Você tem explicações a dar.</t>
+          <t>Ha! Fingir ser inofensivo agora não vai te salvar, dragão vil! Quase sacrificamos um dos nossos por tua causa. Você tem muito a explicar.</t>
         </is>
       </c>
     </row>
@@ -7031,7 +6964,7 @@
       </c>
       <c r="L386" s="36" t="inlineStr">
         <is>
-          <t>O quê, já esqueceu, Quruitzia? Esse dragão vil quase fez com que você...</t>
+          <t>Hã, já esqueceu, Quruitzia? Este dragão vil quase te...</t>
         </is>
       </c>
     </row>
@@ -7063,7 +6996,7 @@
       </c>
       <c r="L387" s="36" t="inlineStr">
         <is>
-          <t>Este aqui não fez nada de errado...!</t>
+          <t>Este não fez nada de errado...!</t>
         </is>
       </c>
     </row>
@@ -7095,7 +7028,7 @@
       </c>
       <c r="L388" s="36" t="inlineStr">
         <is>
-          <t>Dragão, diga-me... por que me escolheu como sacrifício?</t>
+          <t>Dragão, me diga... por que escolheu a mim como sacrifício?</t>
         </is>
       </c>
     </row>
@@ -7159,7 +7092,7 @@
       </c>
       <c r="L390" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Meu... olho? O que quer dizer...? </t>
+          <t xml:space="preserve">Meu... olho? Como assim...? </t>
         </is>
       </c>
     </row>
@@ -7223,7 +7156,7 @@
       </c>
       <c r="L392" s="36" t="inlineStr">
         <is>
-          <t>O que é isso? Nem consegue falar direito quando está com medo? Ha, parecia tão formidável quando se escondia atrás daquela sombra gigantesca!</t>
+          <t>Que é isso? Não sabe nem falar direito quando assustado? Ha, e parecia tão temível quando se escondia atrás daquela sombra enorme!</t>
         </is>
       </c>
     </row>
@@ -7255,7 +7188,7 @@
       </c>
       <c r="L393" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Loytel, fique quieto! </t>
+          <t xml:space="preserve">...Loytel, quieto! </t>
         </is>
       </c>
     </row>
@@ -7300,7 +7233,7 @@
       </c>
       <c r="L395" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ma... ma...) </t>
+          <t xml:space="preserve">(mã... mã...) </t>
         </is>
       </c>
     </row>
@@ -7377,7 +7310,7 @@
       </c>
       <c r="L398" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ma... maa...) </t>
+          <t xml:space="preserve">(mã... maa...) </t>
         </is>
       </c>
     </row>
@@ -7409,7 +7342,7 @@
       </c>
       <c r="L399" s="36" t="inlineStr">
         <is>
-          <t>Este aqui... me vê como...</t>
+          <t>Este... me enxerga como...</t>
         </is>
       </c>
     </row>
@@ -7486,7 +7419,7 @@
       </c>
       <c r="L402" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Loytel... Quero levar este comigo. </t>
+          <t xml:space="preserve">Loytel... eu quero levar este para casa. </t>
         </is>
       </c>
     </row>
@@ -7582,7 +7515,7 @@
       </c>
       <c r="L405" s="36" t="inlineStr">
         <is>
-          <t>Por quê?!</t>
+          <t>Por quê!</t>
         </is>
       </c>
     </row>
@@ -7604,7 +7537,7 @@
       </c>
       <c r="J406" s="39" t="inlineStr">
         <is>
-          <t>考えても見ろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
+          <t>考えてもみろ。この竜は黄金を食べるんだろう？そんな竜を、貧乏な我々がどうやって養うというのだ？</t>
         </is>
       </c>
       <c r="K406" s="40" t="inlineStr">
@@ -7614,7 +7547,7 @@
       </c>
       <c r="L406" s="36" t="inlineStr">
         <is>
-          <t>Pense bem. Esse dragão se alimenta de ouro, não? Como vamos alimentá-lo se já mal temos o suficiente para nós?</t>
+          <t>Pense bem. Este dragão come ouro, não come? Como vamos alimentá-lo, se quase não somos ricos?</t>
         </is>
       </c>
     </row>
@@ -7646,7 +7579,7 @@
       </c>
       <c r="L407" s="36" t="inlineStr">
         <is>
-          <t>Eu... cozinharei. Pesquisarei o que ele pode comer, eu... aprenderei alquimia... para que nunca passe fome...</t>
+          <t>Eu... cozinho. Vou pesquisar o que ele pode comer, vou... aprender alquimia... para que ele nunca passe fome...</t>
         </is>
       </c>
     </row>
@@ -7678,7 +7611,7 @@
       </c>
       <c r="L408" s="36" t="inlineStr">
         <is>
-          <t>...Mesmo que esse aqui goste da sua comida, continua sendo um dragão, uma criatura de imenso perigo. E se ele se irritar e cuspir fogo? E se crescer e começar a atacar pessoas?</t>
+          <t>...Suponha que ele goste do seu cozinhado: ainda é um dragão, criatura de imenso perigo. E se ficar com raiva e soltar fogo? E se crescer e começar a atacar pessoas?</t>
         </is>
       </c>
     </row>
@@ -7742,7 +7675,7 @@
       </c>
       <c r="L410" s="36" t="inlineStr">
         <is>
-          <t>Por favor, Loytel. Quero proteger este.</t>
+          <t>Por favor, Loytel. Eu quero proteger este.</t>
         </is>
       </c>
     </row>
@@ -7808,9 +7741,8 @@
       </c>
       <c r="L412" s="36" t="inlineStr">
         <is>
-          <t>...Ha, eu não percebia o quanto você era teimosa._x000D_
-_x000D_
-Acho que finalmente te entendo, Quruitzia. Cla...</t>
+          <t>...Ha, não sabia que você era tão teimosa.
+Acho que finalmente entendi você, Quruitzia. É clar...</t>
         </is>
       </c>
     </row>
@@ -7842,7 +7774,7 @@
       </c>
       <c r="L413" s="36" t="inlineStr">
         <is>
-          <t>Claro que devemos levá-lo para casa! Oh, Quruitzia... Seu apelo sincero tocou nossos corações!</t>
+          <t>Claro que devemos levá-lo para casa! Oh, Quruitzia... Seu apelo sincero comoveu nossos corações!</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7806,7 @@
       </c>
       <c r="L414" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">O quê-... Lady Farris...? </t>
+          <t xml:space="preserve">O-que-...Lady Farris...? </t>
         </is>
       </c>
     </row>
@@ -7908,9 +7840,8 @@
       </c>
       <c r="L415" s="36" t="inlineStr">
         <is>
-          <t>Oh, o descendente do lendário Dragão de Aço, e uma jovem garota carregando um passado trágico...! Esse encontro fatídico certamente inspirará inúmeras histórias e canções que tocarão a alma de muitos._x000D_
-_x000D_
-Quruitzia, vamos criar este pequeno para se tornar um magnífico dragão com nossas próprias mãos!</t>
+          <t>Oh, o descendente do lendário Dragão de Aço, e uma jovem carregando um passado trágico...! Este encontro do destino há de inspirar incontáveis contos e canções que tocarão a alma de muitos.
+Quruitzia, vamos criar este para ser um dragão magnífico com as nossas mãos!</t>
         </is>
       </c>
     </row>
@@ -7974,7 +7905,7 @@
       </c>
       <c r="L417" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ma... maa...) </t>
+          <t xml:space="preserve">(mã... maa...) </t>
         </is>
       </c>
     </row>
@@ -8038,7 +7969,7 @@
       </c>
       <c r="L419" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">...O que acabou de acontecer? </t>
+          <t xml:space="preserve">...O que foi que aconteceu agora? </t>
         </is>
       </c>
     </row>
@@ -8102,7 +8033,7 @@
       </c>
       <c r="L421" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Heh, parece que você assumiu um grande papel, Loytel. Agradeço por isso. </t>
+          <t xml:space="preserve">Heh, parece que você assumiu uma tarefa e tanto, Loytel. Fico grata. </t>
         </is>
       </c>
     </row>
@@ -8134,7 +8065,7 @@
       </c>
       <c r="L422" s="36" t="inlineStr">
         <is>
-          <t>...Eu continuo sendo o vilão, não é?</t>
+          <t>...Eu fico de vilão, né?</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8161,7 @@
       </c>
       <c r="L430" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bem, resolvemos o problema da mina, mas parece que todo o ouro foi devorado por esse pequeno.  </t>
+          <t>Bom, resolvemos o problema da mina, mas descobrimos que todo o ouro já foi comido por este pequeno aqui.</t>
         </is>
       </c>
     </row>
@@ -8262,7 +8193,7 @@
       </c>
       <c r="L431" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(mokyu)  </t>
+          <t>(mokyu)</t>
         </is>
       </c>
     </row>
@@ -8290,7 +8221,7 @@
       </c>
       <c r="L432" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">O Dragão de Aço Corgon, hein? Um nome tão grandioso para alguém tão pequeno.  </t>
+          <t>O Dragão de Aço Corgon, é? Bem pequeno para um nome tão grandioso.</t>
         </is>
       </c>
     </row>
@@ -8326,11 +8257,9 @@
       </c>
       <c r="L433" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">O lendário Dragão de Aço era dito ser uma criatura colossal, erguendo-se acima dos muros de Palmia.  _x000D_
-_x000D_
-Será que este aqui é apenas jovem, ou algo está impedindo seu crescimento? E há também a questão da pedra mágica que supostamente foi enviada ao Dragão de Aço, e o motivo pelo qual essa criança buscou Quruitzia como sacrifício... Temos muito a aprender com esse pequeno dragão.  _x000D_
-_x000D_
-Mas... veja só.  </t>
+          <t>Dizem que o lendário Dragão de Aço era uma criatura colossal, maior que as muralhas de Palmia.
+Este é apenas jovem, ou há algo impedindo seu crescimento? E ainda há a questão da pedra mágica que dizem ter sido entregue ao Dragão de Aço, e o motivo de este filhote querer Quruitzia como sacrifício... Temos muito a aprender com este dragão filhote.
+Mas... olhe-os ali.</t>
         </is>
       </c>
     </row>
@@ -8362,7 +8291,7 @@
       </c>
       <c r="L434" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(Corgon...♪)  </t>
+          <t xml:space="preserve">(Corgon...♪) </t>
         </is>
       </c>
     </row>
@@ -8394,7 +8323,7 @@
       </c>
       <c r="L435" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">(ma... maa...)  </t>
+          <t>(mã... maa...)</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8355,7 @@
       </c>
       <c r="L436" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">...Ver o rosto de Quruitzia se iluminar com um sorriso vale mais para mim do que uma montanha de ouro.  </t>
+          <t>...Ver o rosto de Quruitzia se iluminar com um sorriso vale mais para mim que uma montanha de ouro.</t>
         </is>
       </c>
     </row>
@@ -8460,9 +8389,8 @@
       </c>
       <c r="L437" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Viajamos por tanto tempo e tão longe, mas parece que finalmente encontramos um lugar para criar raízes.  _x000D_
-_x000D_
-Não apenas como visitantes, mas espero fazer parte de suas vidas aqui, como um de vocês, se nos aceitarem.  </t>
+          <t>Viajamos longe e por muito tempo, mas parece que finalmente encontramos um lugar para fincar raízes.
+Não só como hóspedes: espero poder me juntar às vidas de vocês aqui como um de vocês, se nos aceitarem.</t>
         </is>
       </c>
     </row>
@@ -8492,9 +8420,8 @@
       </c>
       <c r="L438" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Oh, é claro, será um grande prazer!  _x000D_
-_x000D_
-Bem-vindos novamente, Kettle, Quruitzia. E você também, pequeno dragão.  </t>
+          <t>Oh, claro, será um prazer!
+Sejam bem-vindos mais uma vez, Kettle, Quruitzia. E você também, pequeno dragão.</t>
         </is>
       </c>
     </row>
@@ -8526,7 +8453,7 @@
       </c>
       <c r="L439" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Mokyu!  </t>
+          <t>Mokyu!</t>
         </is>
       </c>
     </row>
@@ -8554,7 +8481,7 @@
       </c>
       <c r="L440" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">Sem ouro desta vez, mas bem, esse não é um final tão ruim, #pc, é?  </t>
+          <t>Sem ouro desta vez, mas, bom, este final não é dos piores, #pc, né?</t>
         </is>
       </c>
     </row>
@@ -8605,9 +8532,9 @@
           <t>Ah, preparing food already? Admirable dedication so early in the morning, Quru...Quru..</t>
         </is>
       </c>
-      <c r="L446" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, já preparando comida? Admirável dedicação tão cedo pela manhã, Quru...Quru..  </t>
+      <c r="L446" s="32" t="inlineStr">
+        <is>
+          <t>Ah, preparando comida já? Dedicação admirável tão cedo, Quru...Quru..</t>
         </is>
       </c>
     </row>
@@ -8626,9 +8553,9 @@
           <t>Quruitzia.</t>
         </is>
       </c>
-      <c r="L447" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Quruitzia.  </t>
+      <c r="L447" s="32" t="inlineStr">
+        <is>
+          <t>Quruitzia.</t>
         </is>
       </c>
     </row>
@@ -8714,9 +8641,9 @@
           <t>#pc, Lady Farris, everyone...</t>
         </is>
       </c>
-      <c r="L460" t="inlineStr">
-        <is>
-          <t xml:space="preserve">#pc, Lady Farris, todos...  </t>
+      <c r="L460" s="32" t="inlineStr">
+        <is>
+          <t>#pc, Lady Farris, todos...</t>
         </is>
       </c>
     </row>
@@ -8736,11 +8663,10 @@
 Fine, do with me as you will, but no matter how much you berate me, I don't have money, nor do I intend to pay twenty million orens.</t>
         </is>
       </c>
-      <c r="L461" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Suspiro, vocês me encontraram tão facilmente.  _x000D_
-_x000D_
-Tudo bem, façam o que quiserem comigo, mas não importa o quanto me repreendam, eu não tenho dinheiro, nem pretendo pagar vinte milhões de orens.  </t>
+      <c r="L461" s="32" t="inlineStr">
+        <is>
+          <t>...Ufa, me encontraram fácil, fácil.
+Tanto faz, façam de mim o que quiserem, mas por mais que me xinguem, não tenho dinheiro, nem pretendo pagar vinte milhões de orens.</t>
         </is>
       </c>
     </row>
@@ -8763,9 +8689,9 @@
           <t>How flippant... from someone who should be a proud Frontier Inspector of Mysilia...</t>
         </is>
       </c>
-      <c r="L462" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que insolente... para alguém que deveria ser um orgulhoso Inspetor da Fronteira de Mysilia...  </t>
+      <c r="L462" s="32" t="inlineStr">
+        <is>
+          <t>Que descaramento... vindo de quem deveria ser um orgulhoso Inspetor de Fronteira de Mysilia...</t>
         </is>
       </c>
     </row>
@@ -8783,9 +8709,9 @@
           <t>No, Lady Farris... think about it. As much as I've tarnished the honor of Mysilia, twenty million orens for a single flower is outrageously excessive, isn't it?</t>
         </is>
       </c>
-      <c r="L463" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não, Lady Farris... pense bem. Por mais que eu tenha manchado a honra de Mysilia, vinte milhões de orens por uma única flor é um absurdo, não acha?  </t>
+      <c r="L463" s="32" t="inlineStr">
+        <is>
+          <t>Não, Lady Farris... pense bem. Por mais que eu tenha manchado a honra de Mysilia, vinte milhões de orens por uma única flor é um exagero escandaloso, não é?</t>
         </is>
       </c>
     </row>
@@ -8803,9 +8729,9 @@
           <t>This country is impoverished. But are they trying to squeeze money even from someone as capable as me? My loyalty to Mysilia is wavering.</t>
         </is>
       </c>
-      <c r="L464" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Este país está empobrecido. Mas será que querem arrancar dinheiro até de alguém tão capaz quanto eu? Minha lealdade a Mysilia está vacilante.  </t>
+      <c r="L464" s="32" t="inlineStr">
+        <is>
+          <t>Este país está na pindaíba. Mas querem espremer dinheiro até de alguém tão capaz quanto eu? Minha lealdade a Mysilia está vacilando.</t>
         </is>
       </c>
       <c r="M464" s="32" t="n"/>
@@ -8832,11 +8758,10 @@
 But Lord Loytel, if it's you...</t>
         </is>
       </c>
-      <c r="L465" t="inlineStr">
-        <is>
-          <t xml:space="preserve">As exigências de Mysilia são de fato absurdas. Uma dívida tão grande que poderia comprar uma cidade inteira... Levaria cem anos para pagá-la por meios legítimos.  _x000D_
-_x000D_
-Mas Lorde Loytel, se for você...  </t>
+      <c r="L465" s="32" t="inlineStr">
+        <is>
+          <t>As exigências de Mysilia são realmente absurdas. Uma dívida tão colossal que compraria uma cidade inteira... Levaria cem anos para pagar pelos meios legítimos.
+Mas Lorde Loytel, se for o senhor...</t>
         </is>
       </c>
     </row>
@@ -8854,9 +8779,9 @@
           <t>No, it's impossible, Lady Farris. With the gold of Vernis now a vanished dream, how am I supposed to come up with twenty million orens... I am... I am done for.</t>
         </is>
       </c>
-      <c r="L466" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não, é impossível, Lady Farris. Com o ouro de Vernis agora reduzido a um sonho perdido, como eu deveria conseguir vinte milhões de orens... Eu estou... estou acabado.  </t>
+      <c r="L466" s="32" t="inlineStr">
+        <is>
+          <t>Não, é impossível, Lady Farris. Com o ouro de Vernis virando sonho desfeito, como eu vou juntar vinte milhões de orens... Estou... estou acabado.</t>
         </is>
       </c>
     </row>
@@ -8874,9 +8799,9 @@
           <t>It's over for me...</t>
         </is>
       </c>
-      <c r="L467" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Está tudo perdido para mim...  </t>
+      <c r="L467" s="32" t="inlineStr">
+        <is>
+          <t>Tudo acabado para mim...</t>
         </is>
       </c>
     </row>
@@ -8894,9 +8819,9 @@
           <t>It's all over for me...</t>
         </is>
       </c>
-      <c r="L468" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Está tudo acabado...  </t>
+      <c r="L468" s="32" t="inlineStr">
+        <is>
+          <t>Tudo acabou para mim...</t>
         </is>
       </c>
     </row>
@@ -8919,9 +8844,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L469" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L469" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -8956,9 +8881,9 @@
           <t>That's not true...</t>
         </is>
       </c>
-      <c r="L471" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isso não é verdade...  </t>
+      <c r="L471" s="32" t="inlineStr">
+        <is>
+          <t>Isso não é verdade...</t>
         </is>
       </c>
     </row>
@@ -8981,9 +8906,9 @@
           <t>That's not true, Lord Loytel. I know you're not someone whose story ends here. A debt of twenty million orens is nothing but a pebble in your path.</t>
         </is>
       </c>
-      <c r="L472" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Isso não é verdade, Lorde Loytel. Eu sei que você não é alguém cuja história termina aqui. Uma dívida de vinte milhões de orens não passa de uma pedra no seu caminho.  </t>
+      <c r="L472" s="32" t="inlineStr">
+        <is>
+          <t>Isso não é verdade, Lorde Loytel. Sei que o senhor não é alguém cuja história termina aqui. Uma dívida de vinte milhões de orens não passa de uma pedrinha no seu caminho.</t>
         </is>
       </c>
     </row>
@@ -9001,9 +8926,9 @@
           <t>Lady Farris...</t>
         </is>
       </c>
-      <c r="L473" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Lady Farris...  </t>
+      <c r="L473" s="32" t="inlineStr">
+        <is>
+          <t>Lady Farris...</t>
         </is>
       </c>
     </row>
@@ -9040,11 +8965,10 @@
 Your tale with the Phantom Tulip, I feel a great pulse of 'possibility' and 'hope' there.</t>
         </is>
       </c>
-      <c r="L475" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Ouça, Lorde Loytel.  _x000D_
-_x000D_
-Sua história com a Tulipa Fantasma... eu sinto um grande pulsar de 'possibilidade' e 'esperança' nela.  </t>
+      <c r="L475" s="32" t="inlineStr">
+        <is>
+          <t>...Ouça, Lorde Loytel.
+A história do senhor com a Tulipa Fantasma, sinto um grande pulso de 'possibilidade' e 'esperança' ali.</t>
         </is>
       </c>
     </row>
@@ -9067,9 +8991,9 @@
           <t>Eh...?</t>
         </is>
       </c>
-      <c r="L476" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eh...?  </t>
+      <c r="L476" s="32" t="inlineStr">
+        <is>
+          <t>Hã...?</t>
         </is>
       </c>
     </row>
@@ -9094,11 +9018,10 @@
 And this is just the beginning.</t>
         </is>
       </c>
-      <c r="L477" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Não percebe? Sem a Tulipa Fantasma, você nunca teria ficado no campo... Nunca teríamos encontrado Kettle ou Quruitzia, nem ido a Vernis em busca de ouro, ou encontrado o descendente do Dragão de Aço. Sua Tulipa Azul foi onde muitos destinos se entrelaçaram.  _x000D_
-_x000D_
-E isso é só o começo.  </t>
+      <c r="L477" s="32" t="inlineStr">
+        <is>
+          <t>Não percebe? Sem a Tulipa Fantasma, o senhor nunca teria ficado na campina... Nunca teríamos conhecido Kettle ou Quruitzia, nem ido a Vernis atrás de ouro, nem encontrado o descendente do Dragão de Aço. Sua Tulipa Azul é onde muitos destinos se entrelaçaram.
+E isso é só o começo.</t>
         </is>
       </c>
     </row>
@@ -9125,13 +9048,11 @@
 In the future, people will look back on this era and surely call it 'The Era of the Phantom Azure Tulip'.</t>
         </is>
       </c>
-      <c r="L478" t="inlineStr">
-        <is>
-          <t xml:space="preserve">O lendário Dragão de Aço, a garota predestinada, o alquimista que conhece o nome do vento, e os aventureiros ainda repletos de possibilidades infinitas...  _x000D_
-_x000D_
-Se Mysilia está tão empobrecida assim, então apenas pague os vinte milhões de orens. É um preço insignificante comparado ao destino e às lendas que essas crianças irão criar.  _x000D_
-_x000D_
-No futuro, as pessoas olharão para esta era e, com certeza, a chamarão de 'A Era da Tulipa Azul Fantasma'.  </t>
+      <c r="L478" s="32" t="inlineStr">
+        <is>
+          <t>O lendário Dragão de Aço, a garota do destino, a alquimista que conhece o nome do vento, e os aventureiros ainda transbordando possibilidades infinitas...
+Se Mysilia está tão na pindaíba, então simplesmente paguem os vinte milhões de orens. É um preço trivial perto do destino e das lendas que estas crianças vão tecer.
+No futuro, as pessoas olharão para esta época e certamente a chamarão de 'A Era da Tulipa Azul Fantasma'.</t>
         </is>
       </c>
     </row>
@@ -9149,9 +9070,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L479" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L479" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -9178,13 +9099,11 @@
 Let's work together to repay the debt and save Mysilia!</t>
         </is>
       </c>
-      <c r="L480" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, hehe, aí está a expressão de sempre, Lorde Loytel.  _x000D_
-_x000D_
-Sim, somos "companheiros" unidos pelo destino. Vamos ajudar a continuar a história que você começou.  _x000D_
-_x000D_
-Vamos trabalhar juntos para pagar a dívida e salvar Mysilia!  </t>
+      <c r="L480" s="32" t="inlineStr">
+        <is>
+          <t>Ah, hehe, lá está a cara de sempre, Lorde Loytel.
+Sim, somos "companheiros" atados pelo destino. Deixe-nos ajudar a continuar a história que o senhor começou.
+Vamos trabalhar juntos para pagar a dívida e salvar Mysilia!</t>
         </is>
       </c>
     </row>
@@ -9207,9 +9126,9 @@
           <t>If that's the case, I'm more than happy to help too. I may not be able to transmute gold, but I can create as many tulips as you like.</t>
         </is>
       </c>
-      <c r="L481" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Se for assim, terei o maior prazer em ajudar também. Talvez eu não consiga transmutar ouro, mas posso criar quantas tulipas quiser.  </t>
+      <c r="L481" s="32" t="inlineStr">
+        <is>
+          <t>Se for esse o caso, eu também ajudo com prazer. Não posso transmutar ouro, mas posso criar tantas tulipas quanto quiser.</t>
         </is>
       </c>
     </row>
@@ -9232,9 +9151,9 @@
           <t>Loytel, don't run away anymore. I'll gather rare herbs for you too... right, Corgon?</t>
         </is>
       </c>
-      <c r="L482" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Loytel, não fuja mais. Eu também reunirei ervas raras para você... certo, Corgon?  </t>
+      <c r="L482" s="32" t="inlineStr">
+        <is>
+          <t>Loytel, não fuja mais. Vou colher ervas raras para o senhor também... né, Corgon?</t>
         </is>
       </c>
     </row>
@@ -9257,9 +9176,9 @@
           <t>Mokyu!</t>
         </is>
       </c>
-      <c r="L483" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mokyu!  </t>
+      <c r="L483" s="32" t="inlineStr">
+        <is>
+          <t>Mokyu!</t>
         </is>
       </c>
     </row>
@@ -9277,9 +9196,9 @@
           <t xml:space="preserve">You guys... </t>
         </is>
       </c>
-      <c r="L484" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vocês...  </t>
+      <c r="L484" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vocês... </t>
         </is>
       </c>
     </row>
@@ -9297,9 +9216,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L485" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L485" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -9317,9 +9236,9 @@
           <t>Right, Lady Farris... if you say so, I'll make up my mind. No more moping around in this gloomy wine cellar!</t>
         </is>
       </c>
-      <c r="L486" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Certo, Lady Farris... se é assim que você diz, então eu tomarei minha decisão. Nada mais de lamentações neste porão sombrio!  </t>
+      <c r="L486" s="32" t="inlineStr">
+        <is>
+          <t>Pois é, Lady Farris... se é o que diz, decido. Chega de se lamentar nesta adega sombria!</t>
         </is>
       </c>
     </row>
@@ -9339,11 +9258,10 @@
 Rest assured, I don't intend to burden you or hinder our base's development.</t>
         </is>
       </c>
-      <c r="L487" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Muito bem, entendeu, #pc?  _x000D_
-_x000D_
-Fique tranquilo, não pretendo ser um peso para vocês nem atrapalhar o desenvolvimento da nossa base.  </t>
+      <c r="L487" s="32" t="inlineStr">
+        <is>
+          <t>...Entendeu, #pc?
+Fique tranquilo, não pretendo te sobrecarregar nem atrapalhar o desenvolvimento da base.</t>
         </is>
       </c>
     </row>
@@ -9361,9 +9279,9 @@
           <t>But, um... if you want to help voluntarily... I would gladly accept it. After all, we are companions who have endured hardships together.</t>
         </is>
       </c>
-      <c r="L488" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mas, hum... se quiser ajudar voluntariamente... eu aceitaria com prazer. Afinal, somos companheiros que passaram por tantas dificuldades juntos.  </t>
+      <c r="L488" s="32" t="inlineStr">
+        <is>
+          <t>Mas, hum... se você quiser ajudar por vontade própria... aceitaria de bom grado. Afinal, somos companheiros que já enfrentaram provações juntos.</t>
         </is>
       </c>
     </row>
@@ -9381,9 +9299,9 @@
           <t>...Ahem! I also don't intend to go down without a fight. I'll trace my connections and negotiate with the high officials of Mysilia. Saving a nation in crisis should warrant some "support", right?</t>
         </is>
       </c>
-      <c r="L489" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Ahem! E também não pretendo cair sem lutar. Vou usar minhas conexões e negociar com os altos funcionários de Mysilia. Salvar uma nação em crise deve render algum tipo de 'apoio', não acha?  </t>
+      <c r="L489" s="32" t="inlineStr">
+        <is>
+          <t>...Hem-hem! Também não pretendo afundar sem lutar. Vou acionar meus contatos e negociar com os altos oficiais de Mysilia. Salvar uma nação em crise merece algum "apoio", certo?</t>
         </is>
       </c>
     </row>
@@ -9403,11 +9321,10 @@
 ...Heh, I wonder when I'll get to drink Olvina's wine again?</t>
         </is>
       </c>
-      <c r="L490" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Agora que está decidido, vamos voltar para a base e colocar as mãos na massa.  _x000D_
-_x000D_
-...Heh, me pergunto quando poderei tomar o vinho da Olvina de novo?  </t>
+      <c r="L490" s="32" t="inlineStr">
+        <is>
+          <t>Já que está decidido, voltemos à base e vamos trabalhar.
+...Heh, quando será que poderei beber o vinho de Olvina de novo?</t>
         </is>
       </c>
     </row>
@@ -9459,13 +9376,11 @@
 It’s not much, but take this ‘shoulder massage ticket’ as a token of my gratitude.</t>
         </is>
       </c>
-      <c r="L498" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Oh, você já conseguiu pagar parte da dívida!  _x000D_
-_x000D_
-Uma longa jornada de vinte milhões de orens, e demos o primeiro passo. Eu realmente agradeço.  _x000D_
-_x000D_
-Não é muito, mas aceite este ‘vale para massagem nos ombros’ como um sinal da minha gratidão.  </t>
+      <c r="L498" s="32" t="inlineStr">
+        <is>
+          <t>Oh, você já conseguiu pagar uma parte da dívida!
+Uma jornada de vinte milhões de orens, e demos o primeiro passo. Fico realmente grato.
+Não é muita coisa, mas tome este 'vale massagem nos ombros' em agradecimento.</t>
         </is>
       </c>
     </row>
@@ -9487,13 +9402,11 @@
 Well, I’ll have something else ready for next time.</t>
         </is>
       </c>
-      <c r="L499" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh...  _x000D_
-_x000D_
-Não me olhe assim. Eu sei que parece um pouco infantil, mas quando perguntei à Lady Farris o que poderia oferecer, ela recomendou isso. Como eu poderia recusar?  _x000D_
-_x000D_
-Bem, terei algo diferente preparado para a próxima vez.  </t>
+      <c r="L499" s="32" t="inlineStr">
+        <is>
+          <t>Heh...
+Não faça essa cara. Sei que parece um pouco infantil, mas quando consultei a Lady Farris sobre o que poderia oferecer, ela recomendou isto. Como recusar?
+Bom, vou ter outra coisa pronta na próxima.</t>
         </is>
       </c>
     </row>
@@ -9539,11 +9452,10 @@
 It’s not much, but here, take this 'one hour arm pillow ticket'.</t>
         </is>
       </c>
-      <c r="L506" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pagou mais uma parte da dívida. Eu realmente aprecio isso.  _x000D_
-_x000D_
-Não é muito, mas aqui, aceite este 'vale para travesseiro de braço por uma hora'.  </t>
+      <c r="L506" s="32" t="inlineStr">
+        <is>
+          <t>Você pagou mais uma parte da dívida. Fico realmente grato.
+Não é muita coisa, mas tome este 'vale almofada de braço por uma hora'.</t>
         </is>
       </c>
     </row>
@@ -9561,9 +9473,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L507" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L507" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -9585,13 +9497,11 @@
 Anyway... I’ll have something else ready for next time. So, look forward to it.</t>
         </is>
       </c>
-      <c r="L508" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, claro, foi um pedido da Lady Farris.  _x000D_
-_x000D_
-Ela é uma mulher sábia, mas às vezes, eu realmente não faço ideia do que se passa na cabeça dela.  _x000D_
-_x000D_
-De qualquer forma... terei algo diferente preparado para a próxima vez. Então, aguarde ansioso.  </t>
+      <c r="L508" s="32" t="inlineStr">
+        <is>
+          <t>Sim, claro, foi pedido da Lady Farris.
+É uma mulher sábia, mas às vezes não faço ideia do que passa pela cabeça dela.
+Enfim... terei outra coisa pronta na próxima. Fique no aguardo.</t>
         </is>
       </c>
     </row>
@@ -9638,11 +9548,10 @@
 Here, take this ‘champagne call ticket’.</t>
         </is>
       </c>
-      <c r="L513" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Vejo que mais uma parte da dívida foi paga. Obrigado.  _x000D_
-_x000D_
-Aqui, aceite este 'vale para brinde com champanhe'.  </t>
+      <c r="L513" s="32" t="inlineStr">
+        <is>
+          <t>Mais uma parte da dívida paga, vejo. Obrigado.
+Tome, este 'vale chamado do champanhe'.</t>
         </is>
       </c>
     </row>
@@ -9660,9 +9569,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L514" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L514" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -9682,11 +9591,10 @@
 Well... I'll have something ready next time.</t>
         </is>
       </c>
-      <c r="L515" t="inlineStr">
-        <is>
-          <t xml:space="preserve">De acordo com Lady Farris, recitar este cântico antigo e estranho supostamente eleva o ânimo de quem está ao redor. O que será que ela está pensando?  _x000D_
-_x000D_
-Bem... terei algo preparado para a próxima vez.  </t>
+      <c r="L515" s="32" t="inlineStr">
+        <is>
+          <t>Segundo a Lady Farris, recitar esta cantiga antiga e esquisita serve para animar quem está por perto. O que será que ela anda pensando?
+Bom... terei algo pronto na próxima.</t>
         </is>
       </c>
     </row>
@@ -9735,13 +9643,11 @@
 Anyway, here’s something more fitting—this ‘resident ticket’.</t>
         </is>
       </c>
-      <c r="L520" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pagou mais uma parte da dívida. Eu realmente aprecio isso.  _x000D_
-_x000D_
-Heh... não se preocupe. Lady Farris sugeriu um 'vale para ser carregado nos braços como uma princesa', mas eu educadamente recusei. Ela ficou bastante desapontada com isso, então estou um pouco preocupado.  _x000D_
-_x000D_
-De qualquer forma, aqui está algo mais apropriado—este 'vale de residente'.  </t>
+      <c r="L520" s="32" t="inlineStr">
+        <is>
+          <t>Você pagou mais uma parte da dívida. Fico realmente grato.
+Heh... não se preocupe. A Lady Farris sugeriu um 'vale carregadinha no colo', mas recusei educadamente. Ela pareceu bem abalada com a recusa, o que me deixa meio preocupado.
+Enfim, aqui vai algo mais adequado: este 'vale morador'.</t>
         </is>
       </c>
     </row>
@@ -9763,13 +9669,11 @@
 So, look forward to next time!</t>
         </is>
       </c>
-      <c r="L521" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Sempre me impressiono com sua determinação e esforço. O pagamento da dívida está indo bem, graças a você.  _x000D_
-_x000D_
-Não posso depender para sempre das ideias da Lady Farris. Pensarei em algo por conta própria para retribuir seus esforços da maneira adequada.  _x000D_
-_x000D_
-Então, aguarde ansioso pela próxima vez!  </t>
+      <c r="L521" s="32" t="inlineStr">
+        <is>
+          <t>Sua determinação e seu fôlego sempre me surpreendem. O pagamento da dívida está correndo bem, graças a você.
+Não posso depender para sempre das ideias da Lady Farris. Vou pensar em algo por conta própria para retribuir seus esforços direito.
+Então, fique no aguardo da próxima!</t>
         </is>
       </c>
     </row>
@@ -9826,11 +9730,10 @@
 ...I once had a small dream.</t>
         </is>
       </c>
-      <c r="L527" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Escute, #pc.  _x000D_
-_x000D_
-...Eu já tive um pequeno sonho.  </t>
+      <c r="L527" s="32" t="inlineStr">
+        <is>
+          <t>Ouça, #pc.
+...Eu já tive um pequeno sonho.</t>
         </is>
       </c>
     </row>
@@ -9856,13 +9759,11 @@
 Of course, with all this debt trouble, I’d already given up on that dream.</t>
         </is>
       </c>
-      <c r="L529" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eu sempre planejei dedicar meu coração e minha alma aos negócios da fronteira e, quando cumprisse todos os meus deveres, pretendia abrir uma pequena loja para aproveitar meus últimos anos.  _x000D_
-_x000D_
-Não precisava ser um lugar movimentado. Eu apenas imaginava segurar uma taça de vinho Olvina à tarde, conversar com os colonos e admirar a terra que eu mesmo havia conquistado, tudo isso da frente da minha loja... um sonho simples e encantador.  _x000D_
-_x000D_
-Mas, é claro, com toda essa confusão de dívidas, já tinha desistido desse sonho.  </t>
+      <c r="L529" s="32" t="inlineStr">
+        <is>
+          <t>Sempre planejei entregar corpo e alma aos negócios da fronteira e, uma vez cumpridas todas as minhas funções, abrir uma lojinha para desfrutar a terceira idade.
+Não precisava ferver de clientes. Só imaginava tomar um vinho de Olvina à tarde, papear com os colonos e contemplar, da frente da minha loja, a terra que eu mesmo havia aberto... um sonho humilde e charmoso.
+Claro, com toda essa bagunça de dívida, já tinha desistido desse sonho.</t>
         </is>
       </c>
     </row>
@@ -9899,13 +9800,11 @@
 So, I’ve made up my mind, #pc. I’m going to open my store right here—‘Loytel Mart!’</t>
         </is>
       </c>
-      <c r="L532" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mas ao ver o quanto você tem se esforçado... isso reacendeu uma chama em mim.  _x000D_
-_x000D_
-Deveria mesmo desistir do meu pequeno sonho só por causa de uma dívida? Não, eu não posso.  _x000D_
-_x000D_
-Então, tomei minha decisão, #pc. Vou abrir minha loja bem aqui—‘Loytel Mart!’  </t>
+      <c r="L532" s="32" t="inlineStr">
+        <is>
+          <t>Mas vendo o quanto você vem se esforçando... reacendeu um fogo em mim.
+Será que devo mesmo abandonar meu pequeno sonho por causa de uma dívida? Não, não dá.
+Então decidi, #pc. Vou abrir minha loja bem aqui: 'Loytel Mart!'</t>
         </is>
       </c>
     </row>
@@ -9925,11 +9824,10 @@
 With this wagon, you’ll always have access to my shop.</t>
         </is>
       </c>
-      <c r="L533" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Aqui, pegue esta carroça especialmente feita. Trabalhei nela em segredo durante meu tempo livre.  _x000D_
-_x000D_
-Com essa carroça, você sempre terá acesso à minha loja.  </t>
+      <c r="L533" s="32" t="inlineStr">
+        <is>
+          <t>Toma, leve esta carroça especialmente fabricada que eu construía às escondidas nas horas vagas.
+Com ela, você sempre terá acesso à minha loja.</t>
         </is>
       </c>
     </row>
@@ -9949,11 +9847,10 @@
 So, when you return from your adventures, be sure to drop by Loytel Mart.</t>
         </is>
       </c>
-      <c r="L534" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ainda não tenho muito estoque, mas pretendo expandir minha seleção.  _x000D_
-_x000D_
-Então, quando voltar de suas aventuras, não deixe de passar na Loytel Mart.  </t>
+      <c r="L534" s="32" t="inlineStr">
+        <is>
+          <t>Ainda não há muito em estoque, mas pretendo ampliar a seleção.
+Então, quando voltar das suas aventuras, não deixe de passar no Loytel Mart.</t>
         </is>
       </c>
     </row>
@@ -10002,13 +9899,11 @@
 As the top taxpayer in Mysilia, I intend to negotiate to secure some aid for us.</t>
         </is>
       </c>
-      <c r="L539" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Você pagou mais uma parte da dívida. Eu realmente aprecio isso.  _x000D_
-_x000D_
-Tenho certeza de que Mysilia também se beneficiou bastante. Acabei de receber uma mensagem de um alto funcionário do governo que deseja falar comigo diretamente.  _x000D_
-_x000D_
-Como o maior contribuinte de impostos de Mysilia, pretendo negociar para garantir alguma ajuda para nós.  </t>
+      <c r="L539" s="32" t="inlineStr">
+        <is>
+          <t>Você pagou mais uma parte da dívida. Fico realmente grato.
+Tenho certeza de que Mysilia também lucrou com isso. Neste exato momento, recebi o comunicado de um alto oficial do governo que deseja falar comigo diretamente.
+Como maior contribuinte de Mysilia, pretendo negociar para garantir alguma ajuda para nós.</t>
         </is>
       </c>
     </row>
@@ -10030,13 +9925,11 @@
 We might not have rare finds every time, but this should improve our inventory a bit.</t>
         </is>
       </c>
-      <c r="L540" t="inlineStr">
-        <is>
-          <t xml:space="preserve">A propósito, o que está achando da minha loja?  _x000D_
-_x000D_
-Pedi para Kettle e Quruitzia trazerem qualquer item útil que encontrarem.  _x000D_
-_x000D_
-Talvez não tenhamos achados raros o tempo todo, mas isso deve melhorar um pouco nosso estoque.  </t>
+      <c r="L540" s="32" t="inlineStr">
+        <is>
+          <t>Aliás, o que está achando da minha loja?
+Pedi a Kettle e Quruitzia que tragam itens úteis que encontrarem por aí.
+Talvez não venham achados raros toda vez, mas isso já melhora um pouco nosso estoque.</t>
         </is>
       </c>
     </row>
@@ -10056,11 +9949,10 @@
 My handiwork has its limits, but eventually, It will be nice to have some flashy upgrades.</t>
         </is>
       </c>
-      <c r="L541" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Também expandi um pouco a carroça da Loytel Mart.  _x000D_
-_x000D_
-Minhas habilidades têm seus limites, mas, eventualmente, será bom fazer algumas melhorias chamativas.  </t>
+      <c r="L541" s="32" t="inlineStr">
+        <is>
+          <t>Também ampliei um pouco a carroça do Loytel Mart.
+Meu artesanato tem seus limites, mas, com o tempo, será bom ter melhorias mais vistosas.</t>
         </is>
       </c>
     </row>
@@ -10107,10 +9999,10 @@
 ...You say I look troubled? Well, the truth is, I had a meeting with a high-ranking official from Mysilia while you were away.</t>
         </is>
       </c>
-      <c r="L546" t="inlineStr">
-        <is>
-          <t>Ah, sim... é você, #pc. Parece que fez outro pagamento. Sou grato.
-...Diz que pareço preocupado? Bem, a verdade é que tive uma reunião com um oficial de alto escalão de Mysilia enquanto você estava fora.</t>
+      <c r="L546" s="32" t="inlineStr">
+        <is>
+          <t>Ah, sim... é você, #pc. Parece que fez mais um pagamento. Fico grato.
+...Disse que estou com cara de preocupado? Pois é, a verdade é que tive uma reunião com um alto oficial de Mysilia enquanto você estava fora.</t>
         </is>
       </c>
     </row>
@@ -10132,9 +10024,9 @@
           <t>Even if it was a false charge, I’m still technically a criminal under Mysilian law, so I expected a solemn and formal audience...</t>
         </is>
       </c>
-      <c r="L547" t="inlineStr">
-        <is>
-          <t>Mesmo que fosse uma acusação falsa, ainda sou tecnicamente um criminoso sob a lei Mysiliana, então esperava uma audiência solene e formal...</t>
+      <c r="L547" s="32" t="inlineStr">
+        <is>
+          <t>Ainda que fosse uma acusação falsa, legalmente sou um criminoso perante a lei de Mysilia, então esperava uma audiência solene e formal...</t>
         </is>
       </c>
     </row>
@@ -10223,7 +10115,7 @@
           <t>- A room in the Mysilian court -</t>
         </is>
       </c>
-      <c r="L553" t="inlineStr">
+      <c r="L553" s="32" t="inlineStr">
         <is>
           <t>- Uma sala na corte de Mysilia -</t>
         </is>
@@ -10252,7 +10144,7 @@
           <t>Hey, you're late, Loytel. We already got started.</t>
         </is>
       </c>
-      <c r="L555" t="inlineStr">
+      <c r="L555" s="32" t="inlineStr">
         <is>
           <t>Ei, você está atrasado, Loytel. Já começamos.</t>
         </is>
@@ -10291,9 +10183,9 @@
           <t>Eeeeek!</t>
         </is>
       </c>
-      <c r="L557" t="inlineStr">
-        <is>
-          <t>Eeeeek!</t>
+      <c r="L557" s="32" t="inlineStr">
+        <is>
+          <t>Hiieee!</t>
         </is>
       </c>
     </row>
@@ -10316,7 +10208,7 @@
           <t>It’s been a while, Loytel.</t>
         </is>
       </c>
-      <c r="L558" t="inlineStr">
+      <c r="L558" s="32" t="inlineStr">
         <is>
           <t>Faz tempo, Loytel.</t>
         </is>
@@ -10341,7 +10233,7 @@
           <t>Hooo!</t>
         </is>
       </c>
-      <c r="L559" t="inlineStr">
+      <c r="L559" s="32" t="inlineStr">
         <is>
           <t>Hooo!</t>
         </is>
@@ -10361,9 +10253,9 @@
           <t>W–What are you all doing here?</t>
         </is>
       </c>
-      <c r="L560" t="inlineStr">
-        <is>
-          <t>O–O que vocês estão fazendo aqui?</t>
+      <c r="L560" s="32" t="inlineStr">
+        <is>
+          <t>O-O que vocês estão fazendo aqui?</t>
         </is>
       </c>
     </row>
@@ -10386,9 +10278,9 @@
           <t>What do you think? It’s a party! A table full of food, fine booze, and beautiful women!</t>
         </is>
       </c>
-      <c r="L561" t="inlineStr">
-        <is>
-          <t>O que acha? É uma festa! Uma mesa cheia de comida, bebida fina e mulheres lindas!</t>
+      <c r="L561" s="32" t="inlineStr">
+        <is>
+          <t>O que acha? É uma festa! Uma mesa cheia de comida, bebida boa e mulheres belas!</t>
         </is>
       </c>
     </row>
@@ -10425,9 +10317,9 @@
           <t xml:space="preserve">Oh my, Lord Barrich, you're so naughty! </t>
         </is>
       </c>
-      <c r="L563" t="inlineStr">
-        <is>
-          <t>Ai, meu Deus, Lorde Barrich, você é tão safado!</t>
+      <c r="L563" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ah, Lorde Barrich, que maroto o senhor é! </t>
         </is>
       </c>
     </row>
@@ -10450,9 +10342,9 @@
           <t>You’re drinking way too much, Barrich. Your sister warned me to keep an eye on you.</t>
         </is>
       </c>
-      <c r="L564" t="inlineStr">
-        <is>
-          <t>Você está bebendo demais, Barrich. Sua irmã me pediu para ficar de olho em você.</t>
+      <c r="L564" s="32" t="inlineStr">
+        <is>
+          <t>Está bebendo demais, Barrich. Sua irmã me mandou ficar de olho em você.</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10362,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L565" t="inlineStr">
+      <c r="L565" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -10490,9 +10382,9 @@
           <t>I was told there’d be an important meeting with a Mysilian official. But it seems I’ve entered the wrong room. Pardon me.</t>
         </is>
       </c>
-      <c r="L566" t="inlineStr">
-        <is>
-          <t>Fui informado de que haveria uma reunião importante com um oficial Mysiliano. Mas parece que entrei na sala errada. Com licença.</t>
+      <c r="L566" s="32" t="inlineStr">
+        <is>
+          <t>Disseram que haveria uma reunião importante com um oficial de Mysilia. Mas parece que entrei na sala errada. Com licença.</t>
         </is>
       </c>
     </row>
@@ -10515,9 +10407,9 @@
           <t>Still so uptight, huh? It’s been ages—why not relax and sit next to this lovely lady?</t>
         </is>
       </c>
-      <c r="L567" t="inlineStr">
-        <is>
-          <t>Ainda tão tenso, hein? Faz séculos... por que não relaxa e senta ao lado desta linda dama?</t>
+      <c r="L567" s="32" t="inlineStr">
+        <is>
+          <t>Ainda tão amarrado, hein? Faz uma eternidade: que tal relaxar e sentar ao lado desta bela dama?</t>
         </is>
       </c>
     </row>
@@ -10540,9 +10432,9 @@
           <t>Ahem!</t>
         </is>
       </c>
-      <c r="L568" t="inlineStr">
-        <is>
-          <t>Ahem!</t>
+      <c r="L568" s="32" t="inlineStr">
+        <is>
+          <t>Hem-hem!</t>
         </is>
       </c>
     </row>
@@ -10580,9 +10472,9 @@
           <t>Eeeeek!</t>
         </is>
       </c>
-      <c r="L570" t="inlineStr">
-        <is>
-          <t>Eeeeek!</t>
+      <c r="L570" s="32" t="inlineStr">
+        <is>
+          <t>Hiieee!</t>
         </is>
       </c>
     </row>
@@ -10600,9 +10492,9 @@
           <t>L–Lord Caldorn...?</t>
         </is>
       </c>
-      <c r="L571" t="inlineStr">
-        <is>
-          <t>L–Lorde Caldorn...?</t>
+      <c r="L571" s="32" t="inlineStr">
+        <is>
+          <t>L-Lorde Caldorn...?</t>
         </is>
       </c>
     </row>
@@ -10620,9 +10512,9 @@
           <t>You fools! How dare you summon a Mysilian dignitary to such a disgraceful gathering!</t>
         </is>
       </c>
-      <c r="L572" t="inlineStr">
-        <is>
-          <t>Seus tolos! Como ousam convocar um dignitário Mysiliano para uma reunião tão vergonhosa!</t>
+      <c r="L572" s="32" t="inlineStr">
+        <is>
+          <t>Seus tolos! Como ousam convocar um dignatário de Mysilia para uma reunião tão vergonhosa!</t>
         </is>
       </c>
     </row>
@@ -10647,10 +10539,10 @@
 I left the arrangements to young Barrich here, and this is what I walked into. Well, have a seat.</t>
         </is>
       </c>
-      <c r="L573" t="inlineStr">
-        <is>
-          <t>Espere aí, Loytel. O oficial que você veio encontrar... sou eu.
-Deixei os preparativos com o jovem Barrich aqui, e foi isso que encontrei. Bem, sente-se.</t>
+      <c r="L573" s="32" t="inlineStr">
+        <is>
+          <t>Calma aí, Loytel. O oficial com quem você vai se encontrar... sou eu.
+Deixei os preparos com o jovem Barrich aqui, e foi isso que encontrei. Sente-se, vamos.</t>
         </is>
       </c>
     </row>
@@ -10668,9 +10560,9 @@
           <t>Yes, if Your Excellency insists, I shall comply.</t>
         </is>
       </c>
-      <c r="L574" t="inlineStr">
-        <is>
-          <t>Sim, se Vossa Excelência insiste, obedecerei.</t>
+      <c r="L574" s="32" t="inlineStr">
+        <is>
+          <t>Sim, se Sua Excelência insiste, assim farei.</t>
         </is>
       </c>
     </row>
@@ -10693,9 +10585,9 @@
           <t>Good.</t>
         </is>
       </c>
-      <c r="L575" t="inlineStr">
-        <is>
-          <t>Bom.</t>
+      <c r="L575" s="32" t="inlineStr">
+        <is>
+          <t>Ótimo.</t>
         </is>
       </c>
     </row>
@@ -10718,9 +10610,9 @@
           <t>It’s been some time since you last visited the Mysilian capital. We've prepared wine from Olvina—relax and enjoy yourself tonight.</t>
         </is>
       </c>
-      <c r="L576" t="inlineStr">
-        <is>
-          <t>Faz algum tempo desde sua última visita à capital Mysiliana. Preparamos vinho de Olvina... relaxe e aproveite esta noite.</t>
+      <c r="L576" s="32" t="inlineStr">
+        <is>
+          <t>Faz tempo que você não visita a capital de Mysilia. Preparamos vinho de Olvina: relaxe e aproveite a noite.</t>
         </is>
       </c>
     </row>
@@ -10738,7 +10630,7 @@
           <t>Y-Yes.</t>
         </is>
       </c>
-      <c r="L577" t="inlineStr">
+      <c r="L577" s="32" t="inlineStr">
         <is>
           <t>S-Sim.</t>
         </is>
@@ -10763,9 +10655,9 @@
           <t>What’s wrong? I thought you couldn’t resist Olvina wine.</t>
         </is>
       </c>
-      <c r="L578" t="inlineStr">
-        <is>
-          <t>O que foi? Achei que não resistia ao vinho de Olvina.</t>
+      <c r="L578" s="32" t="inlineStr">
+        <is>
+          <t>Que é isso? Pensei que você não resistisse ao vinho de Olvina.</t>
         </is>
       </c>
     </row>
@@ -10783,9 +10675,9 @@
           <t>Well... this feels more like I’m being entertained. But am I not still a criminal in the eyes of Mysilia?</t>
         </is>
       </c>
-      <c r="L579" t="inlineStr">
-        <is>
-          <t>Bem... parece mais que estou sendo entretido. Mas não sou ainda um criminoso aos olhos de Mysilia?</t>
+      <c r="L579" s="32" t="inlineStr">
+        <is>
+          <t>É que... isso parece mais uma desforra de anfitrião. Mas eu ainda não sou um criminoso aos olhos de Mysilia?</t>
         </is>
       </c>
     </row>
@@ -10808,9 +10700,9 @@
           <t>A criminal, hmm… Yes, well...</t>
         </is>
       </c>
-      <c r="L580" t="inlineStr">
-        <is>
-          <t>Um criminoso, hmm... Sim, bem...</t>
+      <c r="L580" s="32" t="inlineStr">
+        <is>
+          <t>Um criminoso, hum... Sim, bem...</t>
         </is>
       </c>
     </row>
@@ -10828,7 +10720,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L581" t="inlineStr">
+      <c r="L581" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -10860,10 +10752,10 @@
 That... what did you call that flower of yours? The phantom... ah yes, your phantom azure tul—pffft! </t>
         </is>
       </c>
-      <c r="L583" t="inlineStr">
-        <is>
-          <t>Sinto muito pela desgraça que lhe aconteceu. Quem poderia prever tamanha tragédia?
-Aquela... como você chamou aquela sua flor? A fanto... ah, sim, seu fantasma de tulipa azul-celeste... pffft!</t>
+      <c r="L583" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Sinto verdadeiramente a desgraça que te alcançou. Quem poderia prever tal tragédia?
+Aquilo... como você chamava a sua flor? A fantasma... ah sim, sua tulipa azul fantasma—pffft! </t>
         </is>
       </c>
     </row>
@@ -10881,7 +10773,7 @@
           <t>Lord Caldorn!?</t>
         </is>
       </c>
-      <c r="L584" t="inlineStr">
+      <c r="L584" s="32" t="inlineStr">
         <is>
           <t>Lorde Caldorn!?</t>
         </is>
@@ -10908,10 +10800,10 @@
 Of course, it’s no laughing matter. Because of that flower, Mysilia almost lost a rare talent like yourself.</t>
         </is>
       </c>
-      <c r="L585" t="inlineStr">
-        <is>
-          <t>M–Minhas desculpas, perdi a compostura por um momento.
-Claro, não é motivo para risos. Por causa daquela flor, Mysilia quase perdeu um talento raro como você.</t>
+      <c r="L585" s="32" t="inlineStr">
+        <is>
+          <t>M-Minhas desculpas, perdi a compostura por um momento.
+Claro, não é piada. Por causa daquela flor, Mysilia quase perdeu um talento raro como você.</t>
         </is>
       </c>
     </row>
@@ -10930,9 +10822,9 @@
           <t>Your words honor me more than I deserve. I never imagined Your Excellency held me in such esteem.</t>
         </is>
       </c>
-      <c r="L586" t="inlineStr">
-        <is>
-          <t>Suas palavras me honram mais do que mereço. Nunca imaginei que Vossa Excelência me tivesse em tão alta estima.</t>
+      <c r="L586" s="32" t="inlineStr">
+        <is>
+          <t>Suas palavras me honram mais do que mereço. Nunca imaginei que Sua Excelência me estimasse tanto.</t>
         </is>
       </c>
     </row>
@@ -10956,10 +10848,10 @@
 In fact, your recent debt incident has only raised your profile within Mysilia. </t>
         </is>
       </c>
-      <c r="L587" t="inlineStr">
-        <is>
-          <t>De fato. Não há uma alma nesta nação que duvide do seu talento.
-Na verdade, seu recente incidente com a dívida só aumentou sua reputação em Mysilia.</t>
+      <c r="L587" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">De fato. Não há alma nesta nação que duvide do seu talento.
+Na verdade, o recente incidente da dívida só aumentou sua fama dentro de Mysilia. </t>
         </is>
       </c>
     </row>
@@ -10984,10 +10876,10 @@
 Someone like Barrich here would’ve just torn up the letter and returned to court like nothing happened. </t>
         </is>
       </c>
-      <c r="L588" t="inlineStr">
-        <is>
-          <t>Vinte milhões de Orens... uma quantia absurda, completamente absurda... e ainda assim, está determinado a pagá-la. Sua sinceridade é louvável.
-Alguém como Barrich aqui teria simplesmente rasgado a carta e voltado à corte como se nada tivesse acontecido.</t>
+      <c r="L588" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vinte milhões de orens: um valor absurdo, completamente absurdo... e ainda assim você está determinado a pagar. Sua sinceridade é louvável.
+Alguém como o Barrich aqui teria rasgado a carta e voltado para a corte como se nada tivesse acontecido. </t>
         </is>
       </c>
     </row>
@@ -11006,7 +10898,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L589" t="inlineStr">
+      <c r="L589" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -11031,9 +10923,9 @@
           <t>You didn’t doubt that letter for even a second, did you?</t>
         </is>
       </c>
-      <c r="L590" t="inlineStr">
-        <is>
-          <t>Você não duvidou daquela carta nem por um segundo, não é?</t>
+      <c r="L590" s="32" t="inlineStr">
+        <is>
+          <t>Você não duvidou daquela carta nem por um segundo, não foi?</t>
         </is>
       </c>
     </row>
@@ -11052,7 +10944,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L591" t="inlineStr">
+      <c r="L591" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -11073,7 +10965,7 @@
           <t>Huh?</t>
         </is>
       </c>
-      <c r="L592" t="inlineStr">
+      <c r="L592" s="32" t="inlineStr">
         <is>
           <t>Hã?</t>
         </is>
@@ -11102,11 +10994,11 @@
 Come, ladies! Pour some wine for Mysilia’s finest! Tonight, we cast off all formalities! </t>
         </is>
       </c>
-      <c r="L593" t="inlineStr">
-        <is>
-          <t>Ah, não importa. Esqueça, Loytel.
-Há muito que gostaria de discutir... sobre o futuro de Mysilia e seu lugar nele. Mas esta noite é o seu banquete.
-Venham, damas! Sirvam vinho para o melhor de Mysilia! Hoje, deixamos de lado todas as formalidades!</t>
+      <c r="L593" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ah, deixa isso. Esquece, Loytel.
+Há muito que gostaria de discutir: sobre o futuro de Mysilia, e o seu lugar nele. Mas esta noite é o seu banquete.
+Venham, moças! Sirvam vinho ao melhor de Mysilia! Esta noite, descartamos toda formalidade! </t>
         </is>
       </c>
     </row>
@@ -11144,9 +11036,9 @@
           <t>Eeeeek!</t>
         </is>
       </c>
-      <c r="L595" t="inlineStr">
-        <is>
-          <t>Eeeeek!</t>
+      <c r="L595" s="32" t="inlineStr">
+        <is>
+          <t>Hiieee!</t>
         </is>
       </c>
     </row>
@@ -11238,7 +11130,7 @@
           <t>...And that’s what happened.</t>
         </is>
       </c>
-      <c r="L605" t="inlineStr">
+      <c r="L605" s="32" t="inlineStr">
         <is>
           <t>...E foi isso que aconteceu.</t>
         </is>
@@ -11263,7 +11155,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L606" t="inlineStr">
+      <c r="L606" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -11287,11 +11179,11 @@
 I have no idea what’ll show up, but I’ll stock it at Loytel Mart. Check in when you’ve got the time. </t>
         </is>
       </c>
-      <c r="L607" t="inlineStr">
-        <is>
-          <t>E–Espera! Admito, foi um encontro bem confuso, mas não fiquei só babando por vinho de Olvina o tempo todo. Enquanto Lorde Caldorn estava apagado de bêbado, consegui garantir uma promessa de apoio.
-Ele concordou em nos passar alguns itens do arsenal Mysiliano que podem ser úteis.
-Não faço ideia do que vai aparecer, mas vou estocar no Loytel Mart. Dê uma passada quando tiver tempo.</t>
+      <c r="L607" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-Espera! Confesso que foi uma reunião bem confusa, mas não fiquei todo o tempo bajulando o vinho de Olvina. Enquanto o Lorde Caldorn dormia bêbado, consegui garantir uma promessa de apoio.
+Ele concordou em nos passar alguns itens do arsenal de Mysilia que podem ser úteis.
+Não faço ideia do que vai aparecer, mas vou estocar no Loytel Mart. Dá uma passada quando tiver tempo. </t>
         </is>
       </c>
     </row>
@@ -11440,9 +11332,9 @@
           <t>What is this chill down my spine I've been feeling...</t>
         </is>
       </c>
-      <c r="L623" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Que é esse arrepio na minha espinha que estou sentindo...?  </t>
+      <c r="L623" s="32" t="inlineStr">
+        <is>
+          <t>Que arrepio na espinha é esse que tenho sentido...</t>
         </is>
       </c>
     </row>
@@ -11466,9 +11358,9 @@
           <t>Heh heh heh...</t>
         </is>
       </c>
-      <c r="L624" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh...  </t>
+      <c r="L624" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh...</t>
         </is>
       </c>
     </row>
@@ -11487,9 +11379,9 @@
           <t xml:space="preserve">Th-This voice... could it be...? </t>
         </is>
       </c>
-      <c r="L625" t="inlineStr">
-        <is>
-          <t xml:space="preserve">E-Essa voz... poderia ser...?  </t>
+      <c r="L625" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">E-Essa voz... será que...? </t>
         </is>
       </c>
     </row>
@@ -11513,9 +11405,9 @@
           <t>Heh heh heh heh...</t>
         </is>
       </c>
-      <c r="L626" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh heh...  </t>
+      <c r="L626" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh heh...</t>
         </is>
       </c>
     </row>
@@ -11534,9 +11426,9 @@
           <t>Show yourself, Demitas!</t>
         </is>
       </c>
-      <c r="L627" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mostre-se, Demitas!  </t>
+      <c r="L627" s="32" t="inlineStr">
+        <is>
+          <t>Mostre-se, Demitas!</t>
         </is>
       </c>
     </row>
@@ -11592,9 +11484,9 @@
           <t>Heh heh heh...</t>
         </is>
       </c>
-      <c r="L630" t="inlineStr">
-        <is>
-          <t>Heh heh heh…</t>
+      <c r="L630" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh...</t>
         </is>
       </c>
     </row>
@@ -11629,9 +11521,9 @@
           <t xml:space="preserve">Eh, Lady Farris? What are you doing...? </t>
         </is>
       </c>
-      <c r="L632" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Eh, Lady Farris? O que você está fazendo...?  </t>
+      <c r="L632" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Hã, Lady Farris? O que você está fazendo...? </t>
         </is>
       </c>
     </row>
@@ -11655,9 +11547,9 @@
           <t>O, daughter of calamity... Thou shalt bringeth ruin upon this world...</t>
         </is>
       </c>
-      <c r="L633" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ó, filha da calamidade... Tu trarás a ruína a este mundo...  </t>
+      <c r="L633" s="32" t="inlineStr">
+        <is>
+          <t>Ó, filha da calamidade... Trazeste a ruína sobre este mundo...</t>
         </is>
       </c>
     </row>
@@ -11677,9 +11569,9 @@
           <t xml:space="preserve">...B-Bwahahaha! Why are you mimicking him? But, you nailed it, Lady Farris! </t>
         </is>
       </c>
-      <c r="L634" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...B-Bwahahaha! Por que você está imitando ele? Mas, mandou bem, Lady Farris!  </t>
+      <c r="L634" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">...B-Buahahaha! Por que você está imitando ele? Mas que impecável, Lady Farris! </t>
         </is>
       </c>
     </row>
@@ -11705,9 +11597,9 @@
           <t>...It seemeth I am still too young to knoweth eternal suffering, 'Kettle.'"</t>
         </is>
       </c>
-      <c r="L635" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Parece que ainda sou jovem demais para conhecer o sofrimento eterno, ‘Kettle.’"  </t>
+      <c r="L635" s="32" t="inlineStr">
+        <is>
+          <t>...Parece que ainda sou jovem demais para conhecer o sofrimento eterno, 'Kettle.'"</t>
         </is>
       </c>
     </row>
@@ -11727,9 +11619,9 @@
           <t xml:space="preserve">Bwahahaha!! Please stop, Lady Farris, my stomach hurts! </t>
         </is>
       </c>
-      <c r="L636" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bwahahaha!! Por favor, pare, Lady Farris, minha barriga está doendo!  </t>
+      <c r="L636" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Buahahaha!! Pelo amor, Lady Farris, minha barriga dói! </t>
         </is>
       </c>
     </row>
@@ -11759,9 +11651,9 @@
           <t>Well... dost thou findeth mirth in this?</t>
         </is>
       </c>
-      <c r="L638" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Bem... achas graça nisso?  </t>
+      <c r="L638" s="32" t="inlineStr">
+        <is>
+          <t>Bom... achais graça nisso?</t>
         </is>
       </c>
     </row>
@@ -11785,9 +11677,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L639" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L639" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -11811,9 +11703,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L640" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L640" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -11837,9 +11729,9 @@
           <t>Heh heh heh... What meaneth this...?</t>
         </is>
       </c>
-      <c r="L641" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh... O que significa isso...?  </t>
+      <c r="L641" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh... Que significa isso...?</t>
         </is>
       </c>
     </row>
@@ -11863,9 +11755,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L642" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L642" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -11889,9 +11781,9 @@
           <t>Heh heh heh...</t>
         </is>
       </c>
-      <c r="L643" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Heh heh heh...  </t>
+      <c r="L643" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh...</t>
         </is>
       </c>
     </row>
@@ -11915,9 +11807,9 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L644" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...  </t>
+      <c r="L644" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
         </is>
       </c>
     </row>
@@ -11941,9 +11833,9 @@
           <t>...D-</t>
         </is>
       </c>
-      <c r="L645" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...D-  </t>
+      <c r="L645" s="32" t="inlineStr">
+        <is>
+          <t>...E-</t>
         </is>
       </c>
     </row>
@@ -11982,9 +11874,9 @@
           <t>...Don't look!</t>
         </is>
       </c>
-      <c r="L647" t="inlineStr">
-        <is>
-          <t xml:space="preserve">...Não olhe!  </t>
+      <c r="L647" s="32" t="inlineStr">
+        <is>
+          <t>...Não olhe!</t>
         </is>
       </c>
     </row>
@@ -12004,9 +11896,9 @@
           <t>Ah, Lady Farris...!</t>
         </is>
       </c>
-      <c r="L648" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ah, Lady Farris...!  </t>
+      <c r="L648" s="32" t="inlineStr">
+        <is>
+          <t>Ah, Lady Farris...!</t>
         </is>
       </c>
     </row>
@@ -12026,9 +11918,9 @@
           <t xml:space="preserve">She ran away... </t>
         </is>
       </c>
-      <c r="L649" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Ela fugiu...  </t>
+      <c r="L649" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Ela fugiu... </t>
         </is>
       </c>
     </row>
@@ -12116,9 +12008,9 @@
           <t>Lady Farris, have you seen Kettle around? Corgon made a real mess of my watering can, and I was hoping Kettle could patch it up, but he's nowhere to be found.</t>
         </is>
       </c>
-      <c r="L659" t="inlineStr">
-        <is>
-          <t>Lady Farris, você viu o Kettle por aí? Corgon fez uma bagunça danada no meu regador, e eu esperava que o Kettle pudesse dar um jeito, mas ele sumiu.</t>
+      <c r="L659" s="32" t="inlineStr">
+        <is>
+          <t>Lady Farris, viu o Kettle por aí? O Corgon destruiu meu regador de verdade, e eu esperava que o Kettle consertasse, mas ele não aparece em lugar nenhum.</t>
         </is>
       </c>
     </row>
@@ -12141,9 +12033,9 @@
           <t>Now that you mention it, I haven't seen him for quite a while. I was hoping he might mend my cracked pot, as well.</t>
         </is>
       </c>
-      <c r="L660" t="inlineStr">
-        <is>
-          <t>Agora que você mencionou, faz um tempão que não o vejo. Eu esperava que ele consertasse meu pote rachado também.</t>
+      <c r="L660" s="32" t="inlineStr">
+        <is>
+          <t>Agora que comentou, faz um tempo que não o vejo também. Eu esperava que ele consertasse minha panela rachada.</t>
         </is>
       </c>
     </row>
@@ -12161,9 +12053,9 @@
           <t>This is troubling. I asked Quruitzia too, but oddly, just mentioning Kettle's name sets her off in a foul mood.</t>
         </is>
       </c>
-      <c r="L661" t="inlineStr">
-        <is>
-          <t>Isso é preocupante. Perguntei à Quruitzia também, mas, estranhamente, só de mencionar o nome do Kettle ela já fica de mau humor.</t>
+      <c r="L661" s="32" t="inlineStr">
+        <is>
+          <t>Isso é preocupante. Perguntei à Quruitzia também, mas, esquisitamente, só de mencionar o nome de Kettle ela entra numa má cara terrível.</t>
         </is>
       </c>
     </row>
@@ -12186,9 +12078,9 @@
           <t>Well, she is at a delicate age, burdened with many worries. Perhaps we should inquire with Master Demitas.</t>
         </is>
       </c>
-      <c r="L662" t="inlineStr">
-        <is>
-          <t>Bom, ela está numa idade delicada, carregando muitas preocupações. Talvez devêssemos perguntar ao Mestre Demitas.</t>
+      <c r="L662" s="32" t="inlineStr">
+        <is>
+          <t>Bom, ela está numa idade delicada, cheia de preocupações. Talvez devêssemos perguntar ao Mestre Demitas.</t>
         </is>
       </c>
     </row>
@@ -12206,9 +12098,9 @@
           <t>Master Demitas...? Why would you call that ghost a master?</t>
         </is>
       </c>
-      <c r="L663" t="inlineStr">
-        <is>
-          <t>Mestre Demitas...? Por que chamaria aquele fantasma de mestre?</t>
+      <c r="L663" s="32" t="inlineStr">
+        <is>
+          <t>Mestre Demitas...? Por que chamar aquele fantasma de mestre?</t>
         </is>
       </c>
     </row>
@@ -12233,10 +12125,10 @@
 That’s why I’ve chosen to address him respectfully as 'Master.'</t>
         </is>
       </c>
-      <c r="L664" t="inlineStr">
-        <is>
-          <t>Ora, isso não é nada respeitoso, Lorde Loytel. Quanto mais você aprende sobre ele, mais intrigante ele se torna—como uma ruína antiga cheia de segredos ocultos. Dizem que, em vida, ele até se aventurou na replicação de tomos mágicos—um verdadeiro erudito.
-Por isso escolhi tratá-lo respeitosamente como "Mestre".</t>
+      <c r="L664" s="32" t="inlineStr">
+        <is>
+          <t>Ora, isso é pouco respeitoso, Lorde Loytel. Quanto mais se aprende sobre ele, mais intrigante ele fica: como uma ruína antiga cheia de segredos escondidos. Dizem que em vida ele até se arriscou na replicação de tomos mágicos: um erudito de verdade.
+Por isso escolhi tratá-lo com respeito, como 'Mestre'.</t>
         </is>
       </c>
     </row>
@@ -12256,10 +12148,10 @@
 Very well, let’s visit this 'Master' of yours.</t>
         </is>
       </c>
-      <c r="L665" t="inlineStr">
-        <is>
-          <t>Lady Farris... Não, não direi mais nada. Seus olhos sempre brilham quando fala dele.
-Muito bem, vamos visitar esse seu "Mestre".</t>
+      <c r="L665" s="32" t="inlineStr">
+        <is>
+          <t>Lady Farris... Não, não digo mais nada. Seus olhos sempre brilham quando fala dele.
+Muito bem, vamos visitar esse seu 'Mestre'.</t>
         </is>
       </c>
     </row>
@@ -12338,7 +12230,7 @@
           <t>Master Demitas...</t>
         </is>
       </c>
-      <c r="L672" t="inlineStr">
+      <c r="L672" s="32" t="inlineStr">
         <is>
           <t>Mestre Demitas...</t>
         </is>
@@ -12363,9 +12255,9 @@
           <t>Begone.</t>
         </is>
       </c>
-      <c r="L673" t="inlineStr">
-        <is>
-          <t>Sumam daqui.</t>
+      <c r="L673" s="32" t="inlineStr">
+        <is>
+          <t>Retire-se.</t>
         </is>
       </c>
     </row>
@@ -12388,9 +12280,9 @@
           <t>But Master, please grant us a moment!</t>
         </is>
       </c>
-      <c r="L674" t="inlineStr">
-        <is>
-          <t>Mas Mestre, nos conceda um momento!</t>
+      <c r="L674" s="32" t="inlineStr">
+        <is>
+          <t>Mas Mestre, por favor, conceda-nos um momento!</t>
         </is>
       </c>
     </row>
@@ -12413,9 +12305,9 @@
           <t>I recall taking no disciples.</t>
         </is>
       </c>
-      <c r="L675" t="inlineStr">
-        <is>
-          <t>Não me recordo de ter aceitado discípulos.</t>
+      <c r="L675" s="32" t="inlineStr">
+        <is>
+          <t>Não me recordo de ter tomado discípulos.</t>
         </is>
       </c>
     </row>
@@ -12433,9 +12325,9 @@
           <t>Now, now, let's all remain calm. We're looking for Kettle—do you know where he's gone?</t>
         </is>
       </c>
-      <c r="L676" t="inlineStr">
-        <is>
-          <t>Vamos, vamos, mantenhamos a calma. Estamos procurando o Kettle—sabe para onde ele foi?</t>
+      <c r="L676" s="32" t="inlineStr">
+        <is>
+          <t>Ora, ora, vamos manter a calma. Estamos procurando Kettle: sabe para onde ele foi?</t>
         </is>
       </c>
     </row>
@@ -12458,9 +12350,9 @@
           <t>Is that all? Heh heh heh... So, the man has left without a word, has he?</t>
         </is>
       </c>
-      <c r="L677" t="inlineStr">
-        <is>
-          <t>É só isso? Heh heh heh... Então, o homem partiu sem dizer uma palavra, não é?</t>
+      <c r="L677" s="32" t="inlineStr">
+        <is>
+          <t>É só isso? Heh heh heh... Então o homem partiu sem dizer uma palavra, foi?</t>
         </is>
       </c>
     </row>
@@ -12478,7 +12370,7 @@
           <t>Left? To where, and for what purpose?</t>
         </is>
       </c>
-      <c r="L678" t="inlineStr">
+      <c r="L678" s="32" t="inlineStr">
         <is>
           <t>Partiu? Para onde, e com que propósito?</t>
         </is>
@@ -12503,9 +12395,9 @@
           <t>His destination can only be one place—to seek out his former disciple, Issizzle. Perhaps to negotiate.</t>
         </is>
       </c>
-      <c r="L679" t="inlineStr">
-        <is>
-          <t>Seu destino só pode ser um lugar—procurar seu antigo discípulo, Issizzle. Talvez para negociar.</t>
+      <c r="L679" s="32" t="inlineStr">
+        <is>
+          <t>Seu destino só pode ser um lugar: buscar seu antigo discípulo, Issizzle. Talvez para negociar.</t>
         </is>
       </c>
     </row>
@@ -12523,9 +12415,9 @@
           <t>Negotiation? Surely, it's to protect Quruitzia and Corgon... but do we have anything of value to offer? I worry greatly for Kettle’s safety.</t>
         </is>
       </c>
-      <c r="L680" t="inlineStr">
-        <is>
-          <t>Negociar? Certamente é para proteger Quruitzia e Corgon... mas temos algo de valor para oferecer? Estou muito preocupado com a segurança do Kettle.</t>
+      <c r="L680" s="32" t="inlineStr">
+        <is>
+          <t>Negociar? Certamente é para proteger Quruitzia e Corgon... mas temos algo de valor a oferecer? Preocupo-me muito com a segurança de Kettle.</t>
         </is>
       </c>
     </row>
@@ -12550,10 +12442,10 @@
 Heh heh heh... How charmingly naive. Hast thou never considered that those two might themselves be bargaining chips?</t>
         </is>
       </c>
-      <c r="L681" t="inlineStr">
-        <is>
-          <t>...Proteger a criança dragão e a bruxa de olhos doentes?
-Heh heh heh... Que ingenuidade encantadora. Já consideraste que aqueles dois podem ser, eles mesmos, moedas de troca?</t>
+      <c r="L681" s="32" t="inlineStr">
+        <is>
+          <t>...Para proteger o filhote de dragão e a bruxa de mau olhado?
+Heh heh heh... Que ingenuidade charmosa. Nunca consideraste que esses dois podem, eles mesmos, serem fichas de barganha?</t>
         </is>
       </c>
     </row>
@@ -12571,9 +12463,9 @@
           <t>Are you suggesting... Kettle would betray us? That’s absurd!</t>
         </is>
       </c>
-      <c r="L682" t="inlineStr">
-        <is>
-          <t>Está sugerindo... que o Kettle nos trairia? Isso é absurdo!</t>
+      <c r="L682" s="32" t="inlineStr">
+        <is>
+          <t>Está sugerindo... que Kettle nos trairia? Que absurdo!</t>
         </is>
       </c>
     </row>
@@ -12596,9 +12488,9 @@
           <t>Heh heh heh... What dost thou truly know of Kettle? Back in the reign of King Zashim, when I yet walked as a man, I knew him well—him and his disciple Issizzle.</t>
         </is>
       </c>
-      <c r="L683" t="inlineStr">
-        <is>
-          <t>Heh heh heh... O que sabes tu verdadeiramente sobre Kettle? No reinado do Rei Zashim, quando eu ainda caminhava como homem, eu o conhecia bem — a ele e a seu discípulo Issizzle.</t>
+      <c r="L683" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh... O que sabes de verdade sobre Kettle? No reinado do rei Zashim, quando ainda andava como homem, eu o conhecia bem: a ele e a seu discípulo Issizzle.</t>
         </is>
       </c>
     </row>
@@ -12623,10 +12515,10 @@
 ...What the two whispered of within those walls, I know not. Yet when Kettle emerged, his hands were free of blood.</t>
         </is>
       </c>
-      <c r="L684" t="inlineStr">
-        <is>
-          <t>Quando Kettle foi confrontar Issizzle, que já estava enredado pela Pedra Mágica, eu estava lá.
-...O que os dois sussurraram dentro daquelas paredes, eu não sei. Porém, quando Kettle emergiu, suas mãos estavam livres de sangue.</t>
+      <c r="L684" s="32" t="inlineStr">
+        <is>
+          <t>Quando Kettle foi confrontar Issizzle, já preso pela Pedra Mágica, eu estava lá.
+...O que os dois sussurraram dentro daquelas paredes, não sei. Mas quando Kettle saiu, suas mãos estavam limpas de sangue.</t>
         </is>
       </c>
     </row>
@@ -12648,16 +12540,16 @@
       </c>
       <c r="K685" s="36" t="inlineStr">
         <is>
-          <t>Soon after, a figure cloaked in black bagan to visit Kettle, time and again, as though the bond between master and student had never been severed.
+          <t>Soon after, a figure cloaked in black began to visit Kettle, time and again, as though the bond between master and student had never been severed.
 A man in black... heh heh heh... indeed, Issizzle still remained human then.
 But thou knowest well what dread monster the Magic Stone eventually made of him. An unholy darkness, a necromancer who commands the dead... whose whispered name strikes terror into children and adults alike.</t>
         </is>
       </c>
-      <c r="L685" t="inlineStr">
-        <is>
-          <t>Pouco depois, uma figura envolta em negro começou a visitar Kettle, vez após outra, como se o laço entre mestre e discípulo jamais tivesse sido rompido.
-Um homem de negro... heh heh heh... de fato, Issizzle ainda permanecia humano então.
-Mas tu bem sabes que monstro terrível a Pedra Mágica acabou fazendo dele. Uma escuridão profana, um necromante que comanda os mortos... cujo nome sussurrado aterroriza crianças e adultos.</t>
+      <c r="L685" s="32" t="inlineStr">
+        <is>
+          <t>Pouco depois, uma figura de capa preta começou a visitar Kettle, vez após vez, como se o vínculo entre mestre e discípulo nunca tivesse se rompido.
+Um homem de preto... heh heh heh... de fato, Issizzle ainda era humano então.
+Mas tu sabes bem que monstro medonho a Pedra Mágica acabou fazendo dele. Uma escuridão ímpia, um necromante que comanda os mortos... cujo nome sussurrado arrepia crianças e adultos igualmente.</t>
         </is>
       </c>
     </row>
@@ -12682,10 +12574,10 @@
 I remember it well. Whenever he spoke of the Magic Stone, his voice trembled with barely contained fervor and heat.</t>
         </is>
       </c>
-      <c r="L686" t="inlineStr">
-        <is>
-          <t>Dize-me, foi pena que conteve a mão de Kettle naquele dia, ou foi um propósito oculto dele próprio?
-Eu me lembro bem. Sempre que falava da Pedra Mágica, sua voz tremia com um fervor e calor mal contidos.</t>
+      <c r="L686" s="32" t="inlineStr">
+        <is>
+          <t>Dize-me, foi piedade que segurou a mão de Kettle naquele dia, ou era um propósito oculto dele próprio?
+Lembro bem. Toda vez que falava da Pedra Mágica, sua voz tremia de um fervor e um calor mal contidos.</t>
         </is>
       </c>
     </row>
@@ -12708,9 +12600,9 @@
           <t>He said Issizzle was captivated by the Stone. Heh heh heh... Perhaps he, too, is but another soul bound by its wicked allure.</t>
         </is>
       </c>
-      <c r="L687" t="inlineStr">
-        <is>
-          <t>Ele disse que Issizzle estava cativado pela Pedra. Heh heh heh... Talvez ele também não passe de outra alma aprisionada por seu maligno fascínio.</t>
+      <c r="L687" s="32" t="inlineStr">
+        <is>
+          <t>Ele disse que Issizzle estava cativado pela Pedra. Heh heh heh... Talvez ele também seja apenas mais uma alma presa pelo seu perverso encanto.</t>
         </is>
       </c>
     </row>
@@ -12736,9 +12628,9 @@
           <t>No... I can’t believe it. Not Kettle...</t>
         </is>
       </c>
-      <c r="L689" t="inlineStr">
-        <is>
-          <t>Não... Não posso acreditar nisso. Não Kettle...</t>
+      <c r="L689" s="32" t="inlineStr">
+        <is>
+          <t>Não... Não posso acreditar. Não o Kettle...</t>
         </is>
       </c>
     </row>
@@ -12758,10 +12650,10 @@
 Kettle is a riddle, to be sure, I cannot even say for certain if he is human. But considering I’m living with a floating ragged ghost nowadays, on top of a dragon hatchling, and the descendant of an ancient witch, I suppose such questions hardly matter anymore... Oh, no offense meant by 'ragged ghost.'</t>
         </is>
       </c>
-      <c r="L690" t="inlineStr">
-        <is>
-          <t>Nem eu.
-Kettle é um enigma, com certeza. Não posso nem dizer ao certo se ele é humano. Mas considerando que vivo agora com um fantasma esfarrapado flutuante, além de um filhote de dragão e a descendente de uma antiga bruxa, suponho que tais questões já não importam mais... Ah, sem ofensas pelo 'fantasma esfarrapado'.</t>
+      <c r="L690" s="32" t="inlineStr">
+        <is>
+          <t>Eu também não.
+Kettle é um enigma, sem dúvida: não sei nem afirmar se ele é humano. Mas considerando que hoje eu moro com um fantasma esfarrapado flutuante, ainda por cima de um filhote de dragão e de uma descendente de bruxa antiga, acho que essas perguntas já importam pouco... Ah, sem ofensa com o 'fantasma esfarrapado'.</t>
         </is>
       </c>
     </row>
@@ -12784,9 +12676,9 @@
           <t>...Call me as thou wilt.</t>
         </is>
       </c>
-      <c r="L691" t="inlineStr">
-        <is>
-          <t>...Chama-me como quiseres.</t>
+      <c r="L691" s="32" t="inlineStr">
+        <is>
+          <t>...Chame-me como quiseres.</t>
         </is>
       </c>
     </row>
@@ -12804,9 +12696,9 @@
           <t>Regardless, whatever Kettle’s intentions may be, we have no choice but to trust him and await his return. I'm afraid your cracked pot must wait, Lady Farris.</t>
         </is>
       </c>
-      <c r="L692" t="inlineStr">
-        <is>
-          <t>Independentemente disso, quaisquer que sejam as intenções de Kettle, não temos escolha senão confiar nele e aguardar seu retorno. Receio que teu pote rachado terá que esperar, Lady Farris.</t>
+      <c r="L692" s="32" t="inlineStr">
+        <is>
+          <t>Ainda assim, sejam quais forem as intenções de Kettle, não temos escolha a não ser confiar nele e aguardar seu retorno. Temo que sua panela rachada terá de esperar, Lady Farris.</t>
         </is>
       </c>
     </row>
@@ -12829,9 +12721,9 @@
           <t>That’s quite all right. Though, Corgon has taken quite a liking to chewing through my frying pan as well. Heh, I imagine Kettle will be quite busy when he returns.</t>
         </is>
       </c>
-      <c r="L693" t="inlineStr">
-        <is>
-          <t>Tudo bem. Embora Corgon tenha criado um gosto especial por roer minha frigideira também. Heh, imagino que Kettle terá muito trabalho quando voltar.</t>
+      <c r="L693" s="32" t="inlineStr">
+        <is>
+          <t>Tudo bem. Ainda assim, o Corgon também pegou gosto de roer minha frigideira. Heh, imagino que o Kettle vai ter muito serviço quando voltar.</t>
         </is>
       </c>
     </row>
@@ -12854,7 +12746,7 @@
           <t>...</t>
         </is>
       </c>
-      <c r="L694" t="inlineStr">
+      <c r="L694" s="32" t="inlineStr">
         <is>
           <t>...</t>
         </is>
@@ -12882,9 +12774,9 @@
           <t>Heh heh heh... Speaking with thee muddles my wits. Here, take this bracelet—I no longer have need of it.</t>
         </is>
       </c>
-      <c r="L696" t="inlineStr">
-        <is>
-          <t>Heh heh heh... Falar contigo embaralha minha mente. Toma, aceita este bracelete — não tenho mais necessidade dele.</t>
+      <c r="L696" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh... Conversar contigo embaralha meus sentidos. Toma, leva esta pulseira: não tenho mais uso para ela.</t>
         </is>
       </c>
     </row>
@@ -12902,7 +12794,7 @@
           <t>What is this?</t>
         </is>
       </c>
-      <c r="L697" t="inlineStr">
+      <c r="L697" s="32" t="inlineStr">
         <is>
           <t>O que é isto?</t>
         </is>
@@ -12924,13 +12816,13 @@
       </c>
       <c r="K698" s="36" t="inlineStr">
         <is>
-          <t xml:space="preserve">In the shadow of the eastern mountains of Mysiria lies a dark, ancient forest. There, thou wilt find the village of the Exiles—my kin, my kindred. It is shielded by a barrier, yet this bracelet shall grant thee passage.
+          <t xml:space="preserve">In the shadow of the eastern mountains of Mysilia lies a dark, ancient forest. There, thou wilt find the village of the Exiles—my kin, my kindred. It is shielded by a barrier, yet this bracelet shall grant thee passage.
 </t>
         </is>
       </c>
-      <c r="L698" t="inlineStr">
-        <is>
-          <t xml:space="preserve">À sombra das montanhas orientais de Mysiria, há uma floresta antiga e sombria. Lá, encontrarás a aldeia dos Exilados — meu povo, meus parentes. Ela é protegida por uma barreira, mas este bracelete te concederá passagem.
+      <c r="L698" s="32" t="inlineStr">
+        <is>
+          <t xml:space="preserve">À sombra das montanhas ao leste de Mysilia há uma floresta escura e antiga. Ali encontrarás a vila dos Exilados: minha família, meu povo. Ela é protegida por uma barreira, mas esta pulseira te dará passagem.
 </t>
         </is>
       </c>
@@ -12954,9 +12846,9 @@
           <t>Seek out their elder, Bicerin. A cunning old wretch, yet one who holds knowledge long lost to the world. Should thou find thyself facing Issizzle or even Kettle, the elder’s wisdom may yet prove of use.</t>
         </is>
       </c>
-      <c r="L699" t="inlineStr">
-        <is>
-          <t>Procura pelo ancião deles, Bicerin. Um velho astuto, mas que guarda conhecimentos há muito perdidos para o mundo. Se te vires diante de Issizzle ou até mesmo de Kettle, a sabedoria do ancião ainda pode ser útil.</t>
+      <c r="L699" s="32" t="inlineStr">
+        <is>
+          <t>Procurem o ancião deles, Bicerin. Um velho trapaceiro esperto, mas que guarda conhecimento há muito perdido para o mundo. Se por acaso enfrentares Issizzle ou até Kettle, a sabedoria do ancião pode ainda ser útil.</t>
         </is>
       </c>
     </row>
@@ -12979,9 +12871,9 @@
           <t>An Exile’s village... The name alone sets my heart racing with curiosity.</t>
         </is>
       </c>
-      <c r="L700" t="inlineStr">
-        <is>
-          <t>Uma aldeia de Exilados... Só o nome já faz meu coração acelerar de curiosidade.</t>
+      <c r="L700" s="32" t="inlineStr">
+        <is>
+          <t>A vila dos Exilados... Só o nome já acelera meu coração de curiosidade.</t>
         </is>
       </c>
     </row>
@@ -12999,9 +12891,9 @@
           <t>Hm... Intriguing, but why offer us such aid?</t>
         </is>
       </c>
-      <c r="L701" t="inlineStr">
-        <is>
-          <t>Hm... Intrigante, mas por que nos oferecer tal ajuda?</t>
+      <c r="L701" s="32" t="inlineStr">
+        <is>
+          <t>Hum... Intrigante, mas por que nos oferecer tal ajuda?</t>
         </is>
       </c>
     </row>
@@ -13026,10 +12918,10 @@
 Verily, thou art about to stand against the one closest to the gods in this realm.</t>
         </is>
       </c>
-      <c r="L702" t="inlineStr">
-        <is>
-          <t>Heh heh heh... Por diversão ociosa, talvez. E, na verdade, não seria injusto demais de outra forma?
-Em verdade, estás prestes a enfrentar aquele que está mais próximo dos deuses neste reino.</t>
+      <c r="L702" s="32" t="inlineStr">
+        <is>
+          <t>Heh heh heh... Por diversão ociosa, talvez. E, em verdade, não seria injusto demais o contrário?
+Na verdade, tu estás prestes a enfrentar aquele que está mais perto dos deuses neste reino.</t>
         </is>
       </c>
     </row>
@@ -13058,8 +12950,942 @@
         </is>
       </c>
     </row>
+    <row r="711" ht="12.8" customHeight="1" s="34">
+      <c r="A711" s="32" t="inlineStr">
+        <is>
+          <t>quest_stone_dream</t>
+        </is>
+      </c>
+      <c r="F711" s="32" t="n"/>
+    </row>
+    <row r="712" ht="12.8" customHeight="1" s="34">
+      <c r="D712" s="36" t="n"/>
+      <c r="E712" s="32" t="inlineStr">
+        <is>
+          <t>acceptQuest</t>
+        </is>
+      </c>
+      <c r="F712" s="44" t="inlineStr">
+        <is>
+          <t>stone_dream</t>
+        </is>
+      </c>
+      <c r="G712" s="36" t="n"/>
+    </row>
+    <row r="713" ht="12.8" customHeight="1" s="34">
+      <c r="D713" s="36" t="n"/>
+      <c r="E713" s="36" t="inlineStr">
+        <is>
+          <t>stopBGM</t>
+        </is>
+      </c>
+      <c r="F713" s="47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G713" s="36" t="n"/>
+    </row>
+    <row r="714" ht="12.8" customHeight="1" s="34">
+      <c r="D714" s="36" t="n"/>
+      <c r="E714" s="36" t="inlineStr">
+        <is>
+          <t>fadeOut</t>
+        </is>
+      </c>
+      <c r="F714" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G714" s="36" t="n"/>
+    </row>
+    <row r="715" ht="12.8" customHeight="1" s="34">
+      <c r="D715" s="36" t="n"/>
+      <c r="E715" s="36" t="inlineStr">
+        <is>
+          <t>setBG</t>
+        </is>
+      </c>
+      <c r="F715" s="53" t="inlineStr">
+        <is>
+          <t>bg3</t>
+        </is>
+      </c>
+      <c r="G715" s="36" t="n"/>
+    </row>
+    <row r="716" ht="12.8" customHeight="1" s="34">
+      <c r="D716" s="36" t="n"/>
+      <c r="E716" s="36" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="F716" s="47" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="G716" s="36" t="n"/>
+    </row>
+    <row r="717" ht="12.8" customHeight="1" s="34">
+      <c r="D717" s="36" t="n"/>
+      <c r="E717" s="36" t="inlineStr">
+        <is>
+          <t>fadeIn</t>
+        </is>
+      </c>
+      <c r="F717" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G717" s="36" t="n"/>
+    </row>
+    <row r="718" ht="13.8" customHeight="1" s="34">
+      <c r="F718" s="32" t="n"/>
+      <c r="J718" s="43" t="n"/>
+      <c r="K718" s="60" t="n"/>
+    </row>
+    <row r="719" ht="23.85" customHeight="1" s="34">
+      <c r="F719" s="32" t="n"/>
+      <c r="I719" s="38" t="n">
+        <v>426</v>
+      </c>
+      <c r="J719" s="43" t="inlineStr">
+        <is>
+          <t>ふぅ、これだけ拠点が大きくなると、帳簿を付けるだけでも一苦労だ。</t>
+        </is>
+      </c>
+      <c r="K719" s="40" t="inlineStr">
+        <is>
+          <t>Whew, now that our settlement has grown this large, keeping the books is becoming quite a task.</t>
+        </is>
+      </c>
+      <c r="L719" s="32" t="inlineStr">
+        <is>
+          <t>Ufa, agora que o assentamento cresceu deste tamanho, manter os livros está virando uma tarefa e tanto.</t>
+        </is>
+      </c>
+    </row>
+    <row r="720" ht="23.85" customHeight="1" s="34">
+      <c r="F720" s="32" t="n"/>
+      <c r="I720" s="38" t="n">
+        <v>427</v>
+      </c>
+      <c r="J720" s="43" t="inlineStr">
+        <is>
+          <t>だが、こういう地味な仕事ほど、誰かがきちんとやらねばな。</t>
+        </is>
+      </c>
+      <c r="K720" s="40" t="inlineStr">
+        <is>
+          <t>Still, it's precisely the sort of mundane work that someone must see to properly.</t>
+        </is>
+      </c>
+      <c r="L720" s="32" t="inlineStr">
+        <is>
+          <t>Ainda assim, é justamente o tipo de trabalho mundano que alguém tem de fazer direito.</t>
+        </is>
+      </c>
+    </row>
+    <row r="721" ht="49.95" customHeight="1" s="34">
+      <c r="F721" s="32" t="n"/>
+      <c r="I721" s="38" t="n">
+        <v>428</v>
+      </c>
+      <c r="J721" s="39" t="inlineStr">
+        <is>
+          <t>家畜の餌に、肥料、研磨剤、耐火ブランケット、魔法書代と。
+修繕費は、訓練木人が二体、鍋、三つ。フライパン、二つ、ジョウロ…四つ？</t>
+        </is>
+      </c>
+      <c r="K721" s="61" t="inlineStr">
+        <is>
+          <t>Livestock feed, fertilizer, polishing powders, fireproof blankets, spellbook expenses...
+And for repairs, let's see: two training dummies, three cooking pots, two frying pans, and... four watering cans?</t>
+        </is>
+      </c>
+      <c r="L721" s="32" t="inlineStr">
+        <is>
+          <t>Ração do gado, adubo, pó de polimento, cobertas corta-fogo, despesas de livros de feitiços...
+E nos reparos, vejamos: dois bonecos de treino, três panelas de cozinha, duas frigideiras, e... quatro regadores?</t>
+        </is>
+      </c>
+    </row>
+    <row r="722" ht="13.8" customHeight="1" s="34">
+      <c r="F722" s="32" t="n"/>
+      <c r="I722" s="38" t="n">
+        <v>429</v>
+      </c>
+      <c r="J722" s="38" t="inlineStr">
+        <is>
+          <t>…四つ？</t>
+        </is>
+      </c>
+      <c r="K722" s="40" t="inlineStr">
+        <is>
+          <t>...Four?</t>
+        </is>
+      </c>
+      <c r="L722" s="32" t="inlineStr">
+        <is>
+          <t>...Quatro?</t>
+        </is>
+      </c>
+    </row>
+    <row r="723" ht="49.95" customHeight="1" s="34">
+      <c r="F723" s="32" t="n"/>
+      <c r="I723" s="38" t="n">
+        <v>430</v>
+      </c>
+      <c r="J723" s="39" t="inlineStr">
+        <is>
+          <t>…犯人は明白だな。備品損耗、と。うむ、これでいい。
+ついでにコルゴンの食費も…必要……経費……と……</t>
+        </is>
+      </c>
+      <c r="K723" s="61" t="inlineStr">
+        <is>
+          <t>...The culprit is obvious. "Equipment wear and tear," then. Hmm, that will do.
+And Corgon's food expenses while I'm at it... a... necessary... expenditure...</t>
+        </is>
+      </c>
+      <c r="L723" s="32" t="inlineStr">
+        <is>
+          <t>...O culpado é óbvio. "Desgaste de equipamento", então. Hmm, isso serve.
+E a comida do Corgon, já que estamos... uma... despesa... necessária...</t>
+        </is>
+      </c>
+    </row>
+    <row r="724" ht="13.8" customHeight="1" s="34">
+      <c r="F724" s="32" t="n"/>
+      <c r="I724" s="38" t="n">
+        <v>431</v>
+      </c>
+      <c r="J724" s="43" t="inlineStr">
+        <is>
+          <t>うーん…眠い。</t>
+        </is>
+      </c>
+      <c r="K724" s="61" t="inlineStr">
+        <is>
+          <t>Mmm... I'm getting sleepy.</t>
+        </is>
+      </c>
+      <c r="L724" s="32" t="inlineStr">
+        <is>
+          <t>Hum... estou ficando com sono.</t>
+        </is>
+      </c>
+    </row>
+    <row r="725" ht="13.8" customHeight="1" s="34">
+      <c r="F725" s="32" t="n"/>
+      <c r="I725" s="38" t="n">
+        <v>432</v>
+      </c>
+      <c r="J725" s="43" t="inlineStr">
+        <is>
+          <t>（むにゅ…むにゃ…）</t>
+        </is>
+      </c>
+      <c r="K725" s="61" t="inlineStr">
+        <is>
+          <t>(Mnh... mngh...)</t>
+        </is>
+      </c>
+      <c r="L725" s="32" t="inlineStr">
+        <is>
+          <t>(Mnh... mngh...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="726" ht="13.8" customHeight="1" s="34">
+      <c r="A726" s="36" t="n"/>
+      <c r="B726" s="36" t="n"/>
+      <c r="C726" s="36" t="n"/>
+      <c r="D726" s="36" t="n"/>
+      <c r="F726" s="32" t="n"/>
+      <c r="G726" s="36" t="n"/>
+      <c r="H726" s="36" t="n"/>
+      <c r="I726" s="38" t="n">
+        <v>433</v>
+      </c>
+      <c r="J726" s="43" t="inlineStr">
+        <is>
+          <t>（すや…すや…）</t>
+        </is>
+      </c>
+      <c r="K726" s="61" t="inlineStr">
+        <is>
+          <t>(Zzz... zzz...)</t>
+        </is>
+      </c>
+      <c r="L726" s="36" t="inlineStr">
+        <is>
+          <t>(Zzz... zzz...)</t>
+        </is>
+      </c>
+      <c r="M726" s="32" t="n"/>
+      <c r="N726" s="32" t="n"/>
+    </row>
+    <row r="727" ht="12.8" customHeight="1" s="34">
+      <c r="D727" s="36" t="n"/>
+      <c r="E727" s="36" t="inlineStr">
+        <is>
+          <t>fadeOut</t>
+        </is>
+      </c>
+      <c r="F727" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G727" s="36" t="n"/>
+    </row>
+    <row r="728" ht="12.8" customHeight="1" s="34">
+      <c r="D728" s="36" t="n"/>
+      <c r="E728" s="36" t="inlineStr">
+        <is>
+          <t>fadeIn</t>
+        </is>
+      </c>
+      <c r="F728" s="36" t="n">
+        <v>2</v>
+      </c>
+      <c r="G728" s="36" t="n"/>
+    </row>
+    <row r="729" ht="12.8" customHeight="1" s="34">
+      <c r="D729" s="36" t="n"/>
+      <c r="E729" s="36" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="F729" s="47" t="inlineStr">
+        <is>
+          <t>67</t>
+        </is>
+      </c>
+      <c r="G729" s="36" t="n"/>
+    </row>
+    <row r="730" ht="29.85" customHeight="1" s="34">
+      <c r="A730" s="36" t="n"/>
+      <c r="B730" s="36" t="n"/>
+      <c r="C730" s="36" t="n"/>
+      <c r="D730" s="36" t="n"/>
+      <c r="F730" s="32" t="n"/>
+      <c r="G730" s="58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="H730" s="36" t="n"/>
+      <c r="I730" s="38" t="n">
+        <v>434</v>
+      </c>
+      <c r="J730" s="43" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K730" s="36" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="L730" s="36" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="M730" s="32" t="n"/>
+      <c r="N730" s="32" t="n"/>
+    </row>
+    <row r="731" ht="13.4" customHeight="1" s="34">
+      <c r="F731" s="32" t="n"/>
+      <c r="G731" s="58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I731" s="38" t="n">
+        <v>435</v>
+      </c>
+      <c r="J731" s="43" t="inlineStr">
+        <is>
+          <t>…さん…</t>
+        </is>
+      </c>
+      <c r="K731" s="36" t="inlineStr">
+        <is>
+          <t>...Sir...</t>
+        </is>
+      </c>
+      <c r="L731" s="32" t="inlineStr">
+        <is>
+          <t>...Senhor...</t>
+        </is>
+      </c>
+    </row>
+    <row r="732" ht="13.4" customHeight="1" s="34">
+      <c r="E732" s="36" t="n"/>
+      <c r="F732" s="47" t="n"/>
+      <c r="G732" s="56" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I732" s="38" t="n">
+        <v>436</v>
+      </c>
+      <c r="J732" s="43" t="inlineStr">
+        <is>
+          <t>…ロイテル…さん…</t>
+        </is>
+      </c>
+      <c r="K732" s="40" t="inlineStr">
+        <is>
+          <t>...Sir Loytel...</t>
+        </is>
+      </c>
+      <c r="L732" s="32" t="inlineStr">
+        <is>
+          <t>...Senhor Loytel...</t>
+        </is>
+      </c>
+    </row>
+    <row r="733" ht="13.8" customHeight="1" s="34">
+      <c r="F733" s="32" t="n"/>
+      <c r="G733" s="36" t="n"/>
+      <c r="I733" s="38" t="n">
+        <v>437</v>
+      </c>
+      <c r="J733" s="43" t="inlineStr">
+        <is>
+          <t>（すや…すや…ぅう……）</t>
+        </is>
+      </c>
+      <c r="K733" s="61" t="inlineStr">
+        <is>
+          <t>(Zzz... zzz... nnh......)</t>
+        </is>
+      </c>
+      <c r="L733" s="32" t="inlineStr">
+        <is>
+          <t>(Zzz... zzz... nnh......)</t>
+        </is>
+      </c>
+    </row>
+    <row r="734" ht="29.85" customHeight="1" s="34">
+      <c r="F734" s="32" t="n"/>
+      <c r="G734" s="58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I734" s="38" t="n">
+        <v>438</v>
+      </c>
+      <c r="J734" s="43" t="inlineStr">
+        <is>
+          <t>…やれるよ…</t>
+        </is>
+      </c>
+      <c r="K734" s="61" t="inlineStr">
+        <is>
+          <t>...I can make it...</t>
+        </is>
+      </c>
+      <c r="L734" s="32" t="inlineStr">
+        <is>
+          <t>...Eu aguento...</t>
+        </is>
+      </c>
+    </row>
+    <row r="735" ht="29.85" customHeight="1" s="34">
+      <c r="F735" s="32" t="n"/>
+      <c r="G735" s="58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I735" s="38" t="n">
+        <v>439</v>
+      </c>
+      <c r="J735" s="43" t="inlineStr">
+        <is>
+          <t>ロイテルさん…ボクはまだやれるよ…</t>
+        </is>
+      </c>
+      <c r="K735" s="61" t="inlineStr">
+        <is>
+          <t>Sir Loytel... I can still make it...</t>
+        </is>
+      </c>
+      <c r="L735" s="32" t="inlineStr">
+        <is>
+          <t>Senhor Loytel... eu ainda aguento...</t>
+        </is>
+      </c>
+    </row>
+    <row r="736" ht="29.85" customHeight="1" s="34">
+      <c r="D736" s="36" t="n"/>
+      <c r="E736" s="36" t="n"/>
+      <c r="F736" s="32" t="n"/>
+      <c r="G736" s="58" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I736" s="38" t="n">
+        <v>440</v>
+      </c>
+      <c r="J736" s="43" t="inlineStr">
+        <is>
+          <t>ロイテルさん、私たちを見捨てないで…！</t>
+        </is>
+      </c>
+      <c r="K736" s="40" t="inlineStr">
+        <is>
+          <t>Sir Loytel...Don't abandon us...!</t>
+        </is>
+      </c>
+      <c r="L736" s="32" t="inlineStr">
+        <is>
+          <t>Senhor Loytel...Não nos abandone...!</t>
+        </is>
+      </c>
+    </row>
+    <row r="737" ht="13.8" customHeight="1" s="34">
+      <c r="F737" s="32" t="n"/>
+      <c r="G737" s="36" t="n"/>
+      <c r="I737" s="38" t="n">
+        <v>441</v>
+      </c>
+      <c r="J737" s="43" t="inlineStr">
+        <is>
+          <t>（う…ウウウ…）</t>
+        </is>
+      </c>
+      <c r="K737" s="61" t="inlineStr">
+        <is>
+          <t>(Nn... Nnngh...)</t>
+        </is>
+      </c>
+      <c r="L737" s="32" t="inlineStr">
+        <is>
+          <t>(Nn... Nnngh...)</t>
+        </is>
+      </c>
+    </row>
+    <row r="738" ht="13.8" customHeight="1" s="34">
+      <c r="F738" s="32" t="n"/>
+      <c r="G738" s="32" t="inlineStr">
+        <is>
+          <t>pebble</t>
+        </is>
+      </c>
+      <c r="I738" s="38" t="n">
+        <v>442</v>
+      </c>
+      <c r="J738" s="43" t="inlineStr">
+        <is>
+          <t>ボクたちを使って…ボクたちはまだやれるよ！</t>
+        </is>
+      </c>
+      <c r="K738" s="61" t="inlineStr">
+        <is>
+          <t>Use us... We can still make it!</t>
+        </is>
+      </c>
+      <c r="L738" s="32" t="inlineStr">
+        <is>
+          <t>Usem a gente... A gente ainda aguenta!</t>
+        </is>
+      </c>
+    </row>
+    <row r="739" ht="13.8" customHeight="1" s="34">
+      <c r="F739" s="32" t="n"/>
+      <c r="G739" s="32" t="inlineStr">
+        <is>
+          <t>pebble</t>
+        </is>
+      </c>
+      <c r="I739" s="38" t="n">
+        <v>443</v>
+      </c>
+      <c r="J739" s="43" t="inlineStr">
+        <is>
+          <t>ロイテルさん、私たちを輝かせて！</t>
+        </is>
+      </c>
+      <c r="K739" s="61" t="inlineStr">
+        <is>
+          <t>Sir Loytel, make us shine!</t>
+        </is>
+      </c>
+      <c r="L739" s="32" t="inlineStr">
+        <is>
+          <t>Senhor Loytel, faça a gente brilhar!</t>
+        </is>
+      </c>
+    </row>
+    <row r="740" ht="13.8" customHeight="1" s="34">
+      <c r="E740" s="36" t="inlineStr">
+        <is>
+          <t>stopBGM</t>
+        </is>
+      </c>
+      <c r="F740" s="47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I740" s="38" t="n"/>
+      <c r="J740" s="43" t="n"/>
+      <c r="K740" s="40" t="n"/>
+    </row>
+    <row r="741" ht="13.8" customHeight="1" s="34">
+      <c r="F741" s="32" t="n"/>
+      <c r="G741" s="36" t="n"/>
+      <c r="I741" s="38" t="n">
+        <v>444</v>
+      </c>
+      <c r="J741" s="43" t="inlineStr">
+        <is>
+          <t>（ウウウ…！）</t>
+        </is>
+      </c>
+      <c r="K741" s="61" t="inlineStr">
+        <is>
+          <t>(Nnngh...!)</t>
+        </is>
+      </c>
+      <c r="L741" s="32" t="inlineStr">
+        <is>
+          <t>(Nnngh...!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="742" ht="13.8" customHeight="1" s="34">
+      <c r="F742" s="32" t="n"/>
+      <c r="I742" s="38" t="n">
+        <v>445</v>
+      </c>
+      <c r="J742" s="43" t="inlineStr">
+        <is>
+          <t>（ハッ…！）</t>
+        </is>
+      </c>
+      <c r="K742" s="61" t="inlineStr">
+        <is>
+          <t>(Haah...!)</t>
+        </is>
+      </c>
+      <c r="L742" s="32" t="inlineStr">
+        <is>
+          <t>(Haah...!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="743" ht="13.8" customHeight="1" s="34">
+      <c r="E743" s="36" t="inlineStr">
+        <is>
+          <t>BGM</t>
+        </is>
+      </c>
+      <c r="F743" s="47" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I743" s="38" t="n"/>
+      <c r="J743" s="43" t="n"/>
+      <c r="K743" s="40" t="n"/>
+    </row>
+    <row r="744" ht="59.7" customHeight="1" s="34">
+      <c r="F744" s="32" t="n"/>
+      <c r="G744" s="36" t="n"/>
+      <c r="I744" s="38" t="n">
+        <v>446</v>
+      </c>
+      <c r="J744" s="46" t="inlineStr">
+        <is>
+          <t>はぁ…はぁ…私としたことが、仕事中に眠ってしまったのか。
+それにしても、妙にリアルな夢だった。まるで、石ころが本当に耳元で囁いているかのような…</t>
+        </is>
+      </c>
+      <c r="K744" s="61" t="inlineStr">
+        <is>
+          <t>Haah... haah... To think that I would fall asleep in the middle of my work.
+Even so, that dream felt strangely real. It was almost as though the pebbles themselves were truly whispering into my ear...</t>
+        </is>
+      </c>
+      <c r="L744" s="32" t="inlineStr">
+        <is>
+          <t>Haah... haah... E eu adormecer no meio do trabalho.
+Mesmo assim, aquele sonho pareceu estranhamente real. Era quase como se as pedrinhas mesmas estivessem sussurrando no meu ouvido...</t>
+        </is>
+      </c>
+    </row>
+    <row r="745" ht="13.8" customHeight="1" s="34">
+      <c r="F745" s="32" t="n"/>
+      <c r="G745" s="32" t="inlineStr">
+        <is>
+          <t>farris</t>
+        </is>
+      </c>
+      <c r="I745" s="38" t="n">
+        <v>447</v>
+      </c>
+      <c r="J745" s="43" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K745" s="40" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="L745" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="746" ht="13.8" customHeight="1" s="34">
+      <c r="F746" s="32" t="n"/>
+      <c r="G746" s="36" t="n"/>
+      <c r="I746" s="38" t="n">
+        <v>448</v>
+      </c>
+      <c r="J746" s="43" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K746" s="40" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="L746" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="747" ht="13.8" customHeight="1" s="34">
+      <c r="F747" s="32" t="n"/>
+      <c r="G747" s="32" t="inlineStr">
+        <is>
+          <t>farris</t>
+        </is>
+      </c>
+      <c r="I747" s="38" t="n">
+        <v>449</v>
+      </c>
+      <c r="J747" s="43" t="inlineStr">
+        <is>
+          <t>お疲れのようですね、ロイテル様。うたた寝なさっていたのですか？</t>
+        </is>
+      </c>
+      <c r="K747" s="61" t="inlineStr">
+        <is>
+          <t>You seem tired, Lord Loytel. Were you taking a little nap?</t>
+        </is>
+      </c>
+      <c r="L747" s="32" t="inlineStr">
+        <is>
+          <t>Parece cansado, Lorde Loytel. Estava tirando um cochilinho?</t>
+        </is>
+      </c>
+    </row>
+    <row r="748" ht="13.8" customHeight="1" s="34">
+      <c r="F748" s="32" t="n"/>
+      <c r="G748" s="36" t="n"/>
+      <c r="I748" s="38" t="n">
+        <v>450</v>
+      </c>
+      <c r="J748" s="43" t="inlineStr">
+        <is>
+          <t>ファリスさん…あなたは、そこで何を…</t>
+        </is>
+      </c>
+      <c r="K748" s="40" t="inlineStr">
+        <is>
+          <t>Lady Farris... What were you doing there...?</t>
+        </is>
+      </c>
+      <c r="L748" s="32" t="inlineStr">
+        <is>
+          <t>Lady Farris... O que você estava fazendo aí...?</t>
+        </is>
+      </c>
+    </row>
+    <row r="749" ht="23.85" customHeight="1" s="34">
+      <c r="F749" s="32" t="n"/>
+      <c r="G749" s="32" t="inlineStr">
+        <is>
+          <t>farris</t>
+        </is>
+      </c>
+      <c r="I749" s="38" t="n">
+        <v>451</v>
+      </c>
+      <c r="J749" s="43" t="inlineStr">
+        <is>
+          <t>何も。ただ、小石たちの切なる声に耳を傾けていただけです。</t>
+        </is>
+      </c>
+      <c r="K749" s="40" t="inlineStr">
+        <is>
+          <t>Nothing at all. I was merely listening to the earnest voices of the pebbles.</t>
+        </is>
+      </c>
+      <c r="L749" s="32" t="inlineStr">
+        <is>
+          <t>Nada, nada. Eu só estava ouvindo as vozes sinceras das pedrinhas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="750" ht="13.8" customHeight="1" s="34">
+      <c r="F750" s="32" t="n"/>
+      <c r="G750" s="36" t="n"/>
+      <c r="I750" s="38" t="n">
+        <v>452</v>
+      </c>
+      <c r="J750" s="43" t="inlineStr">
+        <is>
+          <t>…小石は喋りません。</t>
+        </is>
+      </c>
+      <c r="K750" s="61" t="inlineStr">
+        <is>
+          <t>But pebbles do not speak...</t>
+        </is>
+      </c>
+      <c r="L750" s="32" t="inlineStr">
+        <is>
+          <t>Mas pedrinhas não falam...</t>
+        </is>
+      </c>
+    </row>
+    <row r="751" ht="13.8" customHeight="1" s="34">
+      <c r="F751" s="32" t="n"/>
+      <c r="G751" s="36" t="inlineStr">
+        <is>
+          <t>farris</t>
+        </is>
+      </c>
+      <c r="I751" s="38" t="n">
+        <v>453</v>
+      </c>
+      <c r="J751" s="43" t="inlineStr">
+        <is>
+          <t>では、夢だったのでしょう…</t>
+        </is>
+      </c>
+      <c r="K751" s="61" t="inlineStr">
+        <is>
+          <t>Then it must have been a dream...</t>
+        </is>
+      </c>
+      <c r="L751" s="32" t="inlineStr">
+        <is>
+          <t>Então deve ter sido um sonho...</t>
+        </is>
+      </c>
+    </row>
+    <row r="752" ht="13.8" customHeight="1" s="34">
+      <c r="F752" s="32" t="n"/>
+      <c r="G752" s="36" t="n"/>
+      <c r="I752" s="38" t="n">
+        <v>454</v>
+      </c>
+      <c r="J752" s="43" t="inlineStr">
+        <is>
+          <t>…</t>
+        </is>
+      </c>
+      <c r="K752" s="40" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+      <c r="L752" s="32" t="inlineStr">
+        <is>
+          <t>...</t>
+        </is>
+      </c>
+    </row>
+    <row r="753" ht="13.8" customHeight="1" s="34">
+      <c r="F753" s="32" t="n"/>
+      <c r="G753" s="36" t="n"/>
+      <c r="I753" s="38" t="n">
+        <v>455</v>
+      </c>
+      <c r="J753" s="43" t="inlineStr">
+        <is>
+          <t>（夢…だったのかな…？）</t>
+        </is>
+      </c>
+      <c r="K753" s="61" t="inlineStr">
+        <is>
+          <t>(A dream... was it...?)</t>
+        </is>
+      </c>
+      <c r="L753" s="32" t="inlineStr">
+        <is>
+          <t>(Um sonho... era...?)</t>
+        </is>
+      </c>
+    </row>
+    <row r="754" ht="13.8" customHeight="1" s="34">
+      <c r="F754" s="32" t="n"/>
+      <c r="G754" s="36" t="n"/>
+      <c r="I754" s="38" t="n"/>
+      <c r="J754" s="38" t="n"/>
+      <c r="K754" s="40" t="n"/>
+    </row>
+    <row r="755" ht="13.8" customHeight="1" s="34">
+      <c r="E755" s="32" t="inlineStr">
+        <is>
+          <t>stopBGM</t>
+        </is>
+      </c>
+      <c r="F755" s="32" t="n">
+        <v>3</v>
+      </c>
+      <c r="J755" s="38" t="n"/>
+      <c r="K755" s="38" t="n"/>
+    </row>
+    <row r="756" ht="12.8" customHeight="1" s="34">
+      <c r="E756" s="32" t="inlineStr">
+        <is>
+          <t>completeQuest</t>
+        </is>
+      </c>
+      <c r="F756" s="32" t="n"/>
+    </row>
+    <row r="757" ht="12.8" customHeight="1" s="34">
+      <c r="E757" s="32" t="inlineStr">
+        <is>
+          <t>invoke</t>
+        </is>
+      </c>
+      <c r="F757" s="32" t="inlineStr">
+        <is>
+          <t>reward_stone_dream</t>
+        </is>
+      </c>
+    </row>
+    <row r="758" ht="12.8" customHeight="1" s="34">
+      <c r="E758" s="32" t="inlineStr">
+        <is>
+          <t>end</t>
+        </is>
+      </c>
+      <c r="F758" s="32" t="n"/>
+    </row>
   </sheetData>
-  <conditionalFormatting sqref="I4:I106 I108:I339 I341:I553 I597:J598 I599:I601 I611:I614 I616:I656 I658:I1048576 J547:J550 J599 J615:J619 J623 J637 J650:J651 J656">
+  <conditionalFormatting sqref="I4:I106 I108:I339 I341:I553 I597:J598 I599:I601 I611:I614 I616:I656 I658:I1048576 J547:J550 J599 J615:J619 J623 J637 J650:J651 J656 J712:J715 J719:J727 J730:J754">
     <cfRule type="duplicateValues" rank="0" priority="2" equalAverage="0" aboveAverage="0" dxfId="0" text="" percent="0" bottom="0"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I554:I561 I564:I596 I602:I610">
